--- a/web/src/assets/SurvEpi_modele_historique.xlsx
+++ b/web/src/assets/SurvEpi_modele_historique.xlsx
@@ -44,7 +44,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -59,6 +59,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00004E80"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FBE7E5"/>
       </patternFill>
     </fill>
     <fill>
@@ -113,7 +118,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -136,6 +141,7 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -218,24 +224,49 @@
     <author>SurvEpi</author>
   </authors>
   <commentList>
-    <comment ref="C1" authorId="0" shapeId="0">
+    <comment ref="D1" authorId="0" shapeId="0">
+      <text>
+        <t>Confirmés ce jour et déjà décédés au moment de la confirmation.</t>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0" shapeId="0">
+      <text>
+        <t>Parmi les nouveaux cas confirmés du jour (vivants + décédés).</t>
+      </text>
+    </comment>
+    <comment ref="F1" authorId="0" shapeId="0">
+      <text>
+        <t>Cas confirmés vivants les jours précédents, décédés aujourd’hui. Ce ne sont pas de nouveaux cas.</t>
+      </text>
+    </comment>
+    <comment ref="H1" authorId="0" shapeId="0">
+      <text>
+        <t>Suivis à part : jamais ajoutés au cumul des décès parmi les cas confirmés.</t>
+      </text>
+    </comment>
+    <comment ref="I1" authorId="0" shapeId="0">
       <text>
         <t>Chiffre transmis par l'équipe Alertes. Aucun détail d'alerte n'est stocké.</t>
       </text>
     </comment>
-    <comment ref="D1" authorId="0" shapeId="0">
+    <comment ref="J1" authorId="0" shapeId="0">
       <text>
         <t>Pré-rempli avec le report sortant de la veille.</t>
       </text>
     </comment>
-    <comment ref="L1" authorId="0" shapeId="0">
+    <comment ref="R1" authorId="0" shapeId="0">
       <text>
         <t>Pré-rempli avec les contacts à suivre de la veille.</t>
       </text>
     </comment>
-    <comment ref="O1" authorId="0" shapeId="0">
+    <comment ref="U1" authorId="0" shapeId="0">
       <text>
         <t>Contacts des jours précédents listés aujourd’hui. Entrent dans le suivi mais pas dans le taux de listage.</t>
+      </text>
+    </comment>
+    <comment ref="AH1" authorId="0" shapeId="0">
+      <text>
+        <t>Noms des aires de santé qui ont eu leur 1er cas confirmé ce jour-là, séparés par des virgules. Les noms doivent figurer dans la liste de la ZS (ZS &amp; acteurs &gt; Aires de santé). Une AS déjà touchée n’est jamais recomptée.</t>
       </text>
     </comment>
   </commentList>
@@ -531,7 +562,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A39"/>
+  <dimension ref="A1:A48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="140" customWidth="1" min="1" max="1"/>
@@ -588,213 +619,276 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>I. Situation épidémiologique : seulement les événements du jour (nouveaux confirmés vivants / décédés, dont PPL, décès parmi les confirmés déjà connus, guéris). Ne jamais recopier un cumul : l’app recalcule les cumuls à partir des événements et des valeurs initiales de la ZS.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Les décès probables ou communautaires non confirmés vont dans leur colonne à part : ils ne s’ajoutent jamais au cumul des décès.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
           <t>Les reports (investigations en attente, contacts à suivre, non-vus de la veille) se calculent tout seuls à partir du jour précédent : on peut laisser ces colonnes vides.</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>Les lignes incohérentes (ex. plus d’investigations faites que d’alertes) sont signalées à l’import et ne sont pas enregistrées : les corriger puis recharger le fichier.</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>Une fiche déjà saisie dans l’app n’est jamais écrasée. Recharger le fichier corrigé remplace l’historique déjà importé pour les mêmes dates.</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>Si les outils Excel DPS (investigations, suivi des contacts) sont remplis, les charger aussi à l’import : l’app en tire les chiffres manquants. Ce fichier-ci reste prioritaire.</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>Colonnes</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Nouveaux cas confirmés vivants (utile pour la complétude)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Nouveaux cas confirmés décédés (utile pour la complétude) : Confirmés ce jour et déjà décédés au moment de la confirmation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>dont Personnel de Première Ligne (PPL) (utile pour la complétude) : Parmi les nouveaux cas confirmés du jour (vivants + décédés).</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Nouveaux décès parmi les cas confirmés (utile pour la complétude) : Cas confirmés vivants les jours précédents, décédés aujourd’hui. Ce ne sont pas de nouveaux cas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Nouveaux guéris du jour (utile pour la complétude)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Décès probables / communautaires (non confirmés) : Suivis à part : jamais ajoutés au cumul des décès parmi les cas confirmés.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>Alertes validées du jour (utile pour la complétude) : Chiffre transmis par l'équipe Alertes. Aucun détail d'alerte n'est stocké.</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>Report des investigations entrant (utile pour la complétude) : Pré-rempli avec le report sortant de la veille.</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>Réalisées sur les alertes du jour (utile pour la complétude)</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>Réalisées sur le report (reports apurés) (utile pour la complétude)</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>Dont réalisées en moins de 24 h</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>Narratifs attendus</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>Narratifs disponibles</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>Mappings attendus</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>Mappings disponibles</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>Report des contacts (actifs de la veille) (utile pour la complétude) : Pré-rempli avec les contacts à suivre de la veille.</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>Contacts identifiés aujourd’hui (utile pour la complétude)</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>Contacts listés dans les 24 h (utile pour la complétude)</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>Contacts listés hors délai (&gt; 24 h) : Contacts des jours précédents listés aujourd’hui. Entrent dans le suivi mais pas dans le taux de listage.</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>21 jours terminés (utile pour la complétude)</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>Devenus symptomatiques (utile pour la complétude)</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>Devenus cas confirmés (utile pour la complétude)</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>Perdus de vue (utile pour la complétude)</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>Déplacés / transférés (utile pour la complétude)</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>Décédés (utile pour la complétude)</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>Doublons retirés (utile pour la complétude)</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>Contacts vus (utile pour la complétude)</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>Non-vus de la veille</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>dont rattrapés aujourd’hui</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>RECO actifs (utile pour la complétude)</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>Superviseurs RECO</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>Nouvelles AS touchées : Noms des aires de santé qui ont eu leur 1er cas confirmé ce jour-là, séparés par des virgules. Les noms doivent figurer dans la liste de la ZS (ZS &amp; acteurs &gt; Aires de santé). Une AS déjà touchée n’est jamais recomptée.</t>
         </is>
       </c>
     </row>
@@ -809,7 +903,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC3001"/>
+  <dimension ref="A1:AJ3001"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -839,8 +933,15 @@
     <col width="13" customWidth="1" min="25" max="25"/>
     <col width="13" customWidth="1" min="26" max="26"/>
     <col width="13" customWidth="1" min="27" max="27"/>
-    <col width="28" customWidth="1" min="28" max="28"/>
-    <col width="28" customWidth="1" min="29" max="29"/>
+    <col width="13" customWidth="1" min="28" max="28"/>
+    <col width="13" customWidth="1" min="29" max="29"/>
+    <col width="13" customWidth="1" min="30" max="30"/>
+    <col width="13" customWidth="1" min="31" max="31"/>
+    <col width="13" customWidth="1" min="32" max="32"/>
+    <col width="13" customWidth="1" min="33" max="33"/>
+    <col width="28" customWidth="1" min="34" max="34"/>
+    <col width="28" customWidth="1" min="35" max="35"/>
+    <col width="28" customWidth="1" min="36" max="36"/>
   </cols>
   <sheetData>
     <row r="1" ht="78" customHeight="1">
@@ -856,135 +957,170 @@
       </c>
       <c r="C1" s="5" t="inlineStr">
         <is>
-          <t>Alertes validées du jour</t>
+          <t>Nouveaux cas confirmés vivants</t>
         </is>
       </c>
       <c r="D1" s="5" t="inlineStr">
         <is>
-          <t>Report des investigations entrant</t>
+          <t>Nouveaux cas confirmés décédés</t>
         </is>
       </c>
       <c r="E1" s="5" t="inlineStr">
         <is>
-          <t>Réalisées sur les alertes du jour</t>
+          <t>dont Personnel de Première Ligne (PPL)</t>
         </is>
       </c>
       <c r="F1" s="5" t="inlineStr">
         <is>
-          <t>Réalisées sur le report (reports apurés)</t>
+          <t>Nouveaux décès parmi les cas confirmés</t>
         </is>
       </c>
       <c r="G1" s="5" t="inlineStr">
         <is>
-          <t>Dont réalisées en moins de 24 h</t>
+          <t>Nouveaux guéris du jour</t>
         </is>
       </c>
       <c r="H1" s="5" t="inlineStr">
         <is>
-          <t>Narratifs attendus</t>
+          <t>Décès probables / communautaires (non confirmés)</t>
         </is>
       </c>
       <c r="I1" s="5" t="inlineStr">
         <is>
-          <t>Narratifs disponibles</t>
+          <t>Alertes validées du jour</t>
         </is>
       </c>
       <c r="J1" s="5" t="inlineStr">
         <is>
-          <t>Mappings attendus</t>
+          <t>Report des investigations entrant</t>
         </is>
       </c>
       <c r="K1" s="5" t="inlineStr">
         <is>
-          <t>Mappings disponibles</t>
+          <t>Réalisées sur les alertes du jour</t>
         </is>
       </c>
       <c r="L1" s="5" t="inlineStr">
         <is>
-          <t>Report des contacts (actifs de la veille)</t>
+          <t>Réalisées sur le report (reports apurés)</t>
         </is>
       </c>
       <c r="M1" s="5" t="inlineStr">
         <is>
-          <t>Contacts identifiés aujourd’hui</t>
+          <t>Dont réalisées en moins de 24 h</t>
         </is>
       </c>
       <c r="N1" s="5" t="inlineStr">
         <is>
-          <t>Contacts listés dans les 24 h</t>
+          <t>Narratifs attendus</t>
         </is>
       </c>
       <c r="O1" s="5" t="inlineStr">
         <is>
-          <t>Contacts listés hors délai (&gt; 24 h)</t>
+          <t>Narratifs disponibles</t>
         </is>
       </c>
       <c r="P1" s="5" t="inlineStr">
         <is>
-          <t>21 jours terminés</t>
+          <t>Mappings attendus</t>
         </is>
       </c>
       <c r="Q1" s="5" t="inlineStr">
         <is>
-          <t>Devenus symptomatiques</t>
+          <t>Mappings disponibles</t>
         </is>
       </c>
       <c r="R1" s="5" t="inlineStr">
         <is>
-          <t>Devenus cas confirmés</t>
+          <t>Report des contacts (actifs de la veille)</t>
         </is>
       </c>
       <c r="S1" s="5" t="inlineStr">
         <is>
-          <t>Perdus de vue</t>
+          <t>Contacts identifiés aujourd’hui</t>
         </is>
       </c>
       <c r="T1" s="5" t="inlineStr">
         <is>
-          <t>Déplacés / transférés</t>
+          <t>Contacts listés dans les 24 h</t>
         </is>
       </c>
       <c r="U1" s="5" t="inlineStr">
         <is>
-          <t>Décédés</t>
+          <t>Contacts listés hors délai (&gt; 24 h)</t>
         </is>
       </c>
       <c r="V1" s="5" t="inlineStr">
         <is>
-          <t>Doublons retirés</t>
+          <t>21 jours terminés</t>
         </is>
       </c>
       <c r="W1" s="5" t="inlineStr">
         <is>
-          <t>Contacts vus</t>
+          <t>Devenus symptomatiques</t>
         </is>
       </c>
       <c r="X1" s="5" t="inlineStr">
         <is>
-          <t>Non-vus de la veille</t>
+          <t>Devenus cas confirmés</t>
         </is>
       </c>
       <c r="Y1" s="5" t="inlineStr">
         <is>
-          <t>dont rattrapés aujourd’hui</t>
+          <t>Perdus de vue</t>
         </is>
       </c>
       <c r="Z1" s="5" t="inlineStr">
         <is>
-          <t>RECO actifs</t>
+          <t>Déplacés / transférés</t>
         </is>
       </c>
       <c r="AA1" s="5" t="inlineStr">
         <is>
-          <t>Superviseurs RECO</t>
+          <t>Décédés</t>
         </is>
       </c>
       <c r="AB1" s="5" t="inlineStr">
         <is>
+          <t>Doublons retirés</t>
+        </is>
+      </c>
+      <c r="AC1" s="5" t="inlineStr">
+        <is>
+          <t>Contacts vus</t>
+        </is>
+      </c>
+      <c r="AD1" s="5" t="inlineStr">
+        <is>
+          <t>Non-vus de la veille</t>
+        </is>
+      </c>
+      <c r="AE1" s="5" t="inlineStr">
+        <is>
+          <t>dont rattrapés aujourd’hui</t>
+        </is>
+      </c>
+      <c r="AF1" s="5" t="inlineStr">
+        <is>
+          <t>RECO actifs</t>
+        </is>
+      </c>
+      <c r="AG1" s="5" t="inlineStr">
+        <is>
+          <t>Superviseurs RECO</t>
+        </is>
+      </c>
+      <c r="AH1" s="5" t="inlineStr">
+        <is>
+          <t>Nouvelles AS touchées</t>
+        </is>
+      </c>
+      <c r="AI1" s="5" t="inlineStr">
+        <is>
           <t>Commentaire</t>
         </is>
       </c>
-      <c r="AC1" s="5" t="inlineStr">
+      <c r="AJ1" s="5" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
@@ -998,25 +1134,32 @@
       <c r="F2" s="7" t="n"/>
       <c r="G2" s="7" t="n"/>
       <c r="H2" s="7" t="n"/>
-      <c r="I2" s="7" t="n"/>
-      <c r="J2" s="7" t="n"/>
-      <c r="K2" s="7" t="n"/>
+      <c r="I2" s="8" t="n"/>
+      <c r="J2" s="8" t="n"/>
+      <c r="K2" s="8" t="n"/>
       <c r="L2" s="8" t="n"/>
       <c r="M2" s="8" t="n"/>
       <c r="N2" s="8" t="n"/>
       <c r="O2" s="8" t="n"/>
-      <c r="P2" s="9" t="n"/>
-      <c r="Q2" s="9" t="n"/>
+      <c r="P2" s="8" t="n"/>
+      <c r="Q2" s="8" t="n"/>
       <c r="R2" s="9" t="n"/>
       <c r="S2" s="9" t="n"/>
       <c r="T2" s="9" t="n"/>
       <c r="U2" s="9" t="n"/>
-      <c r="V2" s="9" t="n"/>
+      <c r="V2" s="10" t="n"/>
       <c r="W2" s="10" t="n"/>
       <c r="X2" s="10" t="n"/>
       <c r="Y2" s="10" t="n"/>
-      <c r="Z2" s="11" t="n"/>
-      <c r="AA2" s="11" t="n"/>
+      <c r="Z2" s="10" t="n"/>
+      <c r="AA2" s="10" t="n"/>
+      <c r="AB2" s="10" t="n"/>
+      <c r="AC2" s="11" t="n"/>
+      <c r="AD2" s="11" t="n"/>
+      <c r="AE2" s="11" t="n"/>
+      <c r="AF2" s="12" t="n"/>
+      <c r="AG2" s="12" t="n"/>
+      <c r="AH2" s="7" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="6" t="n"/>
@@ -1026,25 +1169,32 @@
       <c r="F3" s="7" t="n"/>
       <c r="G3" s="7" t="n"/>
       <c r="H3" s="7" t="n"/>
-      <c r="I3" s="7" t="n"/>
-      <c r="J3" s="7" t="n"/>
-      <c r="K3" s="7" t="n"/>
+      <c r="I3" s="8" t="n"/>
+      <c r="J3" s="8" t="n"/>
+      <c r="K3" s="8" t="n"/>
       <c r="L3" s="8" t="n"/>
       <c r="M3" s="8" t="n"/>
       <c r="N3" s="8" t="n"/>
       <c r="O3" s="8" t="n"/>
-      <c r="P3" s="9" t="n"/>
-      <c r="Q3" s="9" t="n"/>
+      <c r="P3" s="8" t="n"/>
+      <c r="Q3" s="8" t="n"/>
       <c r="R3" s="9" t="n"/>
       <c r="S3" s="9" t="n"/>
       <c r="T3" s="9" t="n"/>
       <c r="U3" s="9" t="n"/>
-      <c r="V3" s="9" t="n"/>
+      <c r="V3" s="10" t="n"/>
       <c r="W3" s="10" t="n"/>
       <c r="X3" s="10" t="n"/>
       <c r="Y3" s="10" t="n"/>
-      <c r="Z3" s="11" t="n"/>
-      <c r="AA3" s="11" t="n"/>
+      <c r="Z3" s="10" t="n"/>
+      <c r="AA3" s="10" t="n"/>
+      <c r="AB3" s="10" t="n"/>
+      <c r="AC3" s="11" t="n"/>
+      <c r="AD3" s="11" t="n"/>
+      <c r="AE3" s="11" t="n"/>
+      <c r="AF3" s="12" t="n"/>
+      <c r="AG3" s="12" t="n"/>
+      <c r="AH3" s="7" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="6" t="n"/>
@@ -1054,25 +1204,32 @@
       <c r="F4" s="7" t="n"/>
       <c r="G4" s="7" t="n"/>
       <c r="H4" s="7" t="n"/>
-      <c r="I4" s="7" t="n"/>
-      <c r="J4" s="7" t="n"/>
-      <c r="K4" s="7" t="n"/>
+      <c r="I4" s="8" t="n"/>
+      <c r="J4" s="8" t="n"/>
+      <c r="K4" s="8" t="n"/>
       <c r="L4" s="8" t="n"/>
       <c r="M4" s="8" t="n"/>
       <c r="N4" s="8" t="n"/>
       <c r="O4" s="8" t="n"/>
-      <c r="P4" s="9" t="n"/>
-      <c r="Q4" s="9" t="n"/>
+      <c r="P4" s="8" t="n"/>
+      <c r="Q4" s="8" t="n"/>
       <c r="R4" s="9" t="n"/>
       <c r="S4" s="9" t="n"/>
       <c r="T4" s="9" t="n"/>
       <c r="U4" s="9" t="n"/>
-      <c r="V4" s="9" t="n"/>
+      <c r="V4" s="10" t="n"/>
       <c r="W4" s="10" t="n"/>
       <c r="X4" s="10" t="n"/>
       <c r="Y4" s="10" t="n"/>
-      <c r="Z4" s="11" t="n"/>
-      <c r="AA4" s="11" t="n"/>
+      <c r="Z4" s="10" t="n"/>
+      <c r="AA4" s="10" t="n"/>
+      <c r="AB4" s="10" t="n"/>
+      <c r="AC4" s="11" t="n"/>
+      <c r="AD4" s="11" t="n"/>
+      <c r="AE4" s="11" t="n"/>
+      <c r="AF4" s="12" t="n"/>
+      <c r="AG4" s="12" t="n"/>
+      <c r="AH4" s="7" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="n"/>
@@ -1082,25 +1239,32 @@
       <c r="F5" s="7" t="n"/>
       <c r="G5" s="7" t="n"/>
       <c r="H5" s="7" t="n"/>
-      <c r="I5" s="7" t="n"/>
-      <c r="J5" s="7" t="n"/>
-      <c r="K5" s="7" t="n"/>
+      <c r="I5" s="8" t="n"/>
+      <c r="J5" s="8" t="n"/>
+      <c r="K5" s="8" t="n"/>
       <c r="L5" s="8" t="n"/>
       <c r="M5" s="8" t="n"/>
       <c r="N5" s="8" t="n"/>
       <c r="O5" s="8" t="n"/>
-      <c r="P5" s="9" t="n"/>
-      <c r="Q5" s="9" t="n"/>
+      <c r="P5" s="8" t="n"/>
+      <c r="Q5" s="8" t="n"/>
       <c r="R5" s="9" t="n"/>
       <c r="S5" s="9" t="n"/>
       <c r="T5" s="9" t="n"/>
       <c r="U5" s="9" t="n"/>
-      <c r="V5" s="9" t="n"/>
+      <c r="V5" s="10" t="n"/>
       <c r="W5" s="10" t="n"/>
       <c r="X5" s="10" t="n"/>
       <c r="Y5" s="10" t="n"/>
-      <c r="Z5" s="11" t="n"/>
-      <c r="AA5" s="11" t="n"/>
+      <c r="Z5" s="10" t="n"/>
+      <c r="AA5" s="10" t="n"/>
+      <c r="AB5" s="10" t="n"/>
+      <c r="AC5" s="11" t="n"/>
+      <c r="AD5" s="11" t="n"/>
+      <c r="AE5" s="11" t="n"/>
+      <c r="AF5" s="12" t="n"/>
+      <c r="AG5" s="12" t="n"/>
+      <c r="AH5" s="7" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="6" t="n"/>
@@ -1110,25 +1274,32 @@
       <c r="F6" s="7" t="n"/>
       <c r="G6" s="7" t="n"/>
       <c r="H6" s="7" t="n"/>
-      <c r="I6" s="7" t="n"/>
-      <c r="J6" s="7" t="n"/>
-      <c r="K6" s="7" t="n"/>
+      <c r="I6" s="8" t="n"/>
+      <c r="J6" s="8" t="n"/>
+      <c r="K6" s="8" t="n"/>
       <c r="L6" s="8" t="n"/>
       <c r="M6" s="8" t="n"/>
       <c r="N6" s="8" t="n"/>
       <c r="O6" s="8" t="n"/>
-      <c r="P6" s="9" t="n"/>
-      <c r="Q6" s="9" t="n"/>
+      <c r="P6" s="8" t="n"/>
+      <c r="Q6" s="8" t="n"/>
       <c r="R6" s="9" t="n"/>
       <c r="S6" s="9" t="n"/>
       <c r="T6" s="9" t="n"/>
       <c r="U6" s="9" t="n"/>
-      <c r="V6" s="9" t="n"/>
+      <c r="V6" s="10" t="n"/>
       <c r="W6" s="10" t="n"/>
       <c r="X6" s="10" t="n"/>
       <c r="Y6" s="10" t="n"/>
-      <c r="Z6" s="11" t="n"/>
-      <c r="AA6" s="11" t="n"/>
+      <c r="Z6" s="10" t="n"/>
+      <c r="AA6" s="10" t="n"/>
+      <c r="AB6" s="10" t="n"/>
+      <c r="AC6" s="11" t="n"/>
+      <c r="AD6" s="11" t="n"/>
+      <c r="AE6" s="11" t="n"/>
+      <c r="AF6" s="12" t="n"/>
+      <c r="AG6" s="12" t="n"/>
+      <c r="AH6" s="7" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="6" t="n"/>
@@ -1138,25 +1309,32 @@
       <c r="F7" s="7" t="n"/>
       <c r="G7" s="7" t="n"/>
       <c r="H7" s="7" t="n"/>
-      <c r="I7" s="7" t="n"/>
-      <c r="J7" s="7" t="n"/>
-      <c r="K7" s="7" t="n"/>
+      <c r="I7" s="8" t="n"/>
+      <c r="J7" s="8" t="n"/>
+      <c r="K7" s="8" t="n"/>
       <c r="L7" s="8" t="n"/>
       <c r="M7" s="8" t="n"/>
       <c r="N7" s="8" t="n"/>
       <c r="O7" s="8" t="n"/>
-      <c r="P7" s="9" t="n"/>
-      <c r="Q7" s="9" t="n"/>
+      <c r="P7" s="8" t="n"/>
+      <c r="Q7" s="8" t="n"/>
       <c r="R7" s="9" t="n"/>
       <c r="S7" s="9" t="n"/>
       <c r="T7" s="9" t="n"/>
       <c r="U7" s="9" t="n"/>
-      <c r="V7" s="9" t="n"/>
+      <c r="V7" s="10" t="n"/>
       <c r="W7" s="10" t="n"/>
       <c r="X7" s="10" t="n"/>
       <c r="Y7" s="10" t="n"/>
-      <c r="Z7" s="11" t="n"/>
-      <c r="AA7" s="11" t="n"/>
+      <c r="Z7" s="10" t="n"/>
+      <c r="AA7" s="10" t="n"/>
+      <c r="AB7" s="10" t="n"/>
+      <c r="AC7" s="11" t="n"/>
+      <c r="AD7" s="11" t="n"/>
+      <c r="AE7" s="11" t="n"/>
+      <c r="AF7" s="12" t="n"/>
+      <c r="AG7" s="12" t="n"/>
+      <c r="AH7" s="7" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="6" t="n"/>
@@ -1166,25 +1344,32 @@
       <c r="F8" s="7" t="n"/>
       <c r="G8" s="7" t="n"/>
       <c r="H8" s="7" t="n"/>
-      <c r="I8" s="7" t="n"/>
-      <c r="J8" s="7" t="n"/>
-      <c r="K8" s="7" t="n"/>
+      <c r="I8" s="8" t="n"/>
+      <c r="J8" s="8" t="n"/>
+      <c r="K8" s="8" t="n"/>
       <c r="L8" s="8" t="n"/>
       <c r="M8" s="8" t="n"/>
       <c r="N8" s="8" t="n"/>
       <c r="O8" s="8" t="n"/>
-      <c r="P8" s="9" t="n"/>
-      <c r="Q8" s="9" t="n"/>
+      <c r="P8" s="8" t="n"/>
+      <c r="Q8" s="8" t="n"/>
       <c r="R8" s="9" t="n"/>
       <c r="S8" s="9" t="n"/>
       <c r="T8" s="9" t="n"/>
       <c r="U8" s="9" t="n"/>
-      <c r="V8" s="9" t="n"/>
+      <c r="V8" s="10" t="n"/>
       <c r="W8" s="10" t="n"/>
       <c r="X8" s="10" t="n"/>
       <c r="Y8" s="10" t="n"/>
-      <c r="Z8" s="11" t="n"/>
-      <c r="AA8" s="11" t="n"/>
+      <c r="Z8" s="10" t="n"/>
+      <c r="AA8" s="10" t="n"/>
+      <c r="AB8" s="10" t="n"/>
+      <c r="AC8" s="11" t="n"/>
+      <c r="AD8" s="11" t="n"/>
+      <c r="AE8" s="11" t="n"/>
+      <c r="AF8" s="12" t="n"/>
+      <c r="AG8" s="12" t="n"/>
+      <c r="AH8" s="7" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="6" t="n"/>
@@ -1194,25 +1379,32 @@
       <c r="F9" s="7" t="n"/>
       <c r="G9" s="7" t="n"/>
       <c r="H9" s="7" t="n"/>
-      <c r="I9" s="7" t="n"/>
-      <c r="J9" s="7" t="n"/>
-      <c r="K9" s="7" t="n"/>
+      <c r="I9" s="8" t="n"/>
+      <c r="J9" s="8" t="n"/>
+      <c r="K9" s="8" t="n"/>
       <c r="L9" s="8" t="n"/>
       <c r="M9" s="8" t="n"/>
       <c r="N9" s="8" t="n"/>
       <c r="O9" s="8" t="n"/>
-      <c r="P9" s="9" t="n"/>
-      <c r="Q9" s="9" t="n"/>
+      <c r="P9" s="8" t="n"/>
+      <c r="Q9" s="8" t="n"/>
       <c r="R9" s="9" t="n"/>
       <c r="S9" s="9" t="n"/>
       <c r="T9" s="9" t="n"/>
       <c r="U9" s="9" t="n"/>
-      <c r="V9" s="9" t="n"/>
+      <c r="V9" s="10" t="n"/>
       <c r="W9" s="10" t="n"/>
       <c r="X9" s="10" t="n"/>
       <c r="Y9" s="10" t="n"/>
-      <c r="Z9" s="11" t="n"/>
-      <c r="AA9" s="11" t="n"/>
+      <c r="Z9" s="10" t="n"/>
+      <c r="AA9" s="10" t="n"/>
+      <c r="AB9" s="10" t="n"/>
+      <c r="AC9" s="11" t="n"/>
+      <c r="AD9" s="11" t="n"/>
+      <c r="AE9" s="11" t="n"/>
+      <c r="AF9" s="12" t="n"/>
+      <c r="AG9" s="12" t="n"/>
+      <c r="AH9" s="7" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="6" t="n"/>
@@ -1222,25 +1414,32 @@
       <c r="F10" s="7" t="n"/>
       <c r="G10" s="7" t="n"/>
       <c r="H10" s="7" t="n"/>
-      <c r="I10" s="7" t="n"/>
-      <c r="J10" s="7" t="n"/>
-      <c r="K10" s="7" t="n"/>
+      <c r="I10" s="8" t="n"/>
+      <c r="J10" s="8" t="n"/>
+      <c r="K10" s="8" t="n"/>
       <c r="L10" s="8" t="n"/>
       <c r="M10" s="8" t="n"/>
       <c r="N10" s="8" t="n"/>
       <c r="O10" s="8" t="n"/>
-      <c r="P10" s="9" t="n"/>
-      <c r="Q10" s="9" t="n"/>
+      <c r="P10" s="8" t="n"/>
+      <c r="Q10" s="8" t="n"/>
       <c r="R10" s="9" t="n"/>
       <c r="S10" s="9" t="n"/>
       <c r="T10" s="9" t="n"/>
       <c r="U10" s="9" t="n"/>
-      <c r="V10" s="9" t="n"/>
+      <c r="V10" s="10" t="n"/>
       <c r="W10" s="10" t="n"/>
       <c r="X10" s="10" t="n"/>
       <c r="Y10" s="10" t="n"/>
-      <c r="Z10" s="11" t="n"/>
-      <c r="AA10" s="11" t="n"/>
+      <c r="Z10" s="10" t="n"/>
+      <c r="AA10" s="10" t="n"/>
+      <c r="AB10" s="10" t="n"/>
+      <c r="AC10" s="11" t="n"/>
+      <c r="AD10" s="11" t="n"/>
+      <c r="AE10" s="11" t="n"/>
+      <c r="AF10" s="12" t="n"/>
+      <c r="AG10" s="12" t="n"/>
+      <c r="AH10" s="7" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="6" t="n"/>
@@ -1250,25 +1449,32 @@
       <c r="F11" s="7" t="n"/>
       <c r="G11" s="7" t="n"/>
       <c r="H11" s="7" t="n"/>
-      <c r="I11" s="7" t="n"/>
-      <c r="J11" s="7" t="n"/>
-      <c r="K11" s="7" t="n"/>
+      <c r="I11" s="8" t="n"/>
+      <c r="J11" s="8" t="n"/>
+      <c r="K11" s="8" t="n"/>
       <c r="L11" s="8" t="n"/>
       <c r="M11" s="8" t="n"/>
       <c r="N11" s="8" t="n"/>
       <c r="O11" s="8" t="n"/>
-      <c r="P11" s="9" t="n"/>
-      <c r="Q11" s="9" t="n"/>
+      <c r="P11" s="8" t="n"/>
+      <c r="Q11" s="8" t="n"/>
       <c r="R11" s="9" t="n"/>
       <c r="S11" s="9" t="n"/>
       <c r="T11" s="9" t="n"/>
       <c r="U11" s="9" t="n"/>
-      <c r="V11" s="9" t="n"/>
+      <c r="V11" s="10" t="n"/>
       <c r="W11" s="10" t="n"/>
       <c r="X11" s="10" t="n"/>
       <c r="Y11" s="10" t="n"/>
-      <c r="Z11" s="11" t="n"/>
-      <c r="AA11" s="11" t="n"/>
+      <c r="Z11" s="10" t="n"/>
+      <c r="AA11" s="10" t="n"/>
+      <c r="AB11" s="10" t="n"/>
+      <c r="AC11" s="11" t="n"/>
+      <c r="AD11" s="11" t="n"/>
+      <c r="AE11" s="11" t="n"/>
+      <c r="AF11" s="12" t="n"/>
+      <c r="AG11" s="12" t="n"/>
+      <c r="AH11" s="7" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="n"/>
@@ -1278,25 +1484,32 @@
       <c r="F12" s="7" t="n"/>
       <c r="G12" s="7" t="n"/>
       <c r="H12" s="7" t="n"/>
-      <c r="I12" s="7" t="n"/>
-      <c r="J12" s="7" t="n"/>
-      <c r="K12" s="7" t="n"/>
+      <c r="I12" s="8" t="n"/>
+      <c r="J12" s="8" t="n"/>
+      <c r="K12" s="8" t="n"/>
       <c r="L12" s="8" t="n"/>
       <c r="M12" s="8" t="n"/>
       <c r="N12" s="8" t="n"/>
       <c r="O12" s="8" t="n"/>
-      <c r="P12" s="9" t="n"/>
-      <c r="Q12" s="9" t="n"/>
+      <c r="P12" s="8" t="n"/>
+      <c r="Q12" s="8" t="n"/>
       <c r="R12" s="9" t="n"/>
       <c r="S12" s="9" t="n"/>
       <c r="T12" s="9" t="n"/>
       <c r="U12" s="9" t="n"/>
-      <c r="V12" s="9" t="n"/>
+      <c r="V12" s="10" t="n"/>
       <c r="W12" s="10" t="n"/>
       <c r="X12" s="10" t="n"/>
       <c r="Y12" s="10" t="n"/>
-      <c r="Z12" s="11" t="n"/>
-      <c r="AA12" s="11" t="n"/>
+      <c r="Z12" s="10" t="n"/>
+      <c r="AA12" s="10" t="n"/>
+      <c r="AB12" s="10" t="n"/>
+      <c r="AC12" s="11" t="n"/>
+      <c r="AD12" s="11" t="n"/>
+      <c r="AE12" s="11" t="n"/>
+      <c r="AF12" s="12" t="n"/>
+      <c r="AG12" s="12" t="n"/>
+      <c r="AH12" s="7" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="6" t="n"/>
@@ -1306,25 +1519,32 @@
       <c r="F13" s="7" t="n"/>
       <c r="G13" s="7" t="n"/>
       <c r="H13" s="7" t="n"/>
-      <c r="I13" s="7" t="n"/>
-      <c r="J13" s="7" t="n"/>
-      <c r="K13" s="7" t="n"/>
+      <c r="I13" s="8" t="n"/>
+      <c r="J13" s="8" t="n"/>
+      <c r="K13" s="8" t="n"/>
       <c r="L13" s="8" t="n"/>
       <c r="M13" s="8" t="n"/>
       <c r="N13" s="8" t="n"/>
       <c r="O13" s="8" t="n"/>
-      <c r="P13" s="9" t="n"/>
-      <c r="Q13" s="9" t="n"/>
+      <c r="P13" s="8" t="n"/>
+      <c r="Q13" s="8" t="n"/>
       <c r="R13" s="9" t="n"/>
       <c r="S13" s="9" t="n"/>
       <c r="T13" s="9" t="n"/>
       <c r="U13" s="9" t="n"/>
-      <c r="V13" s="9" t="n"/>
+      <c r="V13" s="10" t="n"/>
       <c r="W13" s="10" t="n"/>
       <c r="X13" s="10" t="n"/>
       <c r="Y13" s="10" t="n"/>
-      <c r="Z13" s="11" t="n"/>
-      <c r="AA13" s="11" t="n"/>
+      <c r="Z13" s="10" t="n"/>
+      <c r="AA13" s="10" t="n"/>
+      <c r="AB13" s="10" t="n"/>
+      <c r="AC13" s="11" t="n"/>
+      <c r="AD13" s="11" t="n"/>
+      <c r="AE13" s="11" t="n"/>
+      <c r="AF13" s="12" t="n"/>
+      <c r="AG13" s="12" t="n"/>
+      <c r="AH13" s="7" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="6" t="n"/>
@@ -1334,25 +1554,32 @@
       <c r="F14" s="7" t="n"/>
       <c r="G14" s="7" t="n"/>
       <c r="H14" s="7" t="n"/>
-      <c r="I14" s="7" t="n"/>
-      <c r="J14" s="7" t="n"/>
-      <c r="K14" s="7" t="n"/>
+      <c r="I14" s="8" t="n"/>
+      <c r="J14" s="8" t="n"/>
+      <c r="K14" s="8" t="n"/>
       <c r="L14" s="8" t="n"/>
       <c r="M14" s="8" t="n"/>
       <c r="N14" s="8" t="n"/>
       <c r="O14" s="8" t="n"/>
-      <c r="P14" s="9" t="n"/>
-      <c r="Q14" s="9" t="n"/>
+      <c r="P14" s="8" t="n"/>
+      <c r="Q14" s="8" t="n"/>
       <c r="R14" s="9" t="n"/>
       <c r="S14" s="9" t="n"/>
       <c r="T14" s="9" t="n"/>
       <c r="U14" s="9" t="n"/>
-      <c r="V14" s="9" t="n"/>
+      <c r="V14" s="10" t="n"/>
       <c r="W14" s="10" t="n"/>
       <c r="X14" s="10" t="n"/>
       <c r="Y14" s="10" t="n"/>
-      <c r="Z14" s="11" t="n"/>
-      <c r="AA14" s="11" t="n"/>
+      <c r="Z14" s="10" t="n"/>
+      <c r="AA14" s="10" t="n"/>
+      <c r="AB14" s="10" t="n"/>
+      <c r="AC14" s="11" t="n"/>
+      <c r="AD14" s="11" t="n"/>
+      <c r="AE14" s="11" t="n"/>
+      <c r="AF14" s="12" t="n"/>
+      <c r="AG14" s="12" t="n"/>
+      <c r="AH14" s="7" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="6" t="n"/>
@@ -1362,25 +1589,32 @@
       <c r="F15" s="7" t="n"/>
       <c r="G15" s="7" t="n"/>
       <c r="H15" s="7" t="n"/>
-      <c r="I15" s="7" t="n"/>
-      <c r="J15" s="7" t="n"/>
-      <c r="K15" s="7" t="n"/>
+      <c r="I15" s="8" t="n"/>
+      <c r="J15" s="8" t="n"/>
+      <c r="K15" s="8" t="n"/>
       <c r="L15" s="8" t="n"/>
       <c r="M15" s="8" t="n"/>
       <c r="N15" s="8" t="n"/>
       <c r="O15" s="8" t="n"/>
-      <c r="P15" s="9" t="n"/>
-      <c r="Q15" s="9" t="n"/>
+      <c r="P15" s="8" t="n"/>
+      <c r="Q15" s="8" t="n"/>
       <c r="R15" s="9" t="n"/>
       <c r="S15" s="9" t="n"/>
       <c r="T15" s="9" t="n"/>
       <c r="U15" s="9" t="n"/>
-      <c r="V15" s="9" t="n"/>
+      <c r="V15" s="10" t="n"/>
       <c r="W15" s="10" t="n"/>
       <c r="X15" s="10" t="n"/>
       <c r="Y15" s="10" t="n"/>
-      <c r="Z15" s="11" t="n"/>
-      <c r="AA15" s="11" t="n"/>
+      <c r="Z15" s="10" t="n"/>
+      <c r="AA15" s="10" t="n"/>
+      <c r="AB15" s="10" t="n"/>
+      <c r="AC15" s="11" t="n"/>
+      <c r="AD15" s="11" t="n"/>
+      <c r="AE15" s="11" t="n"/>
+      <c r="AF15" s="12" t="n"/>
+      <c r="AG15" s="12" t="n"/>
+      <c r="AH15" s="7" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="6" t="n"/>
@@ -1390,25 +1624,32 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="7" t="n"/>
       <c r="H16" s="7" t="n"/>
-      <c r="I16" s="7" t="n"/>
-      <c r="J16" s="7" t="n"/>
-      <c r="K16" s="7" t="n"/>
+      <c r="I16" s="8" t="n"/>
+      <c r="J16" s="8" t="n"/>
+      <c r="K16" s="8" t="n"/>
       <c r="L16" s="8" t="n"/>
       <c r="M16" s="8" t="n"/>
       <c r="N16" s="8" t="n"/>
       <c r="O16" s="8" t="n"/>
-      <c r="P16" s="9" t="n"/>
-      <c r="Q16" s="9" t="n"/>
+      <c r="P16" s="8" t="n"/>
+      <c r="Q16" s="8" t="n"/>
       <c r="R16" s="9" t="n"/>
       <c r="S16" s="9" t="n"/>
       <c r="T16" s="9" t="n"/>
       <c r="U16" s="9" t="n"/>
-      <c r="V16" s="9" t="n"/>
+      <c r="V16" s="10" t="n"/>
       <c r="W16" s="10" t="n"/>
       <c r="X16" s="10" t="n"/>
       <c r="Y16" s="10" t="n"/>
-      <c r="Z16" s="11" t="n"/>
-      <c r="AA16" s="11" t="n"/>
+      <c r="Z16" s="10" t="n"/>
+      <c r="AA16" s="10" t="n"/>
+      <c r="AB16" s="10" t="n"/>
+      <c r="AC16" s="11" t="n"/>
+      <c r="AD16" s="11" t="n"/>
+      <c r="AE16" s="11" t="n"/>
+      <c r="AF16" s="12" t="n"/>
+      <c r="AG16" s="12" t="n"/>
+      <c r="AH16" s="7" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="6" t="n"/>
@@ -1418,25 +1659,32 @@
       <c r="F17" s="7" t="n"/>
       <c r="G17" s="7" t="n"/>
       <c r="H17" s="7" t="n"/>
-      <c r="I17" s="7" t="n"/>
-      <c r="J17" s="7" t="n"/>
-      <c r="K17" s="7" t="n"/>
+      <c r="I17" s="8" t="n"/>
+      <c r="J17" s="8" t="n"/>
+      <c r="K17" s="8" t="n"/>
       <c r="L17" s="8" t="n"/>
       <c r="M17" s="8" t="n"/>
       <c r="N17" s="8" t="n"/>
       <c r="O17" s="8" t="n"/>
-      <c r="P17" s="9" t="n"/>
-      <c r="Q17" s="9" t="n"/>
+      <c r="P17" s="8" t="n"/>
+      <c r="Q17" s="8" t="n"/>
       <c r="R17" s="9" t="n"/>
       <c r="S17" s="9" t="n"/>
       <c r="T17" s="9" t="n"/>
       <c r="U17" s="9" t="n"/>
-      <c r="V17" s="9" t="n"/>
+      <c r="V17" s="10" t="n"/>
       <c r="W17" s="10" t="n"/>
       <c r="X17" s="10" t="n"/>
       <c r="Y17" s="10" t="n"/>
-      <c r="Z17" s="11" t="n"/>
-      <c r="AA17" s="11" t="n"/>
+      <c r="Z17" s="10" t="n"/>
+      <c r="AA17" s="10" t="n"/>
+      <c r="AB17" s="10" t="n"/>
+      <c r="AC17" s="11" t="n"/>
+      <c r="AD17" s="11" t="n"/>
+      <c r="AE17" s="11" t="n"/>
+      <c r="AF17" s="12" t="n"/>
+      <c r="AG17" s="12" t="n"/>
+      <c r="AH17" s="7" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="6" t="n"/>
@@ -1446,25 +1694,32 @@
       <c r="F18" s="7" t="n"/>
       <c r="G18" s="7" t="n"/>
       <c r="H18" s="7" t="n"/>
-      <c r="I18" s="7" t="n"/>
-      <c r="J18" s="7" t="n"/>
-      <c r="K18" s="7" t="n"/>
+      <c r="I18" s="8" t="n"/>
+      <c r="J18" s="8" t="n"/>
+      <c r="K18" s="8" t="n"/>
       <c r="L18" s="8" t="n"/>
       <c r="M18" s="8" t="n"/>
       <c r="N18" s="8" t="n"/>
       <c r="O18" s="8" t="n"/>
-      <c r="P18" s="9" t="n"/>
-      <c r="Q18" s="9" t="n"/>
+      <c r="P18" s="8" t="n"/>
+      <c r="Q18" s="8" t="n"/>
       <c r="R18" s="9" t="n"/>
       <c r="S18" s="9" t="n"/>
       <c r="T18" s="9" t="n"/>
       <c r="U18" s="9" t="n"/>
-      <c r="V18" s="9" t="n"/>
+      <c r="V18" s="10" t="n"/>
       <c r="W18" s="10" t="n"/>
       <c r="X18" s="10" t="n"/>
       <c r="Y18" s="10" t="n"/>
-      <c r="Z18" s="11" t="n"/>
-      <c r="AA18" s="11" t="n"/>
+      <c r="Z18" s="10" t="n"/>
+      <c r="AA18" s="10" t="n"/>
+      <c r="AB18" s="10" t="n"/>
+      <c r="AC18" s="11" t="n"/>
+      <c r="AD18" s="11" t="n"/>
+      <c r="AE18" s="11" t="n"/>
+      <c r="AF18" s="12" t="n"/>
+      <c r="AG18" s="12" t="n"/>
+      <c r="AH18" s="7" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="6" t="n"/>
@@ -1474,25 +1729,32 @@
       <c r="F19" s="7" t="n"/>
       <c r="G19" s="7" t="n"/>
       <c r="H19" s="7" t="n"/>
-      <c r="I19" s="7" t="n"/>
-      <c r="J19" s="7" t="n"/>
-      <c r="K19" s="7" t="n"/>
+      <c r="I19" s="8" t="n"/>
+      <c r="J19" s="8" t="n"/>
+      <c r="K19" s="8" t="n"/>
       <c r="L19" s="8" t="n"/>
       <c r="M19" s="8" t="n"/>
       <c r="N19" s="8" t="n"/>
       <c r="O19" s="8" t="n"/>
-      <c r="P19" s="9" t="n"/>
-      <c r="Q19" s="9" t="n"/>
+      <c r="P19" s="8" t="n"/>
+      <c r="Q19" s="8" t="n"/>
       <c r="R19" s="9" t="n"/>
       <c r="S19" s="9" t="n"/>
       <c r="T19" s="9" t="n"/>
       <c r="U19" s="9" t="n"/>
-      <c r="V19" s="9" t="n"/>
+      <c r="V19" s="10" t="n"/>
       <c r="W19" s="10" t="n"/>
       <c r="X19" s="10" t="n"/>
       <c r="Y19" s="10" t="n"/>
-      <c r="Z19" s="11" t="n"/>
-      <c r="AA19" s="11" t="n"/>
+      <c r="Z19" s="10" t="n"/>
+      <c r="AA19" s="10" t="n"/>
+      <c r="AB19" s="10" t="n"/>
+      <c r="AC19" s="11" t="n"/>
+      <c r="AD19" s="11" t="n"/>
+      <c r="AE19" s="11" t="n"/>
+      <c r="AF19" s="12" t="n"/>
+      <c r="AG19" s="12" t="n"/>
+      <c r="AH19" s="7" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="6" t="n"/>
@@ -1502,25 +1764,32 @@
       <c r="F20" s="7" t="n"/>
       <c r="G20" s="7" t="n"/>
       <c r="H20" s="7" t="n"/>
-      <c r="I20" s="7" t="n"/>
-      <c r="J20" s="7" t="n"/>
-      <c r="K20" s="7" t="n"/>
+      <c r="I20" s="8" t="n"/>
+      <c r="J20" s="8" t="n"/>
+      <c r="K20" s="8" t="n"/>
       <c r="L20" s="8" t="n"/>
       <c r="M20" s="8" t="n"/>
       <c r="N20" s="8" t="n"/>
       <c r="O20" s="8" t="n"/>
-      <c r="P20" s="9" t="n"/>
-      <c r="Q20" s="9" t="n"/>
+      <c r="P20" s="8" t="n"/>
+      <c r="Q20" s="8" t="n"/>
       <c r="R20" s="9" t="n"/>
       <c r="S20" s="9" t="n"/>
       <c r="T20" s="9" t="n"/>
       <c r="U20" s="9" t="n"/>
-      <c r="V20" s="9" t="n"/>
+      <c r="V20" s="10" t="n"/>
       <c r="W20" s="10" t="n"/>
       <c r="X20" s="10" t="n"/>
       <c r="Y20" s="10" t="n"/>
-      <c r="Z20" s="11" t="n"/>
-      <c r="AA20" s="11" t="n"/>
+      <c r="Z20" s="10" t="n"/>
+      <c r="AA20" s="10" t="n"/>
+      <c r="AB20" s="10" t="n"/>
+      <c r="AC20" s="11" t="n"/>
+      <c r="AD20" s="11" t="n"/>
+      <c r="AE20" s="11" t="n"/>
+      <c r="AF20" s="12" t="n"/>
+      <c r="AG20" s="12" t="n"/>
+      <c r="AH20" s="7" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="6" t="n"/>
@@ -1530,25 +1799,32 @@
       <c r="F21" s="7" t="n"/>
       <c r="G21" s="7" t="n"/>
       <c r="H21" s="7" t="n"/>
-      <c r="I21" s="7" t="n"/>
-      <c r="J21" s="7" t="n"/>
-      <c r="K21" s="7" t="n"/>
+      <c r="I21" s="8" t="n"/>
+      <c r="J21" s="8" t="n"/>
+      <c r="K21" s="8" t="n"/>
       <c r="L21" s="8" t="n"/>
       <c r="M21" s="8" t="n"/>
       <c r="N21" s="8" t="n"/>
       <c r="O21" s="8" t="n"/>
-      <c r="P21" s="9" t="n"/>
-      <c r="Q21" s="9" t="n"/>
+      <c r="P21" s="8" t="n"/>
+      <c r="Q21" s="8" t="n"/>
       <c r="R21" s="9" t="n"/>
       <c r="S21" s="9" t="n"/>
       <c r="T21" s="9" t="n"/>
       <c r="U21" s="9" t="n"/>
-      <c r="V21" s="9" t="n"/>
+      <c r="V21" s="10" t="n"/>
       <c r="W21" s="10" t="n"/>
       <c r="X21" s="10" t="n"/>
       <c r="Y21" s="10" t="n"/>
-      <c r="Z21" s="11" t="n"/>
-      <c r="AA21" s="11" t="n"/>
+      <c r="Z21" s="10" t="n"/>
+      <c r="AA21" s="10" t="n"/>
+      <c r="AB21" s="10" t="n"/>
+      <c r="AC21" s="11" t="n"/>
+      <c r="AD21" s="11" t="n"/>
+      <c r="AE21" s="11" t="n"/>
+      <c r="AF21" s="12" t="n"/>
+      <c r="AG21" s="12" t="n"/>
+      <c r="AH21" s="7" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="6" t="n"/>
@@ -1558,25 +1834,32 @@
       <c r="F22" s="7" t="n"/>
       <c r="G22" s="7" t="n"/>
       <c r="H22" s="7" t="n"/>
-      <c r="I22" s="7" t="n"/>
-      <c r="J22" s="7" t="n"/>
-      <c r="K22" s="7" t="n"/>
+      <c r="I22" s="8" t="n"/>
+      <c r="J22" s="8" t="n"/>
+      <c r="K22" s="8" t="n"/>
       <c r="L22" s="8" t="n"/>
       <c r="M22" s="8" t="n"/>
       <c r="N22" s="8" t="n"/>
       <c r="O22" s="8" t="n"/>
-      <c r="P22" s="9" t="n"/>
-      <c r="Q22" s="9" t="n"/>
+      <c r="P22" s="8" t="n"/>
+      <c r="Q22" s="8" t="n"/>
       <c r="R22" s="9" t="n"/>
       <c r="S22" s="9" t="n"/>
       <c r="T22" s="9" t="n"/>
       <c r="U22" s="9" t="n"/>
-      <c r="V22" s="9" t="n"/>
+      <c r="V22" s="10" t="n"/>
       <c r="W22" s="10" t="n"/>
       <c r="X22" s="10" t="n"/>
       <c r="Y22" s="10" t="n"/>
-      <c r="Z22" s="11" t="n"/>
-      <c r="AA22" s="11" t="n"/>
+      <c r="Z22" s="10" t="n"/>
+      <c r="AA22" s="10" t="n"/>
+      <c r="AB22" s="10" t="n"/>
+      <c r="AC22" s="11" t="n"/>
+      <c r="AD22" s="11" t="n"/>
+      <c r="AE22" s="11" t="n"/>
+      <c r="AF22" s="12" t="n"/>
+      <c r="AG22" s="12" t="n"/>
+      <c r="AH22" s="7" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="6" t="n"/>
@@ -1586,25 +1869,32 @@
       <c r="F23" s="7" t="n"/>
       <c r="G23" s="7" t="n"/>
       <c r="H23" s="7" t="n"/>
-      <c r="I23" s="7" t="n"/>
-      <c r="J23" s="7" t="n"/>
-      <c r="K23" s="7" t="n"/>
+      <c r="I23" s="8" t="n"/>
+      <c r="J23" s="8" t="n"/>
+      <c r="K23" s="8" t="n"/>
       <c r="L23" s="8" t="n"/>
       <c r="M23" s="8" t="n"/>
       <c r="N23" s="8" t="n"/>
       <c r="O23" s="8" t="n"/>
-      <c r="P23" s="9" t="n"/>
-      <c r="Q23" s="9" t="n"/>
+      <c r="P23" s="8" t="n"/>
+      <c r="Q23" s="8" t="n"/>
       <c r="R23" s="9" t="n"/>
       <c r="S23" s="9" t="n"/>
       <c r="T23" s="9" t="n"/>
       <c r="U23" s="9" t="n"/>
-      <c r="V23" s="9" t="n"/>
+      <c r="V23" s="10" t="n"/>
       <c r="W23" s="10" t="n"/>
       <c r="X23" s="10" t="n"/>
       <c r="Y23" s="10" t="n"/>
-      <c r="Z23" s="11" t="n"/>
-      <c r="AA23" s="11" t="n"/>
+      <c r="Z23" s="10" t="n"/>
+      <c r="AA23" s="10" t="n"/>
+      <c r="AB23" s="10" t="n"/>
+      <c r="AC23" s="11" t="n"/>
+      <c r="AD23" s="11" t="n"/>
+      <c r="AE23" s="11" t="n"/>
+      <c r="AF23" s="12" t="n"/>
+      <c r="AG23" s="12" t="n"/>
+      <c r="AH23" s="7" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="6" t="n"/>
@@ -1614,25 +1904,32 @@
       <c r="F24" s="7" t="n"/>
       <c r="G24" s="7" t="n"/>
       <c r="H24" s="7" t="n"/>
-      <c r="I24" s="7" t="n"/>
-      <c r="J24" s="7" t="n"/>
-      <c r="K24" s="7" t="n"/>
+      <c r="I24" s="8" t="n"/>
+      <c r="J24" s="8" t="n"/>
+      <c r="K24" s="8" t="n"/>
       <c r="L24" s="8" t="n"/>
       <c r="M24" s="8" t="n"/>
       <c r="N24" s="8" t="n"/>
       <c r="O24" s="8" t="n"/>
-      <c r="P24" s="9" t="n"/>
-      <c r="Q24" s="9" t="n"/>
+      <c r="P24" s="8" t="n"/>
+      <c r="Q24" s="8" t="n"/>
       <c r="R24" s="9" t="n"/>
       <c r="S24" s="9" t="n"/>
       <c r="T24" s="9" t="n"/>
       <c r="U24" s="9" t="n"/>
-      <c r="V24" s="9" t="n"/>
+      <c r="V24" s="10" t="n"/>
       <c r="W24" s="10" t="n"/>
       <c r="X24" s="10" t="n"/>
       <c r="Y24" s="10" t="n"/>
-      <c r="Z24" s="11" t="n"/>
-      <c r="AA24" s="11" t="n"/>
+      <c r="Z24" s="10" t="n"/>
+      <c r="AA24" s="10" t="n"/>
+      <c r="AB24" s="10" t="n"/>
+      <c r="AC24" s="11" t="n"/>
+      <c r="AD24" s="11" t="n"/>
+      <c r="AE24" s="11" t="n"/>
+      <c r="AF24" s="12" t="n"/>
+      <c r="AG24" s="12" t="n"/>
+      <c r="AH24" s="7" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="6" t="n"/>
@@ -1642,25 +1939,32 @@
       <c r="F25" s="7" t="n"/>
       <c r="G25" s="7" t="n"/>
       <c r="H25" s="7" t="n"/>
-      <c r="I25" s="7" t="n"/>
-      <c r="J25" s="7" t="n"/>
-      <c r="K25" s="7" t="n"/>
+      <c r="I25" s="8" t="n"/>
+      <c r="J25" s="8" t="n"/>
+      <c r="K25" s="8" t="n"/>
       <c r="L25" s="8" t="n"/>
       <c r="M25" s="8" t="n"/>
       <c r="N25" s="8" t="n"/>
       <c r="O25" s="8" t="n"/>
-      <c r="P25" s="9" t="n"/>
-      <c r="Q25" s="9" t="n"/>
+      <c r="P25" s="8" t="n"/>
+      <c r="Q25" s="8" t="n"/>
       <c r="R25" s="9" t="n"/>
       <c r="S25" s="9" t="n"/>
       <c r="T25" s="9" t="n"/>
       <c r="U25" s="9" t="n"/>
-      <c r="V25" s="9" t="n"/>
+      <c r="V25" s="10" t="n"/>
       <c r="W25" s="10" t="n"/>
       <c r="X25" s="10" t="n"/>
       <c r="Y25" s="10" t="n"/>
-      <c r="Z25" s="11" t="n"/>
-      <c r="AA25" s="11" t="n"/>
+      <c r="Z25" s="10" t="n"/>
+      <c r="AA25" s="10" t="n"/>
+      <c r="AB25" s="10" t="n"/>
+      <c r="AC25" s="11" t="n"/>
+      <c r="AD25" s="11" t="n"/>
+      <c r="AE25" s="11" t="n"/>
+      <c r="AF25" s="12" t="n"/>
+      <c r="AG25" s="12" t="n"/>
+      <c r="AH25" s="7" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="6" t="n"/>
@@ -1670,25 +1974,32 @@
       <c r="F26" s="7" t="n"/>
       <c r="G26" s="7" t="n"/>
       <c r="H26" s="7" t="n"/>
-      <c r="I26" s="7" t="n"/>
-      <c r="J26" s="7" t="n"/>
-      <c r="K26" s="7" t="n"/>
+      <c r="I26" s="8" t="n"/>
+      <c r="J26" s="8" t="n"/>
+      <c r="K26" s="8" t="n"/>
       <c r="L26" s="8" t="n"/>
       <c r="M26" s="8" t="n"/>
       <c r="N26" s="8" t="n"/>
       <c r="O26" s="8" t="n"/>
-      <c r="P26" s="9" t="n"/>
-      <c r="Q26" s="9" t="n"/>
+      <c r="P26" s="8" t="n"/>
+      <c r="Q26" s="8" t="n"/>
       <c r="R26" s="9" t="n"/>
       <c r="S26" s="9" t="n"/>
       <c r="T26" s="9" t="n"/>
       <c r="U26" s="9" t="n"/>
-      <c r="V26" s="9" t="n"/>
+      <c r="V26" s="10" t="n"/>
       <c r="W26" s="10" t="n"/>
       <c r="X26" s="10" t="n"/>
       <c r="Y26" s="10" t="n"/>
-      <c r="Z26" s="11" t="n"/>
-      <c r="AA26" s="11" t="n"/>
+      <c r="Z26" s="10" t="n"/>
+      <c r="AA26" s="10" t="n"/>
+      <c r="AB26" s="10" t="n"/>
+      <c r="AC26" s="11" t="n"/>
+      <c r="AD26" s="11" t="n"/>
+      <c r="AE26" s="11" t="n"/>
+      <c r="AF26" s="12" t="n"/>
+      <c r="AG26" s="12" t="n"/>
+      <c r="AH26" s="7" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="6" t="n"/>
@@ -1698,25 +2009,32 @@
       <c r="F27" s="7" t="n"/>
       <c r="G27" s="7" t="n"/>
       <c r="H27" s="7" t="n"/>
-      <c r="I27" s="7" t="n"/>
-      <c r="J27" s="7" t="n"/>
-      <c r="K27" s="7" t="n"/>
+      <c r="I27" s="8" t="n"/>
+      <c r="J27" s="8" t="n"/>
+      <c r="K27" s="8" t="n"/>
       <c r="L27" s="8" t="n"/>
       <c r="M27" s="8" t="n"/>
       <c r="N27" s="8" t="n"/>
       <c r="O27" s="8" t="n"/>
-      <c r="P27" s="9" t="n"/>
-      <c r="Q27" s="9" t="n"/>
+      <c r="P27" s="8" t="n"/>
+      <c r="Q27" s="8" t="n"/>
       <c r="R27" s="9" t="n"/>
       <c r="S27" s="9" t="n"/>
       <c r="T27" s="9" t="n"/>
       <c r="U27" s="9" t="n"/>
-      <c r="V27" s="9" t="n"/>
+      <c r="V27" s="10" t="n"/>
       <c r="W27" s="10" t="n"/>
       <c r="X27" s="10" t="n"/>
       <c r="Y27" s="10" t="n"/>
-      <c r="Z27" s="11" t="n"/>
-      <c r="AA27" s="11" t="n"/>
+      <c r="Z27" s="10" t="n"/>
+      <c r="AA27" s="10" t="n"/>
+      <c r="AB27" s="10" t="n"/>
+      <c r="AC27" s="11" t="n"/>
+      <c r="AD27" s="11" t="n"/>
+      <c r="AE27" s="11" t="n"/>
+      <c r="AF27" s="12" t="n"/>
+      <c r="AG27" s="12" t="n"/>
+      <c r="AH27" s="7" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="6" t="n"/>
@@ -1726,25 +2044,32 @@
       <c r="F28" s="7" t="n"/>
       <c r="G28" s="7" t="n"/>
       <c r="H28" s="7" t="n"/>
-      <c r="I28" s="7" t="n"/>
-      <c r="J28" s="7" t="n"/>
-      <c r="K28" s="7" t="n"/>
+      <c r="I28" s="8" t="n"/>
+      <c r="J28" s="8" t="n"/>
+      <c r="K28" s="8" t="n"/>
       <c r="L28" s="8" t="n"/>
       <c r="M28" s="8" t="n"/>
       <c r="N28" s="8" t="n"/>
       <c r="O28" s="8" t="n"/>
-      <c r="P28" s="9" t="n"/>
-      <c r="Q28" s="9" t="n"/>
+      <c r="P28" s="8" t="n"/>
+      <c r="Q28" s="8" t="n"/>
       <c r="R28" s="9" t="n"/>
       <c r="S28" s="9" t="n"/>
       <c r="T28" s="9" t="n"/>
       <c r="U28" s="9" t="n"/>
-      <c r="V28" s="9" t="n"/>
+      <c r="V28" s="10" t="n"/>
       <c r="W28" s="10" t="n"/>
       <c r="X28" s="10" t="n"/>
       <c r="Y28" s="10" t="n"/>
-      <c r="Z28" s="11" t="n"/>
-      <c r="AA28" s="11" t="n"/>
+      <c r="Z28" s="10" t="n"/>
+      <c r="AA28" s="10" t="n"/>
+      <c r="AB28" s="10" t="n"/>
+      <c r="AC28" s="11" t="n"/>
+      <c r="AD28" s="11" t="n"/>
+      <c r="AE28" s="11" t="n"/>
+      <c r="AF28" s="12" t="n"/>
+      <c r="AG28" s="12" t="n"/>
+      <c r="AH28" s="7" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="6" t="n"/>
@@ -1754,25 +2079,32 @@
       <c r="F29" s="7" t="n"/>
       <c r="G29" s="7" t="n"/>
       <c r="H29" s="7" t="n"/>
-      <c r="I29" s="7" t="n"/>
-      <c r="J29" s="7" t="n"/>
-      <c r="K29" s="7" t="n"/>
+      <c r="I29" s="8" t="n"/>
+      <c r="J29" s="8" t="n"/>
+      <c r="K29" s="8" t="n"/>
       <c r="L29" s="8" t="n"/>
       <c r="M29" s="8" t="n"/>
       <c r="N29" s="8" t="n"/>
       <c r="O29" s="8" t="n"/>
-      <c r="P29" s="9" t="n"/>
-      <c r="Q29" s="9" t="n"/>
+      <c r="P29" s="8" t="n"/>
+      <c r="Q29" s="8" t="n"/>
       <c r="R29" s="9" t="n"/>
       <c r="S29" s="9" t="n"/>
       <c r="T29" s="9" t="n"/>
       <c r="U29" s="9" t="n"/>
-      <c r="V29" s="9" t="n"/>
+      <c r="V29" s="10" t="n"/>
       <c r="W29" s="10" t="n"/>
       <c r="X29" s="10" t="n"/>
       <c r="Y29" s="10" t="n"/>
-      <c r="Z29" s="11" t="n"/>
-      <c r="AA29" s="11" t="n"/>
+      <c r="Z29" s="10" t="n"/>
+      <c r="AA29" s="10" t="n"/>
+      <c r="AB29" s="10" t="n"/>
+      <c r="AC29" s="11" t="n"/>
+      <c r="AD29" s="11" t="n"/>
+      <c r="AE29" s="11" t="n"/>
+      <c r="AF29" s="12" t="n"/>
+      <c r="AG29" s="12" t="n"/>
+      <c r="AH29" s="7" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="6" t="n"/>
@@ -1782,25 +2114,32 @@
       <c r="F30" s="7" t="n"/>
       <c r="G30" s="7" t="n"/>
       <c r="H30" s="7" t="n"/>
-      <c r="I30" s="7" t="n"/>
-      <c r="J30" s="7" t="n"/>
-      <c r="K30" s="7" t="n"/>
+      <c r="I30" s="8" t="n"/>
+      <c r="J30" s="8" t="n"/>
+      <c r="K30" s="8" t="n"/>
       <c r="L30" s="8" t="n"/>
       <c r="M30" s="8" t="n"/>
       <c r="N30" s="8" t="n"/>
       <c r="O30" s="8" t="n"/>
-      <c r="P30" s="9" t="n"/>
-      <c r="Q30" s="9" t="n"/>
+      <c r="P30" s="8" t="n"/>
+      <c r="Q30" s="8" t="n"/>
       <c r="R30" s="9" t="n"/>
       <c r="S30" s="9" t="n"/>
       <c r="T30" s="9" t="n"/>
       <c r="U30" s="9" t="n"/>
-      <c r="V30" s="9" t="n"/>
+      <c r="V30" s="10" t="n"/>
       <c r="W30" s="10" t="n"/>
       <c r="X30" s="10" t="n"/>
       <c r="Y30" s="10" t="n"/>
-      <c r="Z30" s="11" t="n"/>
-      <c r="AA30" s="11" t="n"/>
+      <c r="Z30" s="10" t="n"/>
+      <c r="AA30" s="10" t="n"/>
+      <c r="AB30" s="10" t="n"/>
+      <c r="AC30" s="11" t="n"/>
+      <c r="AD30" s="11" t="n"/>
+      <c r="AE30" s="11" t="n"/>
+      <c r="AF30" s="12" t="n"/>
+      <c r="AG30" s="12" t="n"/>
+      <c r="AH30" s="7" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="6" t="n"/>
@@ -1810,25 +2149,32 @@
       <c r="F31" s="7" t="n"/>
       <c r="G31" s="7" t="n"/>
       <c r="H31" s="7" t="n"/>
-      <c r="I31" s="7" t="n"/>
-      <c r="J31" s="7" t="n"/>
-      <c r="K31" s="7" t="n"/>
+      <c r="I31" s="8" t="n"/>
+      <c r="J31" s="8" t="n"/>
+      <c r="K31" s="8" t="n"/>
       <c r="L31" s="8" t="n"/>
       <c r="M31" s="8" t="n"/>
       <c r="N31" s="8" t="n"/>
       <c r="O31" s="8" t="n"/>
-      <c r="P31" s="9" t="n"/>
-      <c r="Q31" s="9" t="n"/>
+      <c r="P31" s="8" t="n"/>
+      <c r="Q31" s="8" t="n"/>
       <c r="R31" s="9" t="n"/>
       <c r="S31" s="9" t="n"/>
       <c r="T31" s="9" t="n"/>
       <c r="U31" s="9" t="n"/>
-      <c r="V31" s="9" t="n"/>
+      <c r="V31" s="10" t="n"/>
       <c r="W31" s="10" t="n"/>
       <c r="X31" s="10" t="n"/>
       <c r="Y31" s="10" t="n"/>
-      <c r="Z31" s="11" t="n"/>
-      <c r="AA31" s="11" t="n"/>
+      <c r="Z31" s="10" t="n"/>
+      <c r="AA31" s="10" t="n"/>
+      <c r="AB31" s="10" t="n"/>
+      <c r="AC31" s="11" t="n"/>
+      <c r="AD31" s="11" t="n"/>
+      <c r="AE31" s="11" t="n"/>
+      <c r="AF31" s="12" t="n"/>
+      <c r="AG31" s="12" t="n"/>
+      <c r="AH31" s="7" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="6" t="n"/>
@@ -1838,25 +2184,32 @@
       <c r="F32" s="7" t="n"/>
       <c r="G32" s="7" t="n"/>
       <c r="H32" s="7" t="n"/>
-      <c r="I32" s="7" t="n"/>
-      <c r="J32" s="7" t="n"/>
-      <c r="K32" s="7" t="n"/>
+      <c r="I32" s="8" t="n"/>
+      <c r="J32" s="8" t="n"/>
+      <c r="K32" s="8" t="n"/>
       <c r="L32" s="8" t="n"/>
       <c r="M32" s="8" t="n"/>
       <c r="N32" s="8" t="n"/>
       <c r="O32" s="8" t="n"/>
-      <c r="P32" s="9" t="n"/>
-      <c r="Q32" s="9" t="n"/>
+      <c r="P32" s="8" t="n"/>
+      <c r="Q32" s="8" t="n"/>
       <c r="R32" s="9" t="n"/>
       <c r="S32" s="9" t="n"/>
       <c r="T32" s="9" t="n"/>
       <c r="U32" s="9" t="n"/>
-      <c r="V32" s="9" t="n"/>
+      <c r="V32" s="10" t="n"/>
       <c r="W32" s="10" t="n"/>
       <c r="X32" s="10" t="n"/>
       <c r="Y32" s="10" t="n"/>
-      <c r="Z32" s="11" t="n"/>
-      <c r="AA32" s="11" t="n"/>
+      <c r="Z32" s="10" t="n"/>
+      <c r="AA32" s="10" t="n"/>
+      <c r="AB32" s="10" t="n"/>
+      <c r="AC32" s="11" t="n"/>
+      <c r="AD32" s="11" t="n"/>
+      <c r="AE32" s="11" t="n"/>
+      <c r="AF32" s="12" t="n"/>
+      <c r="AG32" s="12" t="n"/>
+      <c r="AH32" s="7" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="6" t="n"/>
@@ -1866,25 +2219,32 @@
       <c r="F33" s="7" t="n"/>
       <c r="G33" s="7" t="n"/>
       <c r="H33" s="7" t="n"/>
-      <c r="I33" s="7" t="n"/>
-      <c r="J33" s="7" t="n"/>
-      <c r="K33" s="7" t="n"/>
+      <c r="I33" s="8" t="n"/>
+      <c r="J33" s="8" t="n"/>
+      <c r="K33" s="8" t="n"/>
       <c r="L33" s="8" t="n"/>
       <c r="M33" s="8" t="n"/>
       <c r="N33" s="8" t="n"/>
       <c r="O33" s="8" t="n"/>
-      <c r="P33" s="9" t="n"/>
-      <c r="Q33" s="9" t="n"/>
+      <c r="P33" s="8" t="n"/>
+      <c r="Q33" s="8" t="n"/>
       <c r="R33" s="9" t="n"/>
       <c r="S33" s="9" t="n"/>
       <c r="T33" s="9" t="n"/>
       <c r="U33" s="9" t="n"/>
-      <c r="V33" s="9" t="n"/>
+      <c r="V33" s="10" t="n"/>
       <c r="W33" s="10" t="n"/>
       <c r="X33" s="10" t="n"/>
       <c r="Y33" s="10" t="n"/>
-      <c r="Z33" s="11" t="n"/>
-      <c r="AA33" s="11" t="n"/>
+      <c r="Z33" s="10" t="n"/>
+      <c r="AA33" s="10" t="n"/>
+      <c r="AB33" s="10" t="n"/>
+      <c r="AC33" s="11" t="n"/>
+      <c r="AD33" s="11" t="n"/>
+      <c r="AE33" s="11" t="n"/>
+      <c r="AF33" s="12" t="n"/>
+      <c r="AG33" s="12" t="n"/>
+      <c r="AH33" s="7" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="6" t="n"/>
@@ -1894,25 +2254,32 @@
       <c r="F34" s="7" t="n"/>
       <c r="G34" s="7" t="n"/>
       <c r="H34" s="7" t="n"/>
-      <c r="I34" s="7" t="n"/>
-      <c r="J34" s="7" t="n"/>
-      <c r="K34" s="7" t="n"/>
+      <c r="I34" s="8" t="n"/>
+      <c r="J34" s="8" t="n"/>
+      <c r="K34" s="8" t="n"/>
       <c r="L34" s="8" t="n"/>
       <c r="M34" s="8" t="n"/>
       <c r="N34" s="8" t="n"/>
       <c r="O34" s="8" t="n"/>
-      <c r="P34" s="9" t="n"/>
-      <c r="Q34" s="9" t="n"/>
+      <c r="P34" s="8" t="n"/>
+      <c r="Q34" s="8" t="n"/>
       <c r="R34" s="9" t="n"/>
       <c r="S34" s="9" t="n"/>
       <c r="T34" s="9" t="n"/>
       <c r="U34" s="9" t="n"/>
-      <c r="V34" s="9" t="n"/>
+      <c r="V34" s="10" t="n"/>
       <c r="W34" s="10" t="n"/>
       <c r="X34" s="10" t="n"/>
       <c r="Y34" s="10" t="n"/>
-      <c r="Z34" s="11" t="n"/>
-      <c r="AA34" s="11" t="n"/>
+      <c r="Z34" s="10" t="n"/>
+      <c r="AA34" s="10" t="n"/>
+      <c r="AB34" s="10" t="n"/>
+      <c r="AC34" s="11" t="n"/>
+      <c r="AD34" s="11" t="n"/>
+      <c r="AE34" s="11" t="n"/>
+      <c r="AF34" s="12" t="n"/>
+      <c r="AG34" s="12" t="n"/>
+      <c r="AH34" s="7" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="6" t="n"/>
@@ -1922,25 +2289,32 @@
       <c r="F35" s="7" t="n"/>
       <c r="G35" s="7" t="n"/>
       <c r="H35" s="7" t="n"/>
-      <c r="I35" s="7" t="n"/>
-      <c r="J35" s="7" t="n"/>
-      <c r="K35" s="7" t="n"/>
+      <c r="I35" s="8" t="n"/>
+      <c r="J35" s="8" t="n"/>
+      <c r="K35" s="8" t="n"/>
       <c r="L35" s="8" t="n"/>
       <c r="M35" s="8" t="n"/>
       <c r="N35" s="8" t="n"/>
       <c r="O35" s="8" t="n"/>
-      <c r="P35" s="9" t="n"/>
-      <c r="Q35" s="9" t="n"/>
+      <c r="P35" s="8" t="n"/>
+      <c r="Q35" s="8" t="n"/>
       <c r="R35" s="9" t="n"/>
       <c r="S35" s="9" t="n"/>
       <c r="T35" s="9" t="n"/>
       <c r="U35" s="9" t="n"/>
-      <c r="V35" s="9" t="n"/>
+      <c r="V35" s="10" t="n"/>
       <c r="W35" s="10" t="n"/>
       <c r="X35" s="10" t="n"/>
       <c r="Y35" s="10" t="n"/>
-      <c r="Z35" s="11" t="n"/>
-      <c r="AA35" s="11" t="n"/>
+      <c r="Z35" s="10" t="n"/>
+      <c r="AA35" s="10" t="n"/>
+      <c r="AB35" s="10" t="n"/>
+      <c r="AC35" s="11" t="n"/>
+      <c r="AD35" s="11" t="n"/>
+      <c r="AE35" s="11" t="n"/>
+      <c r="AF35" s="12" t="n"/>
+      <c r="AG35" s="12" t="n"/>
+      <c r="AH35" s="7" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="6" t="n"/>
@@ -1950,25 +2324,32 @@
       <c r="F36" s="7" t="n"/>
       <c r="G36" s="7" t="n"/>
       <c r="H36" s="7" t="n"/>
-      <c r="I36" s="7" t="n"/>
-      <c r="J36" s="7" t="n"/>
-      <c r="K36" s="7" t="n"/>
+      <c r="I36" s="8" t="n"/>
+      <c r="J36" s="8" t="n"/>
+      <c r="K36" s="8" t="n"/>
       <c r="L36" s="8" t="n"/>
       <c r="M36" s="8" t="n"/>
       <c r="N36" s="8" t="n"/>
       <c r="O36" s="8" t="n"/>
-      <c r="P36" s="9" t="n"/>
-      <c r="Q36" s="9" t="n"/>
+      <c r="P36" s="8" t="n"/>
+      <c r="Q36" s="8" t="n"/>
       <c r="R36" s="9" t="n"/>
       <c r="S36" s="9" t="n"/>
       <c r="T36" s="9" t="n"/>
       <c r="U36" s="9" t="n"/>
-      <c r="V36" s="9" t="n"/>
+      <c r="V36" s="10" t="n"/>
       <c r="W36" s="10" t="n"/>
       <c r="X36" s="10" t="n"/>
       <c r="Y36" s="10" t="n"/>
-      <c r="Z36" s="11" t="n"/>
-      <c r="AA36" s="11" t="n"/>
+      <c r="Z36" s="10" t="n"/>
+      <c r="AA36" s="10" t="n"/>
+      <c r="AB36" s="10" t="n"/>
+      <c r="AC36" s="11" t="n"/>
+      <c r="AD36" s="11" t="n"/>
+      <c r="AE36" s="11" t="n"/>
+      <c r="AF36" s="12" t="n"/>
+      <c r="AG36" s="12" t="n"/>
+      <c r="AH36" s="7" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="6" t="n"/>
@@ -1978,25 +2359,32 @@
       <c r="F37" s="7" t="n"/>
       <c r="G37" s="7" t="n"/>
       <c r="H37" s="7" t="n"/>
-      <c r="I37" s="7" t="n"/>
-      <c r="J37" s="7" t="n"/>
-      <c r="K37" s="7" t="n"/>
+      <c r="I37" s="8" t="n"/>
+      <c r="J37" s="8" t="n"/>
+      <c r="K37" s="8" t="n"/>
       <c r="L37" s="8" t="n"/>
       <c r="M37" s="8" t="n"/>
       <c r="N37" s="8" t="n"/>
       <c r="O37" s="8" t="n"/>
-      <c r="P37" s="9" t="n"/>
-      <c r="Q37" s="9" t="n"/>
+      <c r="P37" s="8" t="n"/>
+      <c r="Q37" s="8" t="n"/>
       <c r="R37" s="9" t="n"/>
       <c r="S37" s="9" t="n"/>
       <c r="T37" s="9" t="n"/>
       <c r="U37" s="9" t="n"/>
-      <c r="V37" s="9" t="n"/>
+      <c r="V37" s="10" t="n"/>
       <c r="W37" s="10" t="n"/>
       <c r="X37" s="10" t="n"/>
       <c r="Y37" s="10" t="n"/>
-      <c r="Z37" s="11" t="n"/>
-      <c r="AA37" s="11" t="n"/>
+      <c r="Z37" s="10" t="n"/>
+      <c r="AA37" s="10" t="n"/>
+      <c r="AB37" s="10" t="n"/>
+      <c r="AC37" s="11" t="n"/>
+      <c r="AD37" s="11" t="n"/>
+      <c r="AE37" s="11" t="n"/>
+      <c r="AF37" s="12" t="n"/>
+      <c r="AG37" s="12" t="n"/>
+      <c r="AH37" s="7" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="6" t="n"/>
@@ -2006,25 +2394,32 @@
       <c r="F38" s="7" t="n"/>
       <c r="G38" s="7" t="n"/>
       <c r="H38" s="7" t="n"/>
-      <c r="I38" s="7" t="n"/>
-      <c r="J38" s="7" t="n"/>
-      <c r="K38" s="7" t="n"/>
+      <c r="I38" s="8" t="n"/>
+      <c r="J38" s="8" t="n"/>
+      <c r="K38" s="8" t="n"/>
       <c r="L38" s="8" t="n"/>
       <c r="M38" s="8" t="n"/>
       <c r="N38" s="8" t="n"/>
       <c r="O38" s="8" t="n"/>
-      <c r="P38" s="9" t="n"/>
-      <c r="Q38" s="9" t="n"/>
+      <c r="P38" s="8" t="n"/>
+      <c r="Q38" s="8" t="n"/>
       <c r="R38" s="9" t="n"/>
       <c r="S38" s="9" t="n"/>
       <c r="T38" s="9" t="n"/>
       <c r="U38" s="9" t="n"/>
-      <c r="V38" s="9" t="n"/>
+      <c r="V38" s="10" t="n"/>
       <c r="W38" s="10" t="n"/>
       <c r="X38" s="10" t="n"/>
       <c r="Y38" s="10" t="n"/>
-      <c r="Z38" s="11" t="n"/>
-      <c r="AA38" s="11" t="n"/>
+      <c r="Z38" s="10" t="n"/>
+      <c r="AA38" s="10" t="n"/>
+      <c r="AB38" s="10" t="n"/>
+      <c r="AC38" s="11" t="n"/>
+      <c r="AD38" s="11" t="n"/>
+      <c r="AE38" s="11" t="n"/>
+      <c r="AF38" s="12" t="n"/>
+      <c r="AG38" s="12" t="n"/>
+      <c r="AH38" s="7" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="6" t="n"/>
@@ -2034,25 +2429,32 @@
       <c r="F39" s="7" t="n"/>
       <c r="G39" s="7" t="n"/>
       <c r="H39" s="7" t="n"/>
-      <c r="I39" s="7" t="n"/>
-      <c r="J39" s="7" t="n"/>
-      <c r="K39" s="7" t="n"/>
+      <c r="I39" s="8" t="n"/>
+      <c r="J39" s="8" t="n"/>
+      <c r="K39" s="8" t="n"/>
       <c r="L39" s="8" t="n"/>
       <c r="M39" s="8" t="n"/>
       <c r="N39" s="8" t="n"/>
       <c r="O39" s="8" t="n"/>
-      <c r="P39" s="9" t="n"/>
-      <c r="Q39" s="9" t="n"/>
+      <c r="P39" s="8" t="n"/>
+      <c r="Q39" s="8" t="n"/>
       <c r="R39" s="9" t="n"/>
       <c r="S39" s="9" t="n"/>
       <c r="T39" s="9" t="n"/>
       <c r="U39" s="9" t="n"/>
-      <c r="V39" s="9" t="n"/>
+      <c r="V39" s="10" t="n"/>
       <c r="W39" s="10" t="n"/>
       <c r="X39" s="10" t="n"/>
       <c r="Y39" s="10" t="n"/>
-      <c r="Z39" s="11" t="n"/>
-      <c r="AA39" s="11" t="n"/>
+      <c r="Z39" s="10" t="n"/>
+      <c r="AA39" s="10" t="n"/>
+      <c r="AB39" s="10" t="n"/>
+      <c r="AC39" s="11" t="n"/>
+      <c r="AD39" s="11" t="n"/>
+      <c r="AE39" s="11" t="n"/>
+      <c r="AF39" s="12" t="n"/>
+      <c r="AG39" s="12" t="n"/>
+      <c r="AH39" s="7" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="6" t="n"/>
@@ -2062,25 +2464,32 @@
       <c r="F40" s="7" t="n"/>
       <c r="G40" s="7" t="n"/>
       <c r="H40" s="7" t="n"/>
-      <c r="I40" s="7" t="n"/>
-      <c r="J40" s="7" t="n"/>
-      <c r="K40" s="7" t="n"/>
+      <c r="I40" s="8" t="n"/>
+      <c r="J40" s="8" t="n"/>
+      <c r="K40" s="8" t="n"/>
       <c r="L40" s="8" t="n"/>
       <c r="M40" s="8" t="n"/>
       <c r="N40" s="8" t="n"/>
       <c r="O40" s="8" t="n"/>
-      <c r="P40" s="9" t="n"/>
-      <c r="Q40" s="9" t="n"/>
+      <c r="P40" s="8" t="n"/>
+      <c r="Q40" s="8" t="n"/>
       <c r="R40" s="9" t="n"/>
       <c r="S40" s="9" t="n"/>
       <c r="T40" s="9" t="n"/>
       <c r="U40" s="9" t="n"/>
-      <c r="V40" s="9" t="n"/>
+      <c r="V40" s="10" t="n"/>
       <c r="W40" s="10" t="n"/>
       <c r="X40" s="10" t="n"/>
       <c r="Y40" s="10" t="n"/>
-      <c r="Z40" s="11" t="n"/>
-      <c r="AA40" s="11" t="n"/>
+      <c r="Z40" s="10" t="n"/>
+      <c r="AA40" s="10" t="n"/>
+      <c r="AB40" s="10" t="n"/>
+      <c r="AC40" s="11" t="n"/>
+      <c r="AD40" s="11" t="n"/>
+      <c r="AE40" s="11" t="n"/>
+      <c r="AF40" s="12" t="n"/>
+      <c r="AG40" s="12" t="n"/>
+      <c r="AH40" s="7" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="6" t="n"/>
@@ -2090,25 +2499,32 @@
       <c r="F41" s="7" t="n"/>
       <c r="G41" s="7" t="n"/>
       <c r="H41" s="7" t="n"/>
-      <c r="I41" s="7" t="n"/>
-      <c r="J41" s="7" t="n"/>
-      <c r="K41" s="7" t="n"/>
+      <c r="I41" s="8" t="n"/>
+      <c r="J41" s="8" t="n"/>
+      <c r="K41" s="8" t="n"/>
       <c r="L41" s="8" t="n"/>
       <c r="M41" s="8" t="n"/>
       <c r="N41" s="8" t="n"/>
       <c r="O41" s="8" t="n"/>
-      <c r="P41" s="9" t="n"/>
-      <c r="Q41" s="9" t="n"/>
+      <c r="P41" s="8" t="n"/>
+      <c r="Q41" s="8" t="n"/>
       <c r="R41" s="9" t="n"/>
       <c r="S41" s="9" t="n"/>
       <c r="T41" s="9" t="n"/>
       <c r="U41" s="9" t="n"/>
-      <c r="V41" s="9" t="n"/>
+      <c r="V41" s="10" t="n"/>
       <c r="W41" s="10" t="n"/>
       <c r="X41" s="10" t="n"/>
       <c r="Y41" s="10" t="n"/>
-      <c r="Z41" s="11" t="n"/>
-      <c r="AA41" s="11" t="n"/>
+      <c r="Z41" s="10" t="n"/>
+      <c r="AA41" s="10" t="n"/>
+      <c r="AB41" s="10" t="n"/>
+      <c r="AC41" s="11" t="n"/>
+      <c r="AD41" s="11" t="n"/>
+      <c r="AE41" s="11" t="n"/>
+      <c r="AF41" s="12" t="n"/>
+      <c r="AG41" s="12" t="n"/>
+      <c r="AH41" s="7" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="6" t="n"/>
@@ -2118,25 +2534,32 @@
       <c r="F42" s="7" t="n"/>
       <c r="G42" s="7" t="n"/>
       <c r="H42" s="7" t="n"/>
-      <c r="I42" s="7" t="n"/>
-      <c r="J42" s="7" t="n"/>
-      <c r="K42" s="7" t="n"/>
+      <c r="I42" s="8" t="n"/>
+      <c r="J42" s="8" t="n"/>
+      <c r="K42" s="8" t="n"/>
       <c r="L42" s="8" t="n"/>
       <c r="M42" s="8" t="n"/>
       <c r="N42" s="8" t="n"/>
       <c r="O42" s="8" t="n"/>
-      <c r="P42" s="9" t="n"/>
-      <c r="Q42" s="9" t="n"/>
+      <c r="P42" s="8" t="n"/>
+      <c r="Q42" s="8" t="n"/>
       <c r="R42" s="9" t="n"/>
       <c r="S42" s="9" t="n"/>
       <c r="T42" s="9" t="n"/>
       <c r="U42" s="9" t="n"/>
-      <c r="V42" s="9" t="n"/>
+      <c r="V42" s="10" t="n"/>
       <c r="W42" s="10" t="n"/>
       <c r="X42" s="10" t="n"/>
       <c r="Y42" s="10" t="n"/>
-      <c r="Z42" s="11" t="n"/>
-      <c r="AA42" s="11" t="n"/>
+      <c r="Z42" s="10" t="n"/>
+      <c r="AA42" s="10" t="n"/>
+      <c r="AB42" s="10" t="n"/>
+      <c r="AC42" s="11" t="n"/>
+      <c r="AD42" s="11" t="n"/>
+      <c r="AE42" s="11" t="n"/>
+      <c r="AF42" s="12" t="n"/>
+      <c r="AG42" s="12" t="n"/>
+      <c r="AH42" s="7" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="6" t="n"/>
@@ -2146,25 +2569,32 @@
       <c r="F43" s="7" t="n"/>
       <c r="G43" s="7" t="n"/>
       <c r="H43" s="7" t="n"/>
-      <c r="I43" s="7" t="n"/>
-      <c r="J43" s="7" t="n"/>
-      <c r="K43" s="7" t="n"/>
+      <c r="I43" s="8" t="n"/>
+      <c r="J43" s="8" t="n"/>
+      <c r="K43" s="8" t="n"/>
       <c r="L43" s="8" t="n"/>
       <c r="M43" s="8" t="n"/>
       <c r="N43" s="8" t="n"/>
       <c r="O43" s="8" t="n"/>
-      <c r="P43" s="9" t="n"/>
-      <c r="Q43" s="9" t="n"/>
+      <c r="P43" s="8" t="n"/>
+      <c r="Q43" s="8" t="n"/>
       <c r="R43" s="9" t="n"/>
       <c r="S43" s="9" t="n"/>
       <c r="T43" s="9" t="n"/>
       <c r="U43" s="9" t="n"/>
-      <c r="V43" s="9" t="n"/>
+      <c r="V43" s="10" t="n"/>
       <c r="W43" s="10" t="n"/>
       <c r="X43" s="10" t="n"/>
       <c r="Y43" s="10" t="n"/>
-      <c r="Z43" s="11" t="n"/>
-      <c r="AA43" s="11" t="n"/>
+      <c r="Z43" s="10" t="n"/>
+      <c r="AA43" s="10" t="n"/>
+      <c r="AB43" s="10" t="n"/>
+      <c r="AC43" s="11" t="n"/>
+      <c r="AD43" s="11" t="n"/>
+      <c r="AE43" s="11" t="n"/>
+      <c r="AF43" s="12" t="n"/>
+      <c r="AG43" s="12" t="n"/>
+      <c r="AH43" s="7" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="6" t="n"/>
@@ -2174,25 +2604,32 @@
       <c r="F44" s="7" t="n"/>
       <c r="G44" s="7" t="n"/>
       <c r="H44" s="7" t="n"/>
-      <c r="I44" s="7" t="n"/>
-      <c r="J44" s="7" t="n"/>
-      <c r="K44" s="7" t="n"/>
+      <c r="I44" s="8" t="n"/>
+      <c r="J44" s="8" t="n"/>
+      <c r="K44" s="8" t="n"/>
       <c r="L44" s="8" t="n"/>
       <c r="M44" s="8" t="n"/>
       <c r="N44" s="8" t="n"/>
       <c r="O44" s="8" t="n"/>
-      <c r="P44" s="9" t="n"/>
-      <c r="Q44" s="9" t="n"/>
+      <c r="P44" s="8" t="n"/>
+      <c r="Q44" s="8" t="n"/>
       <c r="R44" s="9" t="n"/>
       <c r="S44" s="9" t="n"/>
       <c r="T44" s="9" t="n"/>
       <c r="U44" s="9" t="n"/>
-      <c r="V44" s="9" t="n"/>
+      <c r="V44" s="10" t="n"/>
       <c r="W44" s="10" t="n"/>
       <c r="X44" s="10" t="n"/>
       <c r="Y44" s="10" t="n"/>
-      <c r="Z44" s="11" t="n"/>
-      <c r="AA44" s="11" t="n"/>
+      <c r="Z44" s="10" t="n"/>
+      <c r="AA44" s="10" t="n"/>
+      <c r="AB44" s="10" t="n"/>
+      <c r="AC44" s="11" t="n"/>
+      <c r="AD44" s="11" t="n"/>
+      <c r="AE44" s="11" t="n"/>
+      <c r="AF44" s="12" t="n"/>
+      <c r="AG44" s="12" t="n"/>
+      <c r="AH44" s="7" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="6" t="n"/>
@@ -2202,25 +2639,32 @@
       <c r="F45" s="7" t="n"/>
       <c r="G45" s="7" t="n"/>
       <c r="H45" s="7" t="n"/>
-      <c r="I45" s="7" t="n"/>
-      <c r="J45" s="7" t="n"/>
-      <c r="K45" s="7" t="n"/>
+      <c r="I45" s="8" t="n"/>
+      <c r="J45" s="8" t="n"/>
+      <c r="K45" s="8" t="n"/>
       <c r="L45" s="8" t="n"/>
       <c r="M45" s="8" t="n"/>
       <c r="N45" s="8" t="n"/>
       <c r="O45" s="8" t="n"/>
-      <c r="P45" s="9" t="n"/>
-      <c r="Q45" s="9" t="n"/>
+      <c r="P45" s="8" t="n"/>
+      <c r="Q45" s="8" t="n"/>
       <c r="R45" s="9" t="n"/>
       <c r="S45" s="9" t="n"/>
       <c r="T45" s="9" t="n"/>
       <c r="U45" s="9" t="n"/>
-      <c r="V45" s="9" t="n"/>
+      <c r="V45" s="10" t="n"/>
       <c r="W45" s="10" t="n"/>
       <c r="X45" s="10" t="n"/>
       <c r="Y45" s="10" t="n"/>
-      <c r="Z45" s="11" t="n"/>
-      <c r="AA45" s="11" t="n"/>
+      <c r="Z45" s="10" t="n"/>
+      <c r="AA45" s="10" t="n"/>
+      <c r="AB45" s="10" t="n"/>
+      <c r="AC45" s="11" t="n"/>
+      <c r="AD45" s="11" t="n"/>
+      <c r="AE45" s="11" t="n"/>
+      <c r="AF45" s="12" t="n"/>
+      <c r="AG45" s="12" t="n"/>
+      <c r="AH45" s="7" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="6" t="n"/>
@@ -2230,25 +2674,32 @@
       <c r="F46" s="7" t="n"/>
       <c r="G46" s="7" t="n"/>
       <c r="H46" s="7" t="n"/>
-      <c r="I46" s="7" t="n"/>
-      <c r="J46" s="7" t="n"/>
-      <c r="K46" s="7" t="n"/>
+      <c r="I46" s="8" t="n"/>
+      <c r="J46" s="8" t="n"/>
+      <c r="K46" s="8" t="n"/>
       <c r="L46" s="8" t="n"/>
       <c r="M46" s="8" t="n"/>
       <c r="N46" s="8" t="n"/>
       <c r="O46" s="8" t="n"/>
-      <c r="P46" s="9" t="n"/>
-      <c r="Q46" s="9" t="n"/>
+      <c r="P46" s="8" t="n"/>
+      <c r="Q46" s="8" t="n"/>
       <c r="R46" s="9" t="n"/>
       <c r="S46" s="9" t="n"/>
       <c r="T46" s="9" t="n"/>
       <c r="U46" s="9" t="n"/>
-      <c r="V46" s="9" t="n"/>
+      <c r="V46" s="10" t="n"/>
       <c r="W46" s="10" t="n"/>
       <c r="X46" s="10" t="n"/>
       <c r="Y46" s="10" t="n"/>
-      <c r="Z46" s="11" t="n"/>
-      <c r="AA46" s="11" t="n"/>
+      <c r="Z46" s="10" t="n"/>
+      <c r="AA46" s="10" t="n"/>
+      <c r="AB46" s="10" t="n"/>
+      <c r="AC46" s="11" t="n"/>
+      <c r="AD46" s="11" t="n"/>
+      <c r="AE46" s="11" t="n"/>
+      <c r="AF46" s="12" t="n"/>
+      <c r="AG46" s="12" t="n"/>
+      <c r="AH46" s="7" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="6" t="n"/>
@@ -2258,25 +2709,32 @@
       <c r="F47" s="7" t="n"/>
       <c r="G47" s="7" t="n"/>
       <c r="H47" s="7" t="n"/>
-      <c r="I47" s="7" t="n"/>
-      <c r="J47" s="7" t="n"/>
-      <c r="K47" s="7" t="n"/>
+      <c r="I47" s="8" t="n"/>
+      <c r="J47" s="8" t="n"/>
+      <c r="K47" s="8" t="n"/>
       <c r="L47" s="8" t="n"/>
       <c r="M47" s="8" t="n"/>
       <c r="N47" s="8" t="n"/>
       <c r="O47" s="8" t="n"/>
-      <c r="P47" s="9" t="n"/>
-      <c r="Q47" s="9" t="n"/>
+      <c r="P47" s="8" t="n"/>
+      <c r="Q47" s="8" t="n"/>
       <c r="R47" s="9" t="n"/>
       <c r="S47" s="9" t="n"/>
       <c r="T47" s="9" t="n"/>
       <c r="U47" s="9" t="n"/>
-      <c r="V47" s="9" t="n"/>
+      <c r="V47" s="10" t="n"/>
       <c r="W47" s="10" t="n"/>
       <c r="X47" s="10" t="n"/>
       <c r="Y47" s="10" t="n"/>
-      <c r="Z47" s="11" t="n"/>
-      <c r="AA47" s="11" t="n"/>
+      <c r="Z47" s="10" t="n"/>
+      <c r="AA47" s="10" t="n"/>
+      <c r="AB47" s="10" t="n"/>
+      <c r="AC47" s="11" t="n"/>
+      <c r="AD47" s="11" t="n"/>
+      <c r="AE47" s="11" t="n"/>
+      <c r="AF47" s="12" t="n"/>
+      <c r="AG47" s="12" t="n"/>
+      <c r="AH47" s="7" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="6" t="n"/>
@@ -2286,25 +2744,32 @@
       <c r="F48" s="7" t="n"/>
       <c r="G48" s="7" t="n"/>
       <c r="H48" s="7" t="n"/>
-      <c r="I48" s="7" t="n"/>
-      <c r="J48" s="7" t="n"/>
-      <c r="K48" s="7" t="n"/>
+      <c r="I48" s="8" t="n"/>
+      <c r="J48" s="8" t="n"/>
+      <c r="K48" s="8" t="n"/>
       <c r="L48" s="8" t="n"/>
       <c r="M48" s="8" t="n"/>
       <c r="N48" s="8" t="n"/>
       <c r="O48" s="8" t="n"/>
-      <c r="P48" s="9" t="n"/>
-      <c r="Q48" s="9" t="n"/>
+      <c r="P48" s="8" t="n"/>
+      <c r="Q48" s="8" t="n"/>
       <c r="R48" s="9" t="n"/>
       <c r="S48" s="9" t="n"/>
       <c r="T48" s="9" t="n"/>
       <c r="U48" s="9" t="n"/>
-      <c r="V48" s="9" t="n"/>
+      <c r="V48" s="10" t="n"/>
       <c r="W48" s="10" t="n"/>
       <c r="X48" s="10" t="n"/>
       <c r="Y48" s="10" t="n"/>
-      <c r="Z48" s="11" t="n"/>
-      <c r="AA48" s="11" t="n"/>
+      <c r="Z48" s="10" t="n"/>
+      <c r="AA48" s="10" t="n"/>
+      <c r="AB48" s="10" t="n"/>
+      <c r="AC48" s="11" t="n"/>
+      <c r="AD48" s="11" t="n"/>
+      <c r="AE48" s="11" t="n"/>
+      <c r="AF48" s="12" t="n"/>
+      <c r="AG48" s="12" t="n"/>
+      <c r="AH48" s="7" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="6" t="n"/>
@@ -2314,25 +2779,32 @@
       <c r="F49" s="7" t="n"/>
       <c r="G49" s="7" t="n"/>
       <c r="H49" s="7" t="n"/>
-      <c r="I49" s="7" t="n"/>
-      <c r="J49" s="7" t="n"/>
-      <c r="K49" s="7" t="n"/>
+      <c r="I49" s="8" t="n"/>
+      <c r="J49" s="8" t="n"/>
+      <c r="K49" s="8" t="n"/>
       <c r="L49" s="8" t="n"/>
       <c r="M49" s="8" t="n"/>
       <c r="N49" s="8" t="n"/>
       <c r="O49" s="8" t="n"/>
-      <c r="P49" s="9" t="n"/>
-      <c r="Q49" s="9" t="n"/>
+      <c r="P49" s="8" t="n"/>
+      <c r="Q49" s="8" t="n"/>
       <c r="R49" s="9" t="n"/>
       <c r="S49" s="9" t="n"/>
       <c r="T49" s="9" t="n"/>
       <c r="U49" s="9" t="n"/>
-      <c r="V49" s="9" t="n"/>
+      <c r="V49" s="10" t="n"/>
       <c r="W49" s="10" t="n"/>
       <c r="X49" s="10" t="n"/>
       <c r="Y49" s="10" t="n"/>
-      <c r="Z49" s="11" t="n"/>
-      <c r="AA49" s="11" t="n"/>
+      <c r="Z49" s="10" t="n"/>
+      <c r="AA49" s="10" t="n"/>
+      <c r="AB49" s="10" t="n"/>
+      <c r="AC49" s="11" t="n"/>
+      <c r="AD49" s="11" t="n"/>
+      <c r="AE49" s="11" t="n"/>
+      <c r="AF49" s="12" t="n"/>
+      <c r="AG49" s="12" t="n"/>
+      <c r="AH49" s="7" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="6" t="n"/>
@@ -2342,25 +2814,32 @@
       <c r="F50" s="7" t="n"/>
       <c r="G50" s="7" t="n"/>
       <c r="H50" s="7" t="n"/>
-      <c r="I50" s="7" t="n"/>
-      <c r="J50" s="7" t="n"/>
-      <c r="K50" s="7" t="n"/>
+      <c r="I50" s="8" t="n"/>
+      <c r="J50" s="8" t="n"/>
+      <c r="K50" s="8" t="n"/>
       <c r="L50" s="8" t="n"/>
       <c r="M50" s="8" t="n"/>
       <c r="N50" s="8" t="n"/>
       <c r="O50" s="8" t="n"/>
-      <c r="P50" s="9" t="n"/>
-      <c r="Q50" s="9" t="n"/>
+      <c r="P50" s="8" t="n"/>
+      <c r="Q50" s="8" t="n"/>
       <c r="R50" s="9" t="n"/>
       <c r="S50" s="9" t="n"/>
       <c r="T50" s="9" t="n"/>
       <c r="U50" s="9" t="n"/>
-      <c r="V50" s="9" t="n"/>
+      <c r="V50" s="10" t="n"/>
       <c r="W50" s="10" t="n"/>
       <c r="X50" s="10" t="n"/>
       <c r="Y50" s="10" t="n"/>
-      <c r="Z50" s="11" t="n"/>
-      <c r="AA50" s="11" t="n"/>
+      <c r="Z50" s="10" t="n"/>
+      <c r="AA50" s="10" t="n"/>
+      <c r="AB50" s="10" t="n"/>
+      <c r="AC50" s="11" t="n"/>
+      <c r="AD50" s="11" t="n"/>
+      <c r="AE50" s="11" t="n"/>
+      <c r="AF50" s="12" t="n"/>
+      <c r="AG50" s="12" t="n"/>
+      <c r="AH50" s="7" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="6" t="n"/>
@@ -2370,25 +2849,32 @@
       <c r="F51" s="7" t="n"/>
       <c r="G51" s="7" t="n"/>
       <c r="H51" s="7" t="n"/>
-      <c r="I51" s="7" t="n"/>
-      <c r="J51" s="7" t="n"/>
-      <c r="K51" s="7" t="n"/>
+      <c r="I51" s="8" t="n"/>
+      <c r="J51" s="8" t="n"/>
+      <c r="K51" s="8" t="n"/>
       <c r="L51" s="8" t="n"/>
       <c r="M51" s="8" t="n"/>
       <c r="N51" s="8" t="n"/>
       <c r="O51" s="8" t="n"/>
-      <c r="P51" s="9" t="n"/>
-      <c r="Q51" s="9" t="n"/>
+      <c r="P51" s="8" t="n"/>
+      <c r="Q51" s="8" t="n"/>
       <c r="R51" s="9" t="n"/>
       <c r="S51" s="9" t="n"/>
       <c r="T51" s="9" t="n"/>
       <c r="U51" s="9" t="n"/>
-      <c r="V51" s="9" t="n"/>
+      <c r="V51" s="10" t="n"/>
       <c r="W51" s="10" t="n"/>
       <c r="X51" s="10" t="n"/>
       <c r="Y51" s="10" t="n"/>
-      <c r="Z51" s="11" t="n"/>
-      <c r="AA51" s="11" t="n"/>
+      <c r="Z51" s="10" t="n"/>
+      <c r="AA51" s="10" t="n"/>
+      <c r="AB51" s="10" t="n"/>
+      <c r="AC51" s="11" t="n"/>
+      <c r="AD51" s="11" t="n"/>
+      <c r="AE51" s="11" t="n"/>
+      <c r="AF51" s="12" t="n"/>
+      <c r="AG51" s="12" t="n"/>
+      <c r="AH51" s="7" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="6" t="n"/>
@@ -2398,25 +2884,32 @@
       <c r="F52" s="7" t="n"/>
       <c r="G52" s="7" t="n"/>
       <c r="H52" s="7" t="n"/>
-      <c r="I52" s="7" t="n"/>
-      <c r="J52" s="7" t="n"/>
-      <c r="K52" s="7" t="n"/>
+      <c r="I52" s="8" t="n"/>
+      <c r="J52" s="8" t="n"/>
+      <c r="K52" s="8" t="n"/>
       <c r="L52" s="8" t="n"/>
       <c r="M52" s="8" t="n"/>
       <c r="N52" s="8" t="n"/>
       <c r="O52" s="8" t="n"/>
-      <c r="P52" s="9" t="n"/>
-      <c r="Q52" s="9" t="n"/>
+      <c r="P52" s="8" t="n"/>
+      <c r="Q52" s="8" t="n"/>
       <c r="R52" s="9" t="n"/>
       <c r="S52" s="9" t="n"/>
       <c r="T52" s="9" t="n"/>
       <c r="U52" s="9" t="n"/>
-      <c r="V52" s="9" t="n"/>
+      <c r="V52" s="10" t="n"/>
       <c r="W52" s="10" t="n"/>
       <c r="X52" s="10" t="n"/>
       <c r="Y52" s="10" t="n"/>
-      <c r="Z52" s="11" t="n"/>
-      <c r="AA52" s="11" t="n"/>
+      <c r="Z52" s="10" t="n"/>
+      <c r="AA52" s="10" t="n"/>
+      <c r="AB52" s="10" t="n"/>
+      <c r="AC52" s="11" t="n"/>
+      <c r="AD52" s="11" t="n"/>
+      <c r="AE52" s="11" t="n"/>
+      <c r="AF52" s="12" t="n"/>
+      <c r="AG52" s="12" t="n"/>
+      <c r="AH52" s="7" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="6" t="n"/>
@@ -2426,25 +2919,32 @@
       <c r="F53" s="7" t="n"/>
       <c r="G53" s="7" t="n"/>
       <c r="H53" s="7" t="n"/>
-      <c r="I53" s="7" t="n"/>
-      <c r="J53" s="7" t="n"/>
-      <c r="K53" s="7" t="n"/>
+      <c r="I53" s="8" t="n"/>
+      <c r="J53" s="8" t="n"/>
+      <c r="K53" s="8" t="n"/>
       <c r="L53" s="8" t="n"/>
       <c r="M53" s="8" t="n"/>
       <c r="N53" s="8" t="n"/>
       <c r="O53" s="8" t="n"/>
-      <c r="P53" s="9" t="n"/>
-      <c r="Q53" s="9" t="n"/>
+      <c r="P53" s="8" t="n"/>
+      <c r="Q53" s="8" t="n"/>
       <c r="R53" s="9" t="n"/>
       <c r="S53" s="9" t="n"/>
       <c r="T53" s="9" t="n"/>
       <c r="U53" s="9" t="n"/>
-      <c r="V53" s="9" t="n"/>
+      <c r="V53" s="10" t="n"/>
       <c r="W53" s="10" t="n"/>
       <c r="X53" s="10" t="n"/>
       <c r="Y53" s="10" t="n"/>
-      <c r="Z53" s="11" t="n"/>
-      <c r="AA53" s="11" t="n"/>
+      <c r="Z53" s="10" t="n"/>
+      <c r="AA53" s="10" t="n"/>
+      <c r="AB53" s="10" t="n"/>
+      <c r="AC53" s="11" t="n"/>
+      <c r="AD53" s="11" t="n"/>
+      <c r="AE53" s="11" t="n"/>
+      <c r="AF53" s="12" t="n"/>
+      <c r="AG53" s="12" t="n"/>
+      <c r="AH53" s="7" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="6" t="n"/>
@@ -2454,25 +2954,32 @@
       <c r="F54" s="7" t="n"/>
       <c r="G54" s="7" t="n"/>
       <c r="H54" s="7" t="n"/>
-      <c r="I54" s="7" t="n"/>
-      <c r="J54" s="7" t="n"/>
-      <c r="K54" s="7" t="n"/>
+      <c r="I54" s="8" t="n"/>
+      <c r="J54" s="8" t="n"/>
+      <c r="K54" s="8" t="n"/>
       <c r="L54" s="8" t="n"/>
       <c r="M54" s="8" t="n"/>
       <c r="N54" s="8" t="n"/>
       <c r="O54" s="8" t="n"/>
-      <c r="P54" s="9" t="n"/>
-      <c r="Q54" s="9" t="n"/>
+      <c r="P54" s="8" t="n"/>
+      <c r="Q54" s="8" t="n"/>
       <c r="R54" s="9" t="n"/>
       <c r="S54" s="9" t="n"/>
       <c r="T54" s="9" t="n"/>
       <c r="U54" s="9" t="n"/>
-      <c r="V54" s="9" t="n"/>
+      <c r="V54" s="10" t="n"/>
       <c r="W54" s="10" t="n"/>
       <c r="X54" s="10" t="n"/>
       <c r="Y54" s="10" t="n"/>
-      <c r="Z54" s="11" t="n"/>
-      <c r="AA54" s="11" t="n"/>
+      <c r="Z54" s="10" t="n"/>
+      <c r="AA54" s="10" t="n"/>
+      <c r="AB54" s="10" t="n"/>
+      <c r="AC54" s="11" t="n"/>
+      <c r="AD54" s="11" t="n"/>
+      <c r="AE54" s="11" t="n"/>
+      <c r="AF54" s="12" t="n"/>
+      <c r="AG54" s="12" t="n"/>
+      <c r="AH54" s="7" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="6" t="n"/>
@@ -2482,25 +2989,32 @@
       <c r="F55" s="7" t="n"/>
       <c r="G55" s="7" t="n"/>
       <c r="H55" s="7" t="n"/>
-      <c r="I55" s="7" t="n"/>
-      <c r="J55" s="7" t="n"/>
-      <c r="K55" s="7" t="n"/>
+      <c r="I55" s="8" t="n"/>
+      <c r="J55" s="8" t="n"/>
+      <c r="K55" s="8" t="n"/>
       <c r="L55" s="8" t="n"/>
       <c r="M55" s="8" t="n"/>
       <c r="N55" s="8" t="n"/>
       <c r="O55" s="8" t="n"/>
-      <c r="P55" s="9" t="n"/>
-      <c r="Q55" s="9" t="n"/>
+      <c r="P55" s="8" t="n"/>
+      <c r="Q55" s="8" t="n"/>
       <c r="R55" s="9" t="n"/>
       <c r="S55" s="9" t="n"/>
       <c r="T55" s="9" t="n"/>
       <c r="U55" s="9" t="n"/>
-      <c r="V55" s="9" t="n"/>
+      <c r="V55" s="10" t="n"/>
       <c r="W55" s="10" t="n"/>
       <c r="X55" s="10" t="n"/>
       <c r="Y55" s="10" t="n"/>
-      <c r="Z55" s="11" t="n"/>
-      <c r="AA55" s="11" t="n"/>
+      <c r="Z55" s="10" t="n"/>
+      <c r="AA55" s="10" t="n"/>
+      <c r="AB55" s="10" t="n"/>
+      <c r="AC55" s="11" t="n"/>
+      <c r="AD55" s="11" t="n"/>
+      <c r="AE55" s="11" t="n"/>
+      <c r="AF55" s="12" t="n"/>
+      <c r="AG55" s="12" t="n"/>
+      <c r="AH55" s="7" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="6" t="n"/>
@@ -2510,25 +3024,32 @@
       <c r="F56" s="7" t="n"/>
       <c r="G56" s="7" t="n"/>
       <c r="H56" s="7" t="n"/>
-      <c r="I56" s="7" t="n"/>
-      <c r="J56" s="7" t="n"/>
-      <c r="K56" s="7" t="n"/>
+      <c r="I56" s="8" t="n"/>
+      <c r="J56" s="8" t="n"/>
+      <c r="K56" s="8" t="n"/>
       <c r="L56" s="8" t="n"/>
       <c r="M56" s="8" t="n"/>
       <c r="N56" s="8" t="n"/>
       <c r="O56" s="8" t="n"/>
-      <c r="P56" s="9" t="n"/>
-      <c r="Q56" s="9" t="n"/>
+      <c r="P56" s="8" t="n"/>
+      <c r="Q56" s="8" t="n"/>
       <c r="R56" s="9" t="n"/>
       <c r="S56" s="9" t="n"/>
       <c r="T56" s="9" t="n"/>
       <c r="U56" s="9" t="n"/>
-      <c r="V56" s="9" t="n"/>
+      <c r="V56" s="10" t="n"/>
       <c r="W56" s="10" t="n"/>
       <c r="X56" s="10" t="n"/>
       <c r="Y56" s="10" t="n"/>
-      <c r="Z56" s="11" t="n"/>
-      <c r="AA56" s="11" t="n"/>
+      <c r="Z56" s="10" t="n"/>
+      <c r="AA56" s="10" t="n"/>
+      <c r="AB56" s="10" t="n"/>
+      <c r="AC56" s="11" t="n"/>
+      <c r="AD56" s="11" t="n"/>
+      <c r="AE56" s="11" t="n"/>
+      <c r="AF56" s="12" t="n"/>
+      <c r="AG56" s="12" t="n"/>
+      <c r="AH56" s="7" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="6" t="n"/>
@@ -2538,25 +3059,32 @@
       <c r="F57" s="7" t="n"/>
       <c r="G57" s="7" t="n"/>
       <c r="H57" s="7" t="n"/>
-      <c r="I57" s="7" t="n"/>
-      <c r="J57" s="7" t="n"/>
-      <c r="K57" s="7" t="n"/>
+      <c r="I57" s="8" t="n"/>
+      <c r="J57" s="8" t="n"/>
+      <c r="K57" s="8" t="n"/>
       <c r="L57" s="8" t="n"/>
       <c r="M57" s="8" t="n"/>
       <c r="N57" s="8" t="n"/>
       <c r="O57" s="8" t="n"/>
-      <c r="P57" s="9" t="n"/>
-      <c r="Q57" s="9" t="n"/>
+      <c r="P57" s="8" t="n"/>
+      <c r="Q57" s="8" t="n"/>
       <c r="R57" s="9" t="n"/>
       <c r="S57" s="9" t="n"/>
       <c r="T57" s="9" t="n"/>
       <c r="U57" s="9" t="n"/>
-      <c r="V57" s="9" t="n"/>
+      <c r="V57" s="10" t="n"/>
       <c r="W57" s="10" t="n"/>
       <c r="X57" s="10" t="n"/>
       <c r="Y57" s="10" t="n"/>
-      <c r="Z57" s="11" t="n"/>
-      <c r="AA57" s="11" t="n"/>
+      <c r="Z57" s="10" t="n"/>
+      <c r="AA57" s="10" t="n"/>
+      <c r="AB57" s="10" t="n"/>
+      <c r="AC57" s="11" t="n"/>
+      <c r="AD57" s="11" t="n"/>
+      <c r="AE57" s="11" t="n"/>
+      <c r="AF57" s="12" t="n"/>
+      <c r="AG57" s="12" t="n"/>
+      <c r="AH57" s="7" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="6" t="n"/>
@@ -2566,25 +3094,32 @@
       <c r="F58" s="7" t="n"/>
       <c r="G58" s="7" t="n"/>
       <c r="H58" s="7" t="n"/>
-      <c r="I58" s="7" t="n"/>
-      <c r="J58" s="7" t="n"/>
-      <c r="K58" s="7" t="n"/>
+      <c r="I58" s="8" t="n"/>
+      <c r="J58" s="8" t="n"/>
+      <c r="K58" s="8" t="n"/>
       <c r="L58" s="8" t="n"/>
       <c r="M58" s="8" t="n"/>
       <c r="N58" s="8" t="n"/>
       <c r="O58" s="8" t="n"/>
-      <c r="P58" s="9" t="n"/>
-      <c r="Q58" s="9" t="n"/>
+      <c r="P58" s="8" t="n"/>
+      <c r="Q58" s="8" t="n"/>
       <c r="R58" s="9" t="n"/>
       <c r="S58" s="9" t="n"/>
       <c r="T58" s="9" t="n"/>
       <c r="U58" s="9" t="n"/>
-      <c r="V58" s="9" t="n"/>
+      <c r="V58" s="10" t="n"/>
       <c r="W58" s="10" t="n"/>
       <c r="X58" s="10" t="n"/>
       <c r="Y58" s="10" t="n"/>
-      <c r="Z58" s="11" t="n"/>
-      <c r="AA58" s="11" t="n"/>
+      <c r="Z58" s="10" t="n"/>
+      <c r="AA58" s="10" t="n"/>
+      <c r="AB58" s="10" t="n"/>
+      <c r="AC58" s="11" t="n"/>
+      <c r="AD58" s="11" t="n"/>
+      <c r="AE58" s="11" t="n"/>
+      <c r="AF58" s="12" t="n"/>
+      <c r="AG58" s="12" t="n"/>
+      <c r="AH58" s="7" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="6" t="n"/>
@@ -2594,25 +3129,32 @@
       <c r="F59" s="7" t="n"/>
       <c r="G59" s="7" t="n"/>
       <c r="H59" s="7" t="n"/>
-      <c r="I59" s="7" t="n"/>
-      <c r="J59" s="7" t="n"/>
-      <c r="K59" s="7" t="n"/>
+      <c r="I59" s="8" t="n"/>
+      <c r="J59" s="8" t="n"/>
+      <c r="K59" s="8" t="n"/>
       <c r="L59" s="8" t="n"/>
       <c r="M59" s="8" t="n"/>
       <c r="N59" s="8" t="n"/>
       <c r="O59" s="8" t="n"/>
-      <c r="P59" s="9" t="n"/>
-      <c r="Q59" s="9" t="n"/>
+      <c r="P59" s="8" t="n"/>
+      <c r="Q59" s="8" t="n"/>
       <c r="R59" s="9" t="n"/>
       <c r="S59" s="9" t="n"/>
       <c r="T59" s="9" t="n"/>
       <c r="U59" s="9" t="n"/>
-      <c r="V59" s="9" t="n"/>
+      <c r="V59" s="10" t="n"/>
       <c r="W59" s="10" t="n"/>
       <c r="X59" s="10" t="n"/>
       <c r="Y59" s="10" t="n"/>
-      <c r="Z59" s="11" t="n"/>
-      <c r="AA59" s="11" t="n"/>
+      <c r="Z59" s="10" t="n"/>
+      <c r="AA59" s="10" t="n"/>
+      <c r="AB59" s="10" t="n"/>
+      <c r="AC59" s="11" t="n"/>
+      <c r="AD59" s="11" t="n"/>
+      <c r="AE59" s="11" t="n"/>
+      <c r="AF59" s="12" t="n"/>
+      <c r="AG59" s="12" t="n"/>
+      <c r="AH59" s="7" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="6" t="n"/>
@@ -2622,25 +3164,32 @@
       <c r="F60" s="7" t="n"/>
       <c r="G60" s="7" t="n"/>
       <c r="H60" s="7" t="n"/>
-      <c r="I60" s="7" t="n"/>
-      <c r="J60" s="7" t="n"/>
-      <c r="K60" s="7" t="n"/>
+      <c r="I60" s="8" t="n"/>
+      <c r="J60" s="8" t="n"/>
+      <c r="K60" s="8" t="n"/>
       <c r="L60" s="8" t="n"/>
       <c r="M60" s="8" t="n"/>
       <c r="N60" s="8" t="n"/>
       <c r="O60" s="8" t="n"/>
-      <c r="P60" s="9" t="n"/>
-      <c r="Q60" s="9" t="n"/>
+      <c r="P60" s="8" t="n"/>
+      <c r="Q60" s="8" t="n"/>
       <c r="R60" s="9" t="n"/>
       <c r="S60" s="9" t="n"/>
       <c r="T60" s="9" t="n"/>
       <c r="U60" s="9" t="n"/>
-      <c r="V60" s="9" t="n"/>
+      <c r="V60" s="10" t="n"/>
       <c r="W60" s="10" t="n"/>
       <c r="X60" s="10" t="n"/>
       <c r="Y60" s="10" t="n"/>
-      <c r="Z60" s="11" t="n"/>
-      <c r="AA60" s="11" t="n"/>
+      <c r="Z60" s="10" t="n"/>
+      <c r="AA60" s="10" t="n"/>
+      <c r="AB60" s="10" t="n"/>
+      <c r="AC60" s="11" t="n"/>
+      <c r="AD60" s="11" t="n"/>
+      <c r="AE60" s="11" t="n"/>
+      <c r="AF60" s="12" t="n"/>
+      <c r="AG60" s="12" t="n"/>
+      <c r="AH60" s="7" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="6" t="n"/>
@@ -2650,25 +3199,32 @@
       <c r="F61" s="7" t="n"/>
       <c r="G61" s="7" t="n"/>
       <c r="H61" s="7" t="n"/>
-      <c r="I61" s="7" t="n"/>
-      <c r="J61" s="7" t="n"/>
-      <c r="K61" s="7" t="n"/>
+      <c r="I61" s="8" t="n"/>
+      <c r="J61" s="8" t="n"/>
+      <c r="K61" s="8" t="n"/>
       <c r="L61" s="8" t="n"/>
       <c r="M61" s="8" t="n"/>
       <c r="N61" s="8" t="n"/>
       <c r="O61" s="8" t="n"/>
-      <c r="P61" s="9" t="n"/>
-      <c r="Q61" s="9" t="n"/>
+      <c r="P61" s="8" t="n"/>
+      <c r="Q61" s="8" t="n"/>
       <c r="R61" s="9" t="n"/>
       <c r="S61" s="9" t="n"/>
       <c r="T61" s="9" t="n"/>
       <c r="U61" s="9" t="n"/>
-      <c r="V61" s="9" t="n"/>
+      <c r="V61" s="10" t="n"/>
       <c r="W61" s="10" t="n"/>
       <c r="X61" s="10" t="n"/>
       <c r="Y61" s="10" t="n"/>
-      <c r="Z61" s="11" t="n"/>
-      <c r="AA61" s="11" t="n"/>
+      <c r="Z61" s="10" t="n"/>
+      <c r="AA61" s="10" t="n"/>
+      <c r="AB61" s="10" t="n"/>
+      <c r="AC61" s="11" t="n"/>
+      <c r="AD61" s="11" t="n"/>
+      <c r="AE61" s="11" t="n"/>
+      <c r="AF61" s="12" t="n"/>
+      <c r="AG61" s="12" t="n"/>
+      <c r="AH61" s="7" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="6" t="n"/>
@@ -2678,25 +3234,32 @@
       <c r="F62" s="7" t="n"/>
       <c r="G62" s="7" t="n"/>
       <c r="H62" s="7" t="n"/>
-      <c r="I62" s="7" t="n"/>
-      <c r="J62" s="7" t="n"/>
-      <c r="K62" s="7" t="n"/>
+      <c r="I62" s="8" t="n"/>
+      <c r="J62" s="8" t="n"/>
+      <c r="K62" s="8" t="n"/>
       <c r="L62" s="8" t="n"/>
       <c r="M62" s="8" t="n"/>
       <c r="N62" s="8" t="n"/>
       <c r="O62" s="8" t="n"/>
-      <c r="P62" s="9" t="n"/>
-      <c r="Q62" s="9" t="n"/>
+      <c r="P62" s="8" t="n"/>
+      <c r="Q62" s="8" t="n"/>
       <c r="R62" s="9" t="n"/>
       <c r="S62" s="9" t="n"/>
       <c r="T62" s="9" t="n"/>
       <c r="U62" s="9" t="n"/>
-      <c r="V62" s="9" t="n"/>
+      <c r="V62" s="10" t="n"/>
       <c r="W62" s="10" t="n"/>
       <c r="X62" s="10" t="n"/>
       <c r="Y62" s="10" t="n"/>
-      <c r="Z62" s="11" t="n"/>
-      <c r="AA62" s="11" t="n"/>
+      <c r="Z62" s="10" t="n"/>
+      <c r="AA62" s="10" t="n"/>
+      <c r="AB62" s="10" t="n"/>
+      <c r="AC62" s="11" t="n"/>
+      <c r="AD62" s="11" t="n"/>
+      <c r="AE62" s="11" t="n"/>
+      <c r="AF62" s="12" t="n"/>
+      <c r="AG62" s="12" t="n"/>
+      <c r="AH62" s="7" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="6" t="n"/>
@@ -2706,25 +3269,32 @@
       <c r="F63" s="7" t="n"/>
       <c r="G63" s="7" t="n"/>
       <c r="H63" s="7" t="n"/>
-      <c r="I63" s="7" t="n"/>
-      <c r="J63" s="7" t="n"/>
-      <c r="K63" s="7" t="n"/>
+      <c r="I63" s="8" t="n"/>
+      <c r="J63" s="8" t="n"/>
+      <c r="K63" s="8" t="n"/>
       <c r="L63" s="8" t="n"/>
       <c r="M63" s="8" t="n"/>
       <c r="N63" s="8" t="n"/>
       <c r="O63" s="8" t="n"/>
-      <c r="P63" s="9" t="n"/>
-      <c r="Q63" s="9" t="n"/>
+      <c r="P63" s="8" t="n"/>
+      <c r="Q63" s="8" t="n"/>
       <c r="R63" s="9" t="n"/>
       <c r="S63" s="9" t="n"/>
       <c r="T63" s="9" t="n"/>
       <c r="U63" s="9" t="n"/>
-      <c r="V63" s="9" t="n"/>
+      <c r="V63" s="10" t="n"/>
       <c r="W63" s="10" t="n"/>
       <c r="X63" s="10" t="n"/>
       <c r="Y63" s="10" t="n"/>
-      <c r="Z63" s="11" t="n"/>
-      <c r="AA63" s="11" t="n"/>
+      <c r="Z63" s="10" t="n"/>
+      <c r="AA63" s="10" t="n"/>
+      <c r="AB63" s="10" t="n"/>
+      <c r="AC63" s="11" t="n"/>
+      <c r="AD63" s="11" t="n"/>
+      <c r="AE63" s="11" t="n"/>
+      <c r="AF63" s="12" t="n"/>
+      <c r="AG63" s="12" t="n"/>
+      <c r="AH63" s="7" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="6" t="n"/>
@@ -2734,25 +3304,32 @@
       <c r="F64" s="7" t="n"/>
       <c r="G64" s="7" t="n"/>
       <c r="H64" s="7" t="n"/>
-      <c r="I64" s="7" t="n"/>
-      <c r="J64" s="7" t="n"/>
-      <c r="K64" s="7" t="n"/>
+      <c r="I64" s="8" t="n"/>
+      <c r="J64" s="8" t="n"/>
+      <c r="K64" s="8" t="n"/>
       <c r="L64" s="8" t="n"/>
       <c r="M64" s="8" t="n"/>
       <c r="N64" s="8" t="n"/>
       <c r="O64" s="8" t="n"/>
-      <c r="P64" s="9" t="n"/>
-      <c r="Q64" s="9" t="n"/>
+      <c r="P64" s="8" t="n"/>
+      <c r="Q64" s="8" t="n"/>
       <c r="R64" s="9" t="n"/>
       <c r="S64" s="9" t="n"/>
       <c r="T64" s="9" t="n"/>
       <c r="U64" s="9" t="n"/>
-      <c r="V64" s="9" t="n"/>
+      <c r="V64" s="10" t="n"/>
       <c r="W64" s="10" t="n"/>
       <c r="X64" s="10" t="n"/>
       <c r="Y64" s="10" t="n"/>
-      <c r="Z64" s="11" t="n"/>
-      <c r="AA64" s="11" t="n"/>
+      <c r="Z64" s="10" t="n"/>
+      <c r="AA64" s="10" t="n"/>
+      <c r="AB64" s="10" t="n"/>
+      <c r="AC64" s="11" t="n"/>
+      <c r="AD64" s="11" t="n"/>
+      <c r="AE64" s="11" t="n"/>
+      <c r="AF64" s="12" t="n"/>
+      <c r="AG64" s="12" t="n"/>
+      <c r="AH64" s="7" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="6" t="n"/>
@@ -2762,25 +3339,32 @@
       <c r="F65" s="7" t="n"/>
       <c r="G65" s="7" t="n"/>
       <c r="H65" s="7" t="n"/>
-      <c r="I65" s="7" t="n"/>
-      <c r="J65" s="7" t="n"/>
-      <c r="K65" s="7" t="n"/>
+      <c r="I65" s="8" t="n"/>
+      <c r="J65" s="8" t="n"/>
+      <c r="K65" s="8" t="n"/>
       <c r="L65" s="8" t="n"/>
       <c r="M65" s="8" t="n"/>
       <c r="N65" s="8" t="n"/>
       <c r="O65" s="8" t="n"/>
-      <c r="P65" s="9" t="n"/>
-      <c r="Q65" s="9" t="n"/>
+      <c r="P65" s="8" t="n"/>
+      <c r="Q65" s="8" t="n"/>
       <c r="R65" s="9" t="n"/>
       <c r="S65" s="9" t="n"/>
       <c r="T65" s="9" t="n"/>
       <c r="U65" s="9" t="n"/>
-      <c r="V65" s="9" t="n"/>
+      <c r="V65" s="10" t="n"/>
       <c r="W65" s="10" t="n"/>
       <c r="X65" s="10" t="n"/>
       <c r="Y65" s="10" t="n"/>
-      <c r="Z65" s="11" t="n"/>
-      <c r="AA65" s="11" t="n"/>
+      <c r="Z65" s="10" t="n"/>
+      <c r="AA65" s="10" t="n"/>
+      <c r="AB65" s="10" t="n"/>
+      <c r="AC65" s="11" t="n"/>
+      <c r="AD65" s="11" t="n"/>
+      <c r="AE65" s="11" t="n"/>
+      <c r="AF65" s="12" t="n"/>
+      <c r="AG65" s="12" t="n"/>
+      <c r="AH65" s="7" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="6" t="n"/>
@@ -2790,25 +3374,32 @@
       <c r="F66" s="7" t="n"/>
       <c r="G66" s="7" t="n"/>
       <c r="H66" s="7" t="n"/>
-      <c r="I66" s="7" t="n"/>
-      <c r="J66" s="7" t="n"/>
-      <c r="K66" s="7" t="n"/>
+      <c r="I66" s="8" t="n"/>
+      <c r="J66" s="8" t="n"/>
+      <c r="K66" s="8" t="n"/>
       <c r="L66" s="8" t="n"/>
       <c r="M66" s="8" t="n"/>
       <c r="N66" s="8" t="n"/>
       <c r="O66" s="8" t="n"/>
-      <c r="P66" s="9" t="n"/>
-      <c r="Q66" s="9" t="n"/>
+      <c r="P66" s="8" t="n"/>
+      <c r="Q66" s="8" t="n"/>
       <c r="R66" s="9" t="n"/>
       <c r="S66" s="9" t="n"/>
       <c r="T66" s="9" t="n"/>
       <c r="U66" s="9" t="n"/>
-      <c r="V66" s="9" t="n"/>
+      <c r="V66" s="10" t="n"/>
       <c r="W66" s="10" t="n"/>
       <c r="X66" s="10" t="n"/>
       <c r="Y66" s="10" t="n"/>
-      <c r="Z66" s="11" t="n"/>
-      <c r="AA66" s="11" t="n"/>
+      <c r="Z66" s="10" t="n"/>
+      <c r="AA66" s="10" t="n"/>
+      <c r="AB66" s="10" t="n"/>
+      <c r="AC66" s="11" t="n"/>
+      <c r="AD66" s="11" t="n"/>
+      <c r="AE66" s="11" t="n"/>
+      <c r="AF66" s="12" t="n"/>
+      <c r="AG66" s="12" t="n"/>
+      <c r="AH66" s="7" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="6" t="n"/>
@@ -2818,25 +3409,32 @@
       <c r="F67" s="7" t="n"/>
       <c r="G67" s="7" t="n"/>
       <c r="H67" s="7" t="n"/>
-      <c r="I67" s="7" t="n"/>
-      <c r="J67" s="7" t="n"/>
-      <c r="K67" s="7" t="n"/>
+      <c r="I67" s="8" t="n"/>
+      <c r="J67" s="8" t="n"/>
+      <c r="K67" s="8" t="n"/>
       <c r="L67" s="8" t="n"/>
       <c r="M67" s="8" t="n"/>
       <c r="N67" s="8" t="n"/>
       <c r="O67" s="8" t="n"/>
-      <c r="P67" s="9" t="n"/>
-      <c r="Q67" s="9" t="n"/>
+      <c r="P67" s="8" t="n"/>
+      <c r="Q67" s="8" t="n"/>
       <c r="R67" s="9" t="n"/>
       <c r="S67" s="9" t="n"/>
       <c r="T67" s="9" t="n"/>
       <c r="U67" s="9" t="n"/>
-      <c r="V67" s="9" t="n"/>
+      <c r="V67" s="10" t="n"/>
       <c r="W67" s="10" t="n"/>
       <c r="X67" s="10" t="n"/>
       <c r="Y67" s="10" t="n"/>
-      <c r="Z67" s="11" t="n"/>
-      <c r="AA67" s="11" t="n"/>
+      <c r="Z67" s="10" t="n"/>
+      <c r="AA67" s="10" t="n"/>
+      <c r="AB67" s="10" t="n"/>
+      <c r="AC67" s="11" t="n"/>
+      <c r="AD67" s="11" t="n"/>
+      <c r="AE67" s="11" t="n"/>
+      <c r="AF67" s="12" t="n"/>
+      <c r="AG67" s="12" t="n"/>
+      <c r="AH67" s="7" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="6" t="n"/>
@@ -2846,25 +3444,32 @@
       <c r="F68" s="7" t="n"/>
       <c r="G68" s="7" t="n"/>
       <c r="H68" s="7" t="n"/>
-      <c r="I68" s="7" t="n"/>
-      <c r="J68" s="7" t="n"/>
-      <c r="K68" s="7" t="n"/>
+      <c r="I68" s="8" t="n"/>
+      <c r="J68" s="8" t="n"/>
+      <c r="K68" s="8" t="n"/>
       <c r="L68" s="8" t="n"/>
       <c r="M68" s="8" t="n"/>
       <c r="N68" s="8" t="n"/>
       <c r="O68" s="8" t="n"/>
-      <c r="P68" s="9" t="n"/>
-      <c r="Q68" s="9" t="n"/>
+      <c r="P68" s="8" t="n"/>
+      <c r="Q68" s="8" t="n"/>
       <c r="R68" s="9" t="n"/>
       <c r="S68" s="9" t="n"/>
       <c r="T68" s="9" t="n"/>
       <c r="U68" s="9" t="n"/>
-      <c r="V68" s="9" t="n"/>
+      <c r="V68" s="10" t="n"/>
       <c r="W68" s="10" t="n"/>
       <c r="X68" s="10" t="n"/>
       <c r="Y68" s="10" t="n"/>
-      <c r="Z68" s="11" t="n"/>
-      <c r="AA68" s="11" t="n"/>
+      <c r="Z68" s="10" t="n"/>
+      <c r="AA68" s="10" t="n"/>
+      <c r="AB68" s="10" t="n"/>
+      <c r="AC68" s="11" t="n"/>
+      <c r="AD68" s="11" t="n"/>
+      <c r="AE68" s="11" t="n"/>
+      <c r="AF68" s="12" t="n"/>
+      <c r="AG68" s="12" t="n"/>
+      <c r="AH68" s="7" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="6" t="n"/>
@@ -2874,25 +3479,32 @@
       <c r="F69" s="7" t="n"/>
       <c r="G69" s="7" t="n"/>
       <c r="H69" s="7" t="n"/>
-      <c r="I69" s="7" t="n"/>
-      <c r="J69" s="7" t="n"/>
-      <c r="K69" s="7" t="n"/>
+      <c r="I69" s="8" t="n"/>
+      <c r="J69" s="8" t="n"/>
+      <c r="K69" s="8" t="n"/>
       <c r="L69" s="8" t="n"/>
       <c r="M69" s="8" t="n"/>
       <c r="N69" s="8" t="n"/>
       <c r="O69" s="8" t="n"/>
-      <c r="P69" s="9" t="n"/>
-      <c r="Q69" s="9" t="n"/>
+      <c r="P69" s="8" t="n"/>
+      <c r="Q69" s="8" t="n"/>
       <c r="R69" s="9" t="n"/>
       <c r="S69" s="9" t="n"/>
       <c r="T69" s="9" t="n"/>
       <c r="U69" s="9" t="n"/>
-      <c r="V69" s="9" t="n"/>
+      <c r="V69" s="10" t="n"/>
       <c r="W69" s="10" t="n"/>
       <c r="X69" s="10" t="n"/>
       <c r="Y69" s="10" t="n"/>
-      <c r="Z69" s="11" t="n"/>
-      <c r="AA69" s="11" t="n"/>
+      <c r="Z69" s="10" t="n"/>
+      <c r="AA69" s="10" t="n"/>
+      <c r="AB69" s="10" t="n"/>
+      <c r="AC69" s="11" t="n"/>
+      <c r="AD69" s="11" t="n"/>
+      <c r="AE69" s="11" t="n"/>
+      <c r="AF69" s="12" t="n"/>
+      <c r="AG69" s="12" t="n"/>
+      <c r="AH69" s="7" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="6" t="n"/>
@@ -2902,25 +3514,32 @@
       <c r="F70" s="7" t="n"/>
       <c r="G70" s="7" t="n"/>
       <c r="H70" s="7" t="n"/>
-      <c r="I70" s="7" t="n"/>
-      <c r="J70" s="7" t="n"/>
-      <c r="K70" s="7" t="n"/>
+      <c r="I70" s="8" t="n"/>
+      <c r="J70" s="8" t="n"/>
+      <c r="K70" s="8" t="n"/>
       <c r="L70" s="8" t="n"/>
       <c r="M70" s="8" t="n"/>
       <c r="N70" s="8" t="n"/>
       <c r="O70" s="8" t="n"/>
-      <c r="P70" s="9" t="n"/>
-      <c r="Q70" s="9" t="n"/>
+      <c r="P70" s="8" t="n"/>
+      <c r="Q70" s="8" t="n"/>
       <c r="R70" s="9" t="n"/>
       <c r="S70" s="9" t="n"/>
       <c r="T70" s="9" t="n"/>
       <c r="U70" s="9" t="n"/>
-      <c r="V70" s="9" t="n"/>
+      <c r="V70" s="10" t="n"/>
       <c r="W70" s="10" t="n"/>
       <c r="X70" s="10" t="n"/>
       <c r="Y70" s="10" t="n"/>
-      <c r="Z70" s="11" t="n"/>
-      <c r="AA70" s="11" t="n"/>
+      <c r="Z70" s="10" t="n"/>
+      <c r="AA70" s="10" t="n"/>
+      <c r="AB70" s="10" t="n"/>
+      <c r="AC70" s="11" t="n"/>
+      <c r="AD70" s="11" t="n"/>
+      <c r="AE70" s="11" t="n"/>
+      <c r="AF70" s="12" t="n"/>
+      <c r="AG70" s="12" t="n"/>
+      <c r="AH70" s="7" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="6" t="n"/>
@@ -2930,25 +3549,32 @@
       <c r="F71" s="7" t="n"/>
       <c r="G71" s="7" t="n"/>
       <c r="H71" s="7" t="n"/>
-      <c r="I71" s="7" t="n"/>
-      <c r="J71" s="7" t="n"/>
-      <c r="K71" s="7" t="n"/>
+      <c r="I71" s="8" t="n"/>
+      <c r="J71" s="8" t="n"/>
+      <c r="K71" s="8" t="n"/>
       <c r="L71" s="8" t="n"/>
       <c r="M71" s="8" t="n"/>
       <c r="N71" s="8" t="n"/>
       <c r="O71" s="8" t="n"/>
-      <c r="P71" s="9" t="n"/>
-      <c r="Q71" s="9" t="n"/>
+      <c r="P71" s="8" t="n"/>
+      <c r="Q71" s="8" t="n"/>
       <c r="R71" s="9" t="n"/>
       <c r="S71" s="9" t="n"/>
       <c r="T71" s="9" t="n"/>
       <c r="U71" s="9" t="n"/>
-      <c r="V71" s="9" t="n"/>
+      <c r="V71" s="10" t="n"/>
       <c r="W71" s="10" t="n"/>
       <c r="X71" s="10" t="n"/>
       <c r="Y71" s="10" t="n"/>
-      <c r="Z71" s="11" t="n"/>
-      <c r="AA71" s="11" t="n"/>
+      <c r="Z71" s="10" t="n"/>
+      <c r="AA71" s="10" t="n"/>
+      <c r="AB71" s="10" t="n"/>
+      <c r="AC71" s="11" t="n"/>
+      <c r="AD71" s="11" t="n"/>
+      <c r="AE71" s="11" t="n"/>
+      <c r="AF71" s="12" t="n"/>
+      <c r="AG71" s="12" t="n"/>
+      <c r="AH71" s="7" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="6" t="n"/>
@@ -2958,25 +3584,32 @@
       <c r="F72" s="7" t="n"/>
       <c r="G72" s="7" t="n"/>
       <c r="H72" s="7" t="n"/>
-      <c r="I72" s="7" t="n"/>
-      <c r="J72" s="7" t="n"/>
-      <c r="K72" s="7" t="n"/>
+      <c r="I72" s="8" t="n"/>
+      <c r="J72" s="8" t="n"/>
+      <c r="K72" s="8" t="n"/>
       <c r="L72" s="8" t="n"/>
       <c r="M72" s="8" t="n"/>
       <c r="N72" s="8" t="n"/>
       <c r="O72" s="8" t="n"/>
-      <c r="P72" s="9" t="n"/>
-      <c r="Q72" s="9" t="n"/>
+      <c r="P72" s="8" t="n"/>
+      <c r="Q72" s="8" t="n"/>
       <c r="R72" s="9" t="n"/>
       <c r="S72" s="9" t="n"/>
       <c r="T72" s="9" t="n"/>
       <c r="U72" s="9" t="n"/>
-      <c r="V72" s="9" t="n"/>
+      <c r="V72" s="10" t="n"/>
       <c r="W72" s="10" t="n"/>
       <c r="X72" s="10" t="n"/>
       <c r="Y72" s="10" t="n"/>
-      <c r="Z72" s="11" t="n"/>
-      <c r="AA72" s="11" t="n"/>
+      <c r="Z72" s="10" t="n"/>
+      <c r="AA72" s="10" t="n"/>
+      <c r="AB72" s="10" t="n"/>
+      <c r="AC72" s="11" t="n"/>
+      <c r="AD72" s="11" t="n"/>
+      <c r="AE72" s="11" t="n"/>
+      <c r="AF72" s="12" t="n"/>
+      <c r="AG72" s="12" t="n"/>
+      <c r="AH72" s="7" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="6" t="n"/>
@@ -2986,25 +3619,32 @@
       <c r="F73" s="7" t="n"/>
       <c r="G73" s="7" t="n"/>
       <c r="H73" s="7" t="n"/>
-      <c r="I73" s="7" t="n"/>
-      <c r="J73" s="7" t="n"/>
-      <c r="K73" s="7" t="n"/>
+      <c r="I73" s="8" t="n"/>
+      <c r="J73" s="8" t="n"/>
+      <c r="K73" s="8" t="n"/>
       <c r="L73" s="8" t="n"/>
       <c r="M73" s="8" t="n"/>
       <c r="N73" s="8" t="n"/>
       <c r="O73" s="8" t="n"/>
-      <c r="P73" s="9" t="n"/>
-      <c r="Q73" s="9" t="n"/>
+      <c r="P73" s="8" t="n"/>
+      <c r="Q73" s="8" t="n"/>
       <c r="R73" s="9" t="n"/>
       <c r="S73" s="9" t="n"/>
       <c r="T73" s="9" t="n"/>
       <c r="U73" s="9" t="n"/>
-      <c r="V73" s="9" t="n"/>
+      <c r="V73" s="10" t="n"/>
       <c r="W73" s="10" t="n"/>
       <c r="X73" s="10" t="n"/>
       <c r="Y73" s="10" t="n"/>
-      <c r="Z73" s="11" t="n"/>
-      <c r="AA73" s="11" t="n"/>
+      <c r="Z73" s="10" t="n"/>
+      <c r="AA73" s="10" t="n"/>
+      <c r="AB73" s="10" t="n"/>
+      <c r="AC73" s="11" t="n"/>
+      <c r="AD73" s="11" t="n"/>
+      <c r="AE73" s="11" t="n"/>
+      <c r="AF73" s="12" t="n"/>
+      <c r="AG73" s="12" t="n"/>
+      <c r="AH73" s="7" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="6" t="n"/>
@@ -3014,25 +3654,32 @@
       <c r="F74" s="7" t="n"/>
       <c r="G74" s="7" t="n"/>
       <c r="H74" s="7" t="n"/>
-      <c r="I74" s="7" t="n"/>
-      <c r="J74" s="7" t="n"/>
-      <c r="K74" s="7" t="n"/>
+      <c r="I74" s="8" t="n"/>
+      <c r="J74" s="8" t="n"/>
+      <c r="K74" s="8" t="n"/>
       <c r="L74" s="8" t="n"/>
       <c r="M74" s="8" t="n"/>
       <c r="N74" s="8" t="n"/>
       <c r="O74" s="8" t="n"/>
-      <c r="P74" s="9" t="n"/>
-      <c r="Q74" s="9" t="n"/>
+      <c r="P74" s="8" t="n"/>
+      <c r="Q74" s="8" t="n"/>
       <c r="R74" s="9" t="n"/>
       <c r="S74" s="9" t="n"/>
       <c r="T74" s="9" t="n"/>
       <c r="U74" s="9" t="n"/>
-      <c r="V74" s="9" t="n"/>
+      <c r="V74" s="10" t="n"/>
       <c r="W74" s="10" t="n"/>
       <c r="X74" s="10" t="n"/>
       <c r="Y74" s="10" t="n"/>
-      <c r="Z74" s="11" t="n"/>
-      <c r="AA74" s="11" t="n"/>
+      <c r="Z74" s="10" t="n"/>
+      <c r="AA74" s="10" t="n"/>
+      <c r="AB74" s="10" t="n"/>
+      <c r="AC74" s="11" t="n"/>
+      <c r="AD74" s="11" t="n"/>
+      <c r="AE74" s="11" t="n"/>
+      <c r="AF74" s="12" t="n"/>
+      <c r="AG74" s="12" t="n"/>
+      <c r="AH74" s="7" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="6" t="n"/>
@@ -3042,25 +3689,32 @@
       <c r="F75" s="7" t="n"/>
       <c r="G75" s="7" t="n"/>
       <c r="H75" s="7" t="n"/>
-      <c r="I75" s="7" t="n"/>
-      <c r="J75" s="7" t="n"/>
-      <c r="K75" s="7" t="n"/>
+      <c r="I75" s="8" t="n"/>
+      <c r="J75" s="8" t="n"/>
+      <c r="K75" s="8" t="n"/>
       <c r="L75" s="8" t="n"/>
       <c r="M75" s="8" t="n"/>
       <c r="N75" s="8" t="n"/>
       <c r="O75" s="8" t="n"/>
-      <c r="P75" s="9" t="n"/>
-      <c r="Q75" s="9" t="n"/>
+      <c r="P75" s="8" t="n"/>
+      <c r="Q75" s="8" t="n"/>
       <c r="R75" s="9" t="n"/>
       <c r="S75" s="9" t="n"/>
       <c r="T75" s="9" t="n"/>
       <c r="U75" s="9" t="n"/>
-      <c r="V75" s="9" t="n"/>
+      <c r="V75" s="10" t="n"/>
       <c r="W75" s="10" t="n"/>
       <c r="X75" s="10" t="n"/>
       <c r="Y75" s="10" t="n"/>
-      <c r="Z75" s="11" t="n"/>
-      <c r="AA75" s="11" t="n"/>
+      <c r="Z75" s="10" t="n"/>
+      <c r="AA75" s="10" t="n"/>
+      <c r="AB75" s="10" t="n"/>
+      <c r="AC75" s="11" t="n"/>
+      <c r="AD75" s="11" t="n"/>
+      <c r="AE75" s="11" t="n"/>
+      <c r="AF75" s="12" t="n"/>
+      <c r="AG75" s="12" t="n"/>
+      <c r="AH75" s="7" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="6" t="n"/>
@@ -3070,25 +3724,32 @@
       <c r="F76" s="7" t="n"/>
       <c r="G76" s="7" t="n"/>
       <c r="H76" s="7" t="n"/>
-      <c r="I76" s="7" t="n"/>
-      <c r="J76" s="7" t="n"/>
-      <c r="K76" s="7" t="n"/>
+      <c r="I76" s="8" t="n"/>
+      <c r="J76" s="8" t="n"/>
+      <c r="K76" s="8" t="n"/>
       <c r="L76" s="8" t="n"/>
       <c r="M76" s="8" t="n"/>
       <c r="N76" s="8" t="n"/>
       <c r="O76" s="8" t="n"/>
-      <c r="P76" s="9" t="n"/>
-      <c r="Q76" s="9" t="n"/>
+      <c r="P76" s="8" t="n"/>
+      <c r="Q76" s="8" t="n"/>
       <c r="R76" s="9" t="n"/>
       <c r="S76" s="9" t="n"/>
       <c r="T76" s="9" t="n"/>
       <c r="U76" s="9" t="n"/>
-      <c r="V76" s="9" t="n"/>
+      <c r="V76" s="10" t="n"/>
       <c r="W76" s="10" t="n"/>
       <c r="X76" s="10" t="n"/>
       <c r="Y76" s="10" t="n"/>
-      <c r="Z76" s="11" t="n"/>
-      <c r="AA76" s="11" t="n"/>
+      <c r="Z76" s="10" t="n"/>
+      <c r="AA76" s="10" t="n"/>
+      <c r="AB76" s="10" t="n"/>
+      <c r="AC76" s="11" t="n"/>
+      <c r="AD76" s="11" t="n"/>
+      <c r="AE76" s="11" t="n"/>
+      <c r="AF76" s="12" t="n"/>
+      <c r="AG76" s="12" t="n"/>
+      <c r="AH76" s="7" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="6" t="n"/>
@@ -3098,25 +3759,32 @@
       <c r="F77" s="7" t="n"/>
       <c r="G77" s="7" t="n"/>
       <c r="H77" s="7" t="n"/>
-      <c r="I77" s="7" t="n"/>
-      <c r="J77" s="7" t="n"/>
-      <c r="K77" s="7" t="n"/>
+      <c r="I77" s="8" t="n"/>
+      <c r="J77" s="8" t="n"/>
+      <c r="K77" s="8" t="n"/>
       <c r="L77" s="8" t="n"/>
       <c r="M77" s="8" t="n"/>
       <c r="N77" s="8" t="n"/>
       <c r="O77" s="8" t="n"/>
-      <c r="P77" s="9" t="n"/>
-      <c r="Q77" s="9" t="n"/>
+      <c r="P77" s="8" t="n"/>
+      <c r="Q77" s="8" t="n"/>
       <c r="R77" s="9" t="n"/>
       <c r="S77" s="9" t="n"/>
       <c r="T77" s="9" t="n"/>
       <c r="U77" s="9" t="n"/>
-      <c r="V77" s="9" t="n"/>
+      <c r="V77" s="10" t="n"/>
       <c r="W77" s="10" t="n"/>
       <c r="X77" s="10" t="n"/>
       <c r="Y77" s="10" t="n"/>
-      <c r="Z77" s="11" t="n"/>
-      <c r="AA77" s="11" t="n"/>
+      <c r="Z77" s="10" t="n"/>
+      <c r="AA77" s="10" t="n"/>
+      <c r="AB77" s="10" t="n"/>
+      <c r="AC77" s="11" t="n"/>
+      <c r="AD77" s="11" t="n"/>
+      <c r="AE77" s="11" t="n"/>
+      <c r="AF77" s="12" t="n"/>
+      <c r="AG77" s="12" t="n"/>
+      <c r="AH77" s="7" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="6" t="n"/>
@@ -3126,25 +3794,32 @@
       <c r="F78" s="7" t="n"/>
       <c r="G78" s="7" t="n"/>
       <c r="H78" s="7" t="n"/>
-      <c r="I78" s="7" t="n"/>
-      <c r="J78" s="7" t="n"/>
-      <c r="K78" s="7" t="n"/>
+      <c r="I78" s="8" t="n"/>
+      <c r="J78" s="8" t="n"/>
+      <c r="K78" s="8" t="n"/>
       <c r="L78" s="8" t="n"/>
       <c r="M78" s="8" t="n"/>
       <c r="N78" s="8" t="n"/>
       <c r="O78" s="8" t="n"/>
-      <c r="P78" s="9" t="n"/>
-      <c r="Q78" s="9" t="n"/>
+      <c r="P78" s="8" t="n"/>
+      <c r="Q78" s="8" t="n"/>
       <c r="R78" s="9" t="n"/>
       <c r="S78" s="9" t="n"/>
       <c r="T78" s="9" t="n"/>
       <c r="U78" s="9" t="n"/>
-      <c r="V78" s="9" t="n"/>
+      <c r="V78" s="10" t="n"/>
       <c r="W78" s="10" t="n"/>
       <c r="X78" s="10" t="n"/>
       <c r="Y78" s="10" t="n"/>
-      <c r="Z78" s="11" t="n"/>
-      <c r="AA78" s="11" t="n"/>
+      <c r="Z78" s="10" t="n"/>
+      <c r="AA78" s="10" t="n"/>
+      <c r="AB78" s="10" t="n"/>
+      <c r="AC78" s="11" t="n"/>
+      <c r="AD78" s="11" t="n"/>
+      <c r="AE78" s="11" t="n"/>
+      <c r="AF78" s="12" t="n"/>
+      <c r="AG78" s="12" t="n"/>
+      <c r="AH78" s="7" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="6" t="n"/>
@@ -3154,25 +3829,32 @@
       <c r="F79" s="7" t="n"/>
       <c r="G79" s="7" t="n"/>
       <c r="H79" s="7" t="n"/>
-      <c r="I79" s="7" t="n"/>
-      <c r="J79" s="7" t="n"/>
-      <c r="K79" s="7" t="n"/>
+      <c r="I79" s="8" t="n"/>
+      <c r="J79" s="8" t="n"/>
+      <c r="K79" s="8" t="n"/>
       <c r="L79" s="8" t="n"/>
       <c r="M79" s="8" t="n"/>
       <c r="N79" s="8" t="n"/>
       <c r="O79" s="8" t="n"/>
-      <c r="P79" s="9" t="n"/>
-      <c r="Q79" s="9" t="n"/>
+      <c r="P79" s="8" t="n"/>
+      <c r="Q79" s="8" t="n"/>
       <c r="R79" s="9" t="n"/>
       <c r="S79" s="9" t="n"/>
       <c r="T79" s="9" t="n"/>
       <c r="U79" s="9" t="n"/>
-      <c r="V79" s="9" t="n"/>
+      <c r="V79" s="10" t="n"/>
       <c r="W79" s="10" t="n"/>
       <c r="X79" s="10" t="n"/>
       <c r="Y79" s="10" t="n"/>
-      <c r="Z79" s="11" t="n"/>
-      <c r="AA79" s="11" t="n"/>
+      <c r="Z79" s="10" t="n"/>
+      <c r="AA79" s="10" t="n"/>
+      <c r="AB79" s="10" t="n"/>
+      <c r="AC79" s="11" t="n"/>
+      <c r="AD79" s="11" t="n"/>
+      <c r="AE79" s="11" t="n"/>
+      <c r="AF79" s="12" t="n"/>
+      <c r="AG79" s="12" t="n"/>
+      <c r="AH79" s="7" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="6" t="n"/>
@@ -3182,25 +3864,32 @@
       <c r="F80" s="7" t="n"/>
       <c r="G80" s="7" t="n"/>
       <c r="H80" s="7" t="n"/>
-      <c r="I80" s="7" t="n"/>
-      <c r="J80" s="7" t="n"/>
-      <c r="K80" s="7" t="n"/>
+      <c r="I80" s="8" t="n"/>
+      <c r="J80" s="8" t="n"/>
+      <c r="K80" s="8" t="n"/>
       <c r="L80" s="8" t="n"/>
       <c r="M80" s="8" t="n"/>
       <c r="N80" s="8" t="n"/>
       <c r="O80" s="8" t="n"/>
-      <c r="P80" s="9" t="n"/>
-      <c r="Q80" s="9" t="n"/>
+      <c r="P80" s="8" t="n"/>
+      <c r="Q80" s="8" t="n"/>
       <c r="R80" s="9" t="n"/>
       <c r="S80" s="9" t="n"/>
       <c r="T80" s="9" t="n"/>
       <c r="U80" s="9" t="n"/>
-      <c r="V80" s="9" t="n"/>
+      <c r="V80" s="10" t="n"/>
       <c r="W80" s="10" t="n"/>
       <c r="X80" s="10" t="n"/>
       <c r="Y80" s="10" t="n"/>
-      <c r="Z80" s="11" t="n"/>
-      <c r="AA80" s="11" t="n"/>
+      <c r="Z80" s="10" t="n"/>
+      <c r="AA80" s="10" t="n"/>
+      <c r="AB80" s="10" t="n"/>
+      <c r="AC80" s="11" t="n"/>
+      <c r="AD80" s="11" t="n"/>
+      <c r="AE80" s="11" t="n"/>
+      <c r="AF80" s="12" t="n"/>
+      <c r="AG80" s="12" t="n"/>
+      <c r="AH80" s="7" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="6" t="n"/>
@@ -3210,25 +3899,32 @@
       <c r="F81" s="7" t="n"/>
       <c r="G81" s="7" t="n"/>
       <c r="H81" s="7" t="n"/>
-      <c r="I81" s="7" t="n"/>
-      <c r="J81" s="7" t="n"/>
-      <c r="K81" s="7" t="n"/>
+      <c r="I81" s="8" t="n"/>
+      <c r="J81" s="8" t="n"/>
+      <c r="K81" s="8" t="n"/>
       <c r="L81" s="8" t="n"/>
       <c r="M81" s="8" t="n"/>
       <c r="N81" s="8" t="n"/>
       <c r="O81" s="8" t="n"/>
-      <c r="P81" s="9" t="n"/>
-      <c r="Q81" s="9" t="n"/>
+      <c r="P81" s="8" t="n"/>
+      <c r="Q81" s="8" t="n"/>
       <c r="R81" s="9" t="n"/>
       <c r="S81" s="9" t="n"/>
       <c r="T81" s="9" t="n"/>
       <c r="U81" s="9" t="n"/>
-      <c r="V81" s="9" t="n"/>
+      <c r="V81" s="10" t="n"/>
       <c r="W81" s="10" t="n"/>
       <c r="X81" s="10" t="n"/>
       <c r="Y81" s="10" t="n"/>
-      <c r="Z81" s="11" t="n"/>
-      <c r="AA81" s="11" t="n"/>
+      <c r="Z81" s="10" t="n"/>
+      <c r="AA81" s="10" t="n"/>
+      <c r="AB81" s="10" t="n"/>
+      <c r="AC81" s="11" t="n"/>
+      <c r="AD81" s="11" t="n"/>
+      <c r="AE81" s="11" t="n"/>
+      <c r="AF81" s="12" t="n"/>
+      <c r="AG81" s="12" t="n"/>
+      <c r="AH81" s="7" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="6" t="n"/>
@@ -3238,25 +3934,32 @@
       <c r="F82" s="7" t="n"/>
       <c r="G82" s="7" t="n"/>
       <c r="H82" s="7" t="n"/>
-      <c r="I82" s="7" t="n"/>
-      <c r="J82" s="7" t="n"/>
-      <c r="K82" s="7" t="n"/>
+      <c r="I82" s="8" t="n"/>
+      <c r="J82" s="8" t="n"/>
+      <c r="K82" s="8" t="n"/>
       <c r="L82" s="8" t="n"/>
       <c r="M82" s="8" t="n"/>
       <c r="N82" s="8" t="n"/>
       <c r="O82" s="8" t="n"/>
-      <c r="P82" s="9" t="n"/>
-      <c r="Q82" s="9" t="n"/>
+      <c r="P82" s="8" t="n"/>
+      <c r="Q82" s="8" t="n"/>
       <c r="R82" s="9" t="n"/>
       <c r="S82" s="9" t="n"/>
       <c r="T82" s="9" t="n"/>
       <c r="U82" s="9" t="n"/>
-      <c r="V82" s="9" t="n"/>
+      <c r="V82" s="10" t="n"/>
       <c r="W82" s="10" t="n"/>
       <c r="X82" s="10" t="n"/>
       <c r="Y82" s="10" t="n"/>
-      <c r="Z82" s="11" t="n"/>
-      <c r="AA82" s="11" t="n"/>
+      <c r="Z82" s="10" t="n"/>
+      <c r="AA82" s="10" t="n"/>
+      <c r="AB82" s="10" t="n"/>
+      <c r="AC82" s="11" t="n"/>
+      <c r="AD82" s="11" t="n"/>
+      <c r="AE82" s="11" t="n"/>
+      <c r="AF82" s="12" t="n"/>
+      <c r="AG82" s="12" t="n"/>
+      <c r="AH82" s="7" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="6" t="n"/>
@@ -3266,25 +3969,32 @@
       <c r="F83" s="7" t="n"/>
       <c r="G83" s="7" t="n"/>
       <c r="H83" s="7" t="n"/>
-      <c r="I83" s="7" t="n"/>
-      <c r="J83" s="7" t="n"/>
-      <c r="K83" s="7" t="n"/>
+      <c r="I83" s="8" t="n"/>
+      <c r="J83" s="8" t="n"/>
+      <c r="K83" s="8" t="n"/>
       <c r="L83" s="8" t="n"/>
       <c r="M83" s="8" t="n"/>
       <c r="N83" s="8" t="n"/>
       <c r="O83" s="8" t="n"/>
-      <c r="P83" s="9" t="n"/>
-      <c r="Q83" s="9" t="n"/>
+      <c r="P83" s="8" t="n"/>
+      <c r="Q83" s="8" t="n"/>
       <c r="R83" s="9" t="n"/>
       <c r="S83" s="9" t="n"/>
       <c r="T83" s="9" t="n"/>
       <c r="U83" s="9" t="n"/>
-      <c r="V83" s="9" t="n"/>
+      <c r="V83" s="10" t="n"/>
       <c r="W83" s="10" t="n"/>
       <c r="X83" s="10" t="n"/>
       <c r="Y83" s="10" t="n"/>
-      <c r="Z83" s="11" t="n"/>
-      <c r="AA83" s="11" t="n"/>
+      <c r="Z83" s="10" t="n"/>
+      <c r="AA83" s="10" t="n"/>
+      <c r="AB83" s="10" t="n"/>
+      <c r="AC83" s="11" t="n"/>
+      <c r="AD83" s="11" t="n"/>
+      <c r="AE83" s="11" t="n"/>
+      <c r="AF83" s="12" t="n"/>
+      <c r="AG83" s="12" t="n"/>
+      <c r="AH83" s="7" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="6" t="n"/>
@@ -3294,25 +4004,32 @@
       <c r="F84" s="7" t="n"/>
       <c r="G84" s="7" t="n"/>
       <c r="H84" s="7" t="n"/>
-      <c r="I84" s="7" t="n"/>
-      <c r="J84" s="7" t="n"/>
-      <c r="K84" s="7" t="n"/>
+      <c r="I84" s="8" t="n"/>
+      <c r="J84" s="8" t="n"/>
+      <c r="K84" s="8" t="n"/>
       <c r="L84" s="8" t="n"/>
       <c r="M84" s="8" t="n"/>
       <c r="N84" s="8" t="n"/>
       <c r="O84" s="8" t="n"/>
-      <c r="P84" s="9" t="n"/>
-      <c r="Q84" s="9" t="n"/>
+      <c r="P84" s="8" t="n"/>
+      <c r="Q84" s="8" t="n"/>
       <c r="R84" s="9" t="n"/>
       <c r="S84" s="9" t="n"/>
       <c r="T84" s="9" t="n"/>
       <c r="U84" s="9" t="n"/>
-      <c r="V84" s="9" t="n"/>
+      <c r="V84" s="10" t="n"/>
       <c r="W84" s="10" t="n"/>
       <c r="X84" s="10" t="n"/>
       <c r="Y84" s="10" t="n"/>
-      <c r="Z84" s="11" t="n"/>
-      <c r="AA84" s="11" t="n"/>
+      <c r="Z84" s="10" t="n"/>
+      <c r="AA84" s="10" t="n"/>
+      <c r="AB84" s="10" t="n"/>
+      <c r="AC84" s="11" t="n"/>
+      <c r="AD84" s="11" t="n"/>
+      <c r="AE84" s="11" t="n"/>
+      <c r="AF84" s="12" t="n"/>
+      <c r="AG84" s="12" t="n"/>
+      <c r="AH84" s="7" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="6" t="n"/>
@@ -3322,25 +4039,32 @@
       <c r="F85" s="7" t="n"/>
       <c r="G85" s="7" t="n"/>
       <c r="H85" s="7" t="n"/>
-      <c r="I85" s="7" t="n"/>
-      <c r="J85" s="7" t="n"/>
-      <c r="K85" s="7" t="n"/>
+      <c r="I85" s="8" t="n"/>
+      <c r="J85" s="8" t="n"/>
+      <c r="K85" s="8" t="n"/>
       <c r="L85" s="8" t="n"/>
       <c r="M85" s="8" t="n"/>
       <c r="N85" s="8" t="n"/>
       <c r="O85" s="8" t="n"/>
-      <c r="P85" s="9" t="n"/>
-      <c r="Q85" s="9" t="n"/>
+      <c r="P85" s="8" t="n"/>
+      <c r="Q85" s="8" t="n"/>
       <c r="R85" s="9" t="n"/>
       <c r="S85" s="9" t="n"/>
       <c r="T85" s="9" t="n"/>
       <c r="U85" s="9" t="n"/>
-      <c r="V85" s="9" t="n"/>
+      <c r="V85" s="10" t="n"/>
       <c r="W85" s="10" t="n"/>
       <c r="X85" s="10" t="n"/>
       <c r="Y85" s="10" t="n"/>
-      <c r="Z85" s="11" t="n"/>
-      <c r="AA85" s="11" t="n"/>
+      <c r="Z85" s="10" t="n"/>
+      <c r="AA85" s="10" t="n"/>
+      <c r="AB85" s="10" t="n"/>
+      <c r="AC85" s="11" t="n"/>
+      <c r="AD85" s="11" t="n"/>
+      <c r="AE85" s="11" t="n"/>
+      <c r="AF85" s="12" t="n"/>
+      <c r="AG85" s="12" t="n"/>
+      <c r="AH85" s="7" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="6" t="n"/>
@@ -3350,25 +4074,32 @@
       <c r="F86" s="7" t="n"/>
       <c r="G86" s="7" t="n"/>
       <c r="H86" s="7" t="n"/>
-      <c r="I86" s="7" t="n"/>
-      <c r="J86" s="7" t="n"/>
-      <c r="K86" s="7" t="n"/>
+      <c r="I86" s="8" t="n"/>
+      <c r="J86" s="8" t="n"/>
+      <c r="K86" s="8" t="n"/>
       <c r="L86" s="8" t="n"/>
       <c r="M86" s="8" t="n"/>
       <c r="N86" s="8" t="n"/>
       <c r="O86" s="8" t="n"/>
-      <c r="P86" s="9" t="n"/>
-      <c r="Q86" s="9" t="n"/>
+      <c r="P86" s="8" t="n"/>
+      <c r="Q86" s="8" t="n"/>
       <c r="R86" s="9" t="n"/>
       <c r="S86" s="9" t="n"/>
       <c r="T86" s="9" t="n"/>
       <c r="U86" s="9" t="n"/>
-      <c r="V86" s="9" t="n"/>
+      <c r="V86" s="10" t="n"/>
       <c r="W86" s="10" t="n"/>
       <c r="X86" s="10" t="n"/>
       <c r="Y86" s="10" t="n"/>
-      <c r="Z86" s="11" t="n"/>
-      <c r="AA86" s="11" t="n"/>
+      <c r="Z86" s="10" t="n"/>
+      <c r="AA86" s="10" t="n"/>
+      <c r="AB86" s="10" t="n"/>
+      <c r="AC86" s="11" t="n"/>
+      <c r="AD86" s="11" t="n"/>
+      <c r="AE86" s="11" t="n"/>
+      <c r="AF86" s="12" t="n"/>
+      <c r="AG86" s="12" t="n"/>
+      <c r="AH86" s="7" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="6" t="n"/>
@@ -3378,25 +4109,32 @@
       <c r="F87" s="7" t="n"/>
       <c r="G87" s="7" t="n"/>
       <c r="H87" s="7" t="n"/>
-      <c r="I87" s="7" t="n"/>
-      <c r="J87" s="7" t="n"/>
-      <c r="K87" s="7" t="n"/>
+      <c r="I87" s="8" t="n"/>
+      <c r="J87" s="8" t="n"/>
+      <c r="K87" s="8" t="n"/>
       <c r="L87" s="8" t="n"/>
       <c r="M87" s="8" t="n"/>
       <c r="N87" s="8" t="n"/>
       <c r="O87" s="8" t="n"/>
-      <c r="P87" s="9" t="n"/>
-      <c r="Q87" s="9" t="n"/>
+      <c r="P87" s="8" t="n"/>
+      <c r="Q87" s="8" t="n"/>
       <c r="R87" s="9" t="n"/>
       <c r="S87" s="9" t="n"/>
       <c r="T87" s="9" t="n"/>
       <c r="U87" s="9" t="n"/>
-      <c r="V87" s="9" t="n"/>
+      <c r="V87" s="10" t="n"/>
       <c r="W87" s="10" t="n"/>
       <c r="X87" s="10" t="n"/>
       <c r="Y87" s="10" t="n"/>
-      <c r="Z87" s="11" t="n"/>
-      <c r="AA87" s="11" t="n"/>
+      <c r="Z87" s="10" t="n"/>
+      <c r="AA87" s="10" t="n"/>
+      <c r="AB87" s="10" t="n"/>
+      <c r="AC87" s="11" t="n"/>
+      <c r="AD87" s="11" t="n"/>
+      <c r="AE87" s="11" t="n"/>
+      <c r="AF87" s="12" t="n"/>
+      <c r="AG87" s="12" t="n"/>
+      <c r="AH87" s="7" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="6" t="n"/>
@@ -3406,25 +4144,32 @@
       <c r="F88" s="7" t="n"/>
       <c r="G88" s="7" t="n"/>
       <c r="H88" s="7" t="n"/>
-      <c r="I88" s="7" t="n"/>
-      <c r="J88" s="7" t="n"/>
-      <c r="K88" s="7" t="n"/>
+      <c r="I88" s="8" t="n"/>
+      <c r="J88" s="8" t="n"/>
+      <c r="K88" s="8" t="n"/>
       <c r="L88" s="8" t="n"/>
       <c r="M88" s="8" t="n"/>
       <c r="N88" s="8" t="n"/>
       <c r="O88" s="8" t="n"/>
-      <c r="P88" s="9" t="n"/>
-      <c r="Q88" s="9" t="n"/>
+      <c r="P88" s="8" t="n"/>
+      <c r="Q88" s="8" t="n"/>
       <c r="R88" s="9" t="n"/>
       <c r="S88" s="9" t="n"/>
       <c r="T88" s="9" t="n"/>
       <c r="U88" s="9" t="n"/>
-      <c r="V88" s="9" t="n"/>
+      <c r="V88" s="10" t="n"/>
       <c r="W88" s="10" t="n"/>
       <c r="X88" s="10" t="n"/>
       <c r="Y88" s="10" t="n"/>
-      <c r="Z88" s="11" t="n"/>
-      <c r="AA88" s="11" t="n"/>
+      <c r="Z88" s="10" t="n"/>
+      <c r="AA88" s="10" t="n"/>
+      <c r="AB88" s="10" t="n"/>
+      <c r="AC88" s="11" t="n"/>
+      <c r="AD88" s="11" t="n"/>
+      <c r="AE88" s="11" t="n"/>
+      <c r="AF88" s="12" t="n"/>
+      <c r="AG88" s="12" t="n"/>
+      <c r="AH88" s="7" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="6" t="n"/>
@@ -3434,25 +4179,32 @@
       <c r="F89" s="7" t="n"/>
       <c r="G89" s="7" t="n"/>
       <c r="H89" s="7" t="n"/>
-      <c r="I89" s="7" t="n"/>
-      <c r="J89" s="7" t="n"/>
-      <c r="K89" s="7" t="n"/>
+      <c r="I89" s="8" t="n"/>
+      <c r="J89" s="8" t="n"/>
+      <c r="K89" s="8" t="n"/>
       <c r="L89" s="8" t="n"/>
       <c r="M89" s="8" t="n"/>
       <c r="N89" s="8" t="n"/>
       <c r="O89" s="8" t="n"/>
-      <c r="P89" s="9" t="n"/>
-      <c r="Q89" s="9" t="n"/>
+      <c r="P89" s="8" t="n"/>
+      <c r="Q89" s="8" t="n"/>
       <c r="R89" s="9" t="n"/>
       <c r="S89" s="9" t="n"/>
       <c r="T89" s="9" t="n"/>
       <c r="U89" s="9" t="n"/>
-      <c r="V89" s="9" t="n"/>
+      <c r="V89" s="10" t="n"/>
       <c r="W89" s="10" t="n"/>
       <c r="X89" s="10" t="n"/>
       <c r="Y89" s="10" t="n"/>
-      <c r="Z89" s="11" t="n"/>
-      <c r="AA89" s="11" t="n"/>
+      <c r="Z89" s="10" t="n"/>
+      <c r="AA89" s="10" t="n"/>
+      <c r="AB89" s="10" t="n"/>
+      <c r="AC89" s="11" t="n"/>
+      <c r="AD89" s="11" t="n"/>
+      <c r="AE89" s="11" t="n"/>
+      <c r="AF89" s="12" t="n"/>
+      <c r="AG89" s="12" t="n"/>
+      <c r="AH89" s="7" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="6" t="n"/>
@@ -3462,25 +4214,32 @@
       <c r="F90" s="7" t="n"/>
       <c r="G90" s="7" t="n"/>
       <c r="H90" s="7" t="n"/>
-      <c r="I90" s="7" t="n"/>
-      <c r="J90" s="7" t="n"/>
-      <c r="K90" s="7" t="n"/>
+      <c r="I90" s="8" t="n"/>
+      <c r="J90" s="8" t="n"/>
+      <c r="K90" s="8" t="n"/>
       <c r="L90" s="8" t="n"/>
       <c r="M90" s="8" t="n"/>
       <c r="N90" s="8" t="n"/>
       <c r="O90" s="8" t="n"/>
-      <c r="P90" s="9" t="n"/>
-      <c r="Q90" s="9" t="n"/>
+      <c r="P90" s="8" t="n"/>
+      <c r="Q90" s="8" t="n"/>
       <c r="R90" s="9" t="n"/>
       <c r="S90" s="9" t="n"/>
       <c r="T90" s="9" t="n"/>
       <c r="U90" s="9" t="n"/>
-      <c r="V90" s="9" t="n"/>
+      <c r="V90" s="10" t="n"/>
       <c r="W90" s="10" t="n"/>
       <c r="X90" s="10" t="n"/>
       <c r="Y90" s="10" t="n"/>
-      <c r="Z90" s="11" t="n"/>
-      <c r="AA90" s="11" t="n"/>
+      <c r="Z90" s="10" t="n"/>
+      <c r="AA90" s="10" t="n"/>
+      <c r="AB90" s="10" t="n"/>
+      <c r="AC90" s="11" t="n"/>
+      <c r="AD90" s="11" t="n"/>
+      <c r="AE90" s="11" t="n"/>
+      <c r="AF90" s="12" t="n"/>
+      <c r="AG90" s="12" t="n"/>
+      <c r="AH90" s="7" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="6" t="n"/>
@@ -3490,25 +4249,32 @@
       <c r="F91" s="7" t="n"/>
       <c r="G91" s="7" t="n"/>
       <c r="H91" s="7" t="n"/>
-      <c r="I91" s="7" t="n"/>
-      <c r="J91" s="7" t="n"/>
-      <c r="K91" s="7" t="n"/>
+      <c r="I91" s="8" t="n"/>
+      <c r="J91" s="8" t="n"/>
+      <c r="K91" s="8" t="n"/>
       <c r="L91" s="8" t="n"/>
       <c r="M91" s="8" t="n"/>
       <c r="N91" s="8" t="n"/>
       <c r="O91" s="8" t="n"/>
-      <c r="P91" s="9" t="n"/>
-      <c r="Q91" s="9" t="n"/>
+      <c r="P91" s="8" t="n"/>
+      <c r="Q91" s="8" t="n"/>
       <c r="R91" s="9" t="n"/>
       <c r="S91" s="9" t="n"/>
       <c r="T91" s="9" t="n"/>
       <c r="U91" s="9" t="n"/>
-      <c r="V91" s="9" t="n"/>
+      <c r="V91" s="10" t="n"/>
       <c r="W91" s="10" t="n"/>
       <c r="X91" s="10" t="n"/>
       <c r="Y91" s="10" t="n"/>
-      <c r="Z91" s="11" t="n"/>
-      <c r="AA91" s="11" t="n"/>
+      <c r="Z91" s="10" t="n"/>
+      <c r="AA91" s="10" t="n"/>
+      <c r="AB91" s="10" t="n"/>
+      <c r="AC91" s="11" t="n"/>
+      <c r="AD91" s="11" t="n"/>
+      <c r="AE91" s="11" t="n"/>
+      <c r="AF91" s="12" t="n"/>
+      <c r="AG91" s="12" t="n"/>
+      <c r="AH91" s="7" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="6" t="n"/>
@@ -3518,25 +4284,32 @@
       <c r="F92" s="7" t="n"/>
       <c r="G92" s="7" t="n"/>
       <c r="H92" s="7" t="n"/>
-      <c r="I92" s="7" t="n"/>
-      <c r="J92" s="7" t="n"/>
-      <c r="K92" s="7" t="n"/>
+      <c r="I92" s="8" t="n"/>
+      <c r="J92" s="8" t="n"/>
+      <c r="K92" s="8" t="n"/>
       <c r="L92" s="8" t="n"/>
       <c r="M92" s="8" t="n"/>
       <c r="N92" s="8" t="n"/>
       <c r="O92" s="8" t="n"/>
-      <c r="P92" s="9" t="n"/>
-      <c r="Q92" s="9" t="n"/>
+      <c r="P92" s="8" t="n"/>
+      <c r="Q92" s="8" t="n"/>
       <c r="R92" s="9" t="n"/>
       <c r="S92" s="9" t="n"/>
       <c r="T92" s="9" t="n"/>
       <c r="U92" s="9" t="n"/>
-      <c r="V92" s="9" t="n"/>
+      <c r="V92" s="10" t="n"/>
       <c r="W92" s="10" t="n"/>
       <c r="X92" s="10" t="n"/>
       <c r="Y92" s="10" t="n"/>
-      <c r="Z92" s="11" t="n"/>
-      <c r="AA92" s="11" t="n"/>
+      <c r="Z92" s="10" t="n"/>
+      <c r="AA92" s="10" t="n"/>
+      <c r="AB92" s="10" t="n"/>
+      <c r="AC92" s="11" t="n"/>
+      <c r="AD92" s="11" t="n"/>
+      <c r="AE92" s="11" t="n"/>
+      <c r="AF92" s="12" t="n"/>
+      <c r="AG92" s="12" t="n"/>
+      <c r="AH92" s="7" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="6" t="n"/>
@@ -3546,25 +4319,32 @@
       <c r="F93" s="7" t="n"/>
       <c r="G93" s="7" t="n"/>
       <c r="H93" s="7" t="n"/>
-      <c r="I93" s="7" t="n"/>
-      <c r="J93" s="7" t="n"/>
-      <c r="K93" s="7" t="n"/>
+      <c r="I93" s="8" t="n"/>
+      <c r="J93" s="8" t="n"/>
+      <c r="K93" s="8" t="n"/>
       <c r="L93" s="8" t="n"/>
       <c r="M93" s="8" t="n"/>
       <c r="N93" s="8" t="n"/>
       <c r="O93" s="8" t="n"/>
-      <c r="P93" s="9" t="n"/>
-      <c r="Q93" s="9" t="n"/>
+      <c r="P93" s="8" t="n"/>
+      <c r="Q93" s="8" t="n"/>
       <c r="R93" s="9" t="n"/>
       <c r="S93" s="9" t="n"/>
       <c r="T93" s="9" t="n"/>
       <c r="U93" s="9" t="n"/>
-      <c r="V93" s="9" t="n"/>
+      <c r="V93" s="10" t="n"/>
       <c r="W93" s="10" t="n"/>
       <c r="X93" s="10" t="n"/>
       <c r="Y93" s="10" t="n"/>
-      <c r="Z93" s="11" t="n"/>
-      <c r="AA93" s="11" t="n"/>
+      <c r="Z93" s="10" t="n"/>
+      <c r="AA93" s="10" t="n"/>
+      <c r="AB93" s="10" t="n"/>
+      <c r="AC93" s="11" t="n"/>
+      <c r="AD93" s="11" t="n"/>
+      <c r="AE93" s="11" t="n"/>
+      <c r="AF93" s="12" t="n"/>
+      <c r="AG93" s="12" t="n"/>
+      <c r="AH93" s="7" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="6" t="n"/>
@@ -3574,25 +4354,32 @@
       <c r="F94" s="7" t="n"/>
       <c r="G94" s="7" t="n"/>
       <c r="H94" s="7" t="n"/>
-      <c r="I94" s="7" t="n"/>
-      <c r="J94" s="7" t="n"/>
-      <c r="K94" s="7" t="n"/>
+      <c r="I94" s="8" t="n"/>
+      <c r="J94" s="8" t="n"/>
+      <c r="K94" s="8" t="n"/>
       <c r="L94" s="8" t="n"/>
       <c r="M94" s="8" t="n"/>
       <c r="N94" s="8" t="n"/>
       <c r="O94" s="8" t="n"/>
-      <c r="P94" s="9" t="n"/>
-      <c r="Q94" s="9" t="n"/>
+      <c r="P94" s="8" t="n"/>
+      <c r="Q94" s="8" t="n"/>
       <c r="R94" s="9" t="n"/>
       <c r="S94" s="9" t="n"/>
       <c r="T94" s="9" t="n"/>
       <c r="U94" s="9" t="n"/>
-      <c r="V94" s="9" t="n"/>
+      <c r="V94" s="10" t="n"/>
       <c r="W94" s="10" t="n"/>
       <c r="X94" s="10" t="n"/>
       <c r="Y94" s="10" t="n"/>
-      <c r="Z94" s="11" t="n"/>
-      <c r="AA94" s="11" t="n"/>
+      <c r="Z94" s="10" t="n"/>
+      <c r="AA94" s="10" t="n"/>
+      <c r="AB94" s="10" t="n"/>
+      <c r="AC94" s="11" t="n"/>
+      <c r="AD94" s="11" t="n"/>
+      <c r="AE94" s="11" t="n"/>
+      <c r="AF94" s="12" t="n"/>
+      <c r="AG94" s="12" t="n"/>
+      <c r="AH94" s="7" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="6" t="n"/>
@@ -3602,25 +4389,32 @@
       <c r="F95" s="7" t="n"/>
       <c r="G95" s="7" t="n"/>
       <c r="H95" s="7" t="n"/>
-      <c r="I95" s="7" t="n"/>
-      <c r="J95" s="7" t="n"/>
-      <c r="K95" s="7" t="n"/>
+      <c r="I95" s="8" t="n"/>
+      <c r="J95" s="8" t="n"/>
+      <c r="K95" s="8" t="n"/>
       <c r="L95" s="8" t="n"/>
       <c r="M95" s="8" t="n"/>
       <c r="N95" s="8" t="n"/>
       <c r="O95" s="8" t="n"/>
-      <c r="P95" s="9" t="n"/>
-      <c r="Q95" s="9" t="n"/>
+      <c r="P95" s="8" t="n"/>
+      <c r="Q95" s="8" t="n"/>
       <c r="R95" s="9" t="n"/>
       <c r="S95" s="9" t="n"/>
       <c r="T95" s="9" t="n"/>
       <c r="U95" s="9" t="n"/>
-      <c r="V95" s="9" t="n"/>
+      <c r="V95" s="10" t="n"/>
       <c r="W95" s="10" t="n"/>
       <c r="X95" s="10" t="n"/>
       <c r="Y95" s="10" t="n"/>
-      <c r="Z95" s="11" t="n"/>
-      <c r="AA95" s="11" t="n"/>
+      <c r="Z95" s="10" t="n"/>
+      <c r="AA95" s="10" t="n"/>
+      <c r="AB95" s="10" t="n"/>
+      <c r="AC95" s="11" t="n"/>
+      <c r="AD95" s="11" t="n"/>
+      <c r="AE95" s="11" t="n"/>
+      <c r="AF95" s="12" t="n"/>
+      <c r="AG95" s="12" t="n"/>
+      <c r="AH95" s="7" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="6" t="n"/>
@@ -3630,25 +4424,32 @@
       <c r="F96" s="7" t="n"/>
       <c r="G96" s="7" t="n"/>
       <c r="H96" s="7" t="n"/>
-      <c r="I96" s="7" t="n"/>
-      <c r="J96" s="7" t="n"/>
-      <c r="K96" s="7" t="n"/>
+      <c r="I96" s="8" t="n"/>
+      <c r="J96" s="8" t="n"/>
+      <c r="K96" s="8" t="n"/>
       <c r="L96" s="8" t="n"/>
       <c r="M96" s="8" t="n"/>
       <c r="N96" s="8" t="n"/>
       <c r="O96" s="8" t="n"/>
-      <c r="P96" s="9" t="n"/>
-      <c r="Q96" s="9" t="n"/>
+      <c r="P96" s="8" t="n"/>
+      <c r="Q96" s="8" t="n"/>
       <c r="R96" s="9" t="n"/>
       <c r="S96" s="9" t="n"/>
       <c r="T96" s="9" t="n"/>
       <c r="U96" s="9" t="n"/>
-      <c r="V96" s="9" t="n"/>
+      <c r="V96" s="10" t="n"/>
       <c r="W96" s="10" t="n"/>
       <c r="X96" s="10" t="n"/>
       <c r="Y96" s="10" t="n"/>
-      <c r="Z96" s="11" t="n"/>
-      <c r="AA96" s="11" t="n"/>
+      <c r="Z96" s="10" t="n"/>
+      <c r="AA96" s="10" t="n"/>
+      <c r="AB96" s="10" t="n"/>
+      <c r="AC96" s="11" t="n"/>
+      <c r="AD96" s="11" t="n"/>
+      <c r="AE96" s="11" t="n"/>
+      <c r="AF96" s="12" t="n"/>
+      <c r="AG96" s="12" t="n"/>
+      <c r="AH96" s="7" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="6" t="n"/>
@@ -3658,25 +4459,32 @@
       <c r="F97" s="7" t="n"/>
       <c r="G97" s="7" t="n"/>
       <c r="H97" s="7" t="n"/>
-      <c r="I97" s="7" t="n"/>
-      <c r="J97" s="7" t="n"/>
-      <c r="K97" s="7" t="n"/>
+      <c r="I97" s="8" t="n"/>
+      <c r="J97" s="8" t="n"/>
+      <c r="K97" s="8" t="n"/>
       <c r="L97" s="8" t="n"/>
       <c r="M97" s="8" t="n"/>
       <c r="N97" s="8" t="n"/>
       <c r="O97" s="8" t="n"/>
-      <c r="P97" s="9" t="n"/>
-      <c r="Q97" s="9" t="n"/>
+      <c r="P97" s="8" t="n"/>
+      <c r="Q97" s="8" t="n"/>
       <c r="R97" s="9" t="n"/>
       <c r="S97" s="9" t="n"/>
       <c r="T97" s="9" t="n"/>
       <c r="U97" s="9" t="n"/>
-      <c r="V97" s="9" t="n"/>
+      <c r="V97" s="10" t="n"/>
       <c r="W97" s="10" t="n"/>
       <c r="X97" s="10" t="n"/>
       <c r="Y97" s="10" t="n"/>
-      <c r="Z97" s="11" t="n"/>
-      <c r="AA97" s="11" t="n"/>
+      <c r="Z97" s="10" t="n"/>
+      <c r="AA97" s="10" t="n"/>
+      <c r="AB97" s="10" t="n"/>
+      <c r="AC97" s="11" t="n"/>
+      <c r="AD97" s="11" t="n"/>
+      <c r="AE97" s="11" t="n"/>
+      <c r="AF97" s="12" t="n"/>
+      <c r="AG97" s="12" t="n"/>
+      <c r="AH97" s="7" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="6" t="n"/>
@@ -3686,25 +4494,32 @@
       <c r="F98" s="7" t="n"/>
       <c r="G98" s="7" t="n"/>
       <c r="H98" s="7" t="n"/>
-      <c r="I98" s="7" t="n"/>
-      <c r="J98" s="7" t="n"/>
-      <c r="K98" s="7" t="n"/>
+      <c r="I98" s="8" t="n"/>
+      <c r="J98" s="8" t="n"/>
+      <c r="K98" s="8" t="n"/>
       <c r="L98" s="8" t="n"/>
       <c r="M98" s="8" t="n"/>
       <c r="N98" s="8" t="n"/>
       <c r="O98" s="8" t="n"/>
-      <c r="P98" s="9" t="n"/>
-      <c r="Q98" s="9" t="n"/>
+      <c r="P98" s="8" t="n"/>
+      <c r="Q98" s="8" t="n"/>
       <c r="R98" s="9" t="n"/>
       <c r="S98" s="9" t="n"/>
       <c r="T98" s="9" t="n"/>
       <c r="U98" s="9" t="n"/>
-      <c r="V98" s="9" t="n"/>
+      <c r="V98" s="10" t="n"/>
       <c r="W98" s="10" t="n"/>
       <c r="X98" s="10" t="n"/>
       <c r="Y98" s="10" t="n"/>
-      <c r="Z98" s="11" t="n"/>
-      <c r="AA98" s="11" t="n"/>
+      <c r="Z98" s="10" t="n"/>
+      <c r="AA98" s="10" t="n"/>
+      <c r="AB98" s="10" t="n"/>
+      <c r="AC98" s="11" t="n"/>
+      <c r="AD98" s="11" t="n"/>
+      <c r="AE98" s="11" t="n"/>
+      <c r="AF98" s="12" t="n"/>
+      <c r="AG98" s="12" t="n"/>
+      <c r="AH98" s="7" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="6" t="n"/>
@@ -3714,25 +4529,32 @@
       <c r="F99" s="7" t="n"/>
       <c r="G99" s="7" t="n"/>
       <c r="H99" s="7" t="n"/>
-      <c r="I99" s="7" t="n"/>
-      <c r="J99" s="7" t="n"/>
-      <c r="K99" s="7" t="n"/>
+      <c r="I99" s="8" t="n"/>
+      <c r="J99" s="8" t="n"/>
+      <c r="K99" s="8" t="n"/>
       <c r="L99" s="8" t="n"/>
       <c r="M99" s="8" t="n"/>
       <c r="N99" s="8" t="n"/>
       <c r="O99" s="8" t="n"/>
-      <c r="P99" s="9" t="n"/>
-      <c r="Q99" s="9" t="n"/>
+      <c r="P99" s="8" t="n"/>
+      <c r="Q99" s="8" t="n"/>
       <c r="R99" s="9" t="n"/>
       <c r="S99" s="9" t="n"/>
       <c r="T99" s="9" t="n"/>
       <c r="U99" s="9" t="n"/>
-      <c r="V99" s="9" t="n"/>
+      <c r="V99" s="10" t="n"/>
       <c r="W99" s="10" t="n"/>
       <c r="X99" s="10" t="n"/>
       <c r="Y99" s="10" t="n"/>
-      <c r="Z99" s="11" t="n"/>
-      <c r="AA99" s="11" t="n"/>
+      <c r="Z99" s="10" t="n"/>
+      <c r="AA99" s="10" t="n"/>
+      <c r="AB99" s="10" t="n"/>
+      <c r="AC99" s="11" t="n"/>
+      <c r="AD99" s="11" t="n"/>
+      <c r="AE99" s="11" t="n"/>
+      <c r="AF99" s="12" t="n"/>
+      <c r="AG99" s="12" t="n"/>
+      <c r="AH99" s="7" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="6" t="n"/>
@@ -3742,25 +4564,32 @@
       <c r="F100" s="7" t="n"/>
       <c r="G100" s="7" t="n"/>
       <c r="H100" s="7" t="n"/>
-      <c r="I100" s="7" t="n"/>
-      <c r="J100" s="7" t="n"/>
-      <c r="K100" s="7" t="n"/>
+      <c r="I100" s="8" t="n"/>
+      <c r="J100" s="8" t="n"/>
+      <c r="K100" s="8" t="n"/>
       <c r="L100" s="8" t="n"/>
       <c r="M100" s="8" t="n"/>
       <c r="N100" s="8" t="n"/>
       <c r="O100" s="8" t="n"/>
-      <c r="P100" s="9" t="n"/>
-      <c r="Q100" s="9" t="n"/>
+      <c r="P100" s="8" t="n"/>
+      <c r="Q100" s="8" t="n"/>
       <c r="R100" s="9" t="n"/>
       <c r="S100" s="9" t="n"/>
       <c r="T100" s="9" t="n"/>
       <c r="U100" s="9" t="n"/>
-      <c r="V100" s="9" t="n"/>
+      <c r="V100" s="10" t="n"/>
       <c r="W100" s="10" t="n"/>
       <c r="X100" s="10" t="n"/>
       <c r="Y100" s="10" t="n"/>
-      <c r="Z100" s="11" t="n"/>
-      <c r="AA100" s="11" t="n"/>
+      <c r="Z100" s="10" t="n"/>
+      <c r="AA100" s="10" t="n"/>
+      <c r="AB100" s="10" t="n"/>
+      <c r="AC100" s="11" t="n"/>
+      <c r="AD100" s="11" t="n"/>
+      <c r="AE100" s="11" t="n"/>
+      <c r="AF100" s="12" t="n"/>
+      <c r="AG100" s="12" t="n"/>
+      <c r="AH100" s="7" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="6" t="n"/>
@@ -3770,25 +4599,32 @@
       <c r="F101" s="7" t="n"/>
       <c r="G101" s="7" t="n"/>
       <c r="H101" s="7" t="n"/>
-      <c r="I101" s="7" t="n"/>
-      <c r="J101" s="7" t="n"/>
-      <c r="K101" s="7" t="n"/>
+      <c r="I101" s="8" t="n"/>
+      <c r="J101" s="8" t="n"/>
+      <c r="K101" s="8" t="n"/>
       <c r="L101" s="8" t="n"/>
       <c r="M101" s="8" t="n"/>
       <c r="N101" s="8" t="n"/>
       <c r="O101" s="8" t="n"/>
-      <c r="P101" s="9" t="n"/>
-      <c r="Q101" s="9" t="n"/>
+      <c r="P101" s="8" t="n"/>
+      <c r="Q101" s="8" t="n"/>
       <c r="R101" s="9" t="n"/>
       <c r="S101" s="9" t="n"/>
       <c r="T101" s="9" t="n"/>
       <c r="U101" s="9" t="n"/>
-      <c r="V101" s="9" t="n"/>
+      <c r="V101" s="10" t="n"/>
       <c r="W101" s="10" t="n"/>
       <c r="X101" s="10" t="n"/>
       <c r="Y101" s="10" t="n"/>
-      <c r="Z101" s="11" t="n"/>
-      <c r="AA101" s="11" t="n"/>
+      <c r="Z101" s="10" t="n"/>
+      <c r="AA101" s="10" t="n"/>
+      <c r="AB101" s="10" t="n"/>
+      <c r="AC101" s="11" t="n"/>
+      <c r="AD101" s="11" t="n"/>
+      <c r="AE101" s="11" t="n"/>
+      <c r="AF101" s="12" t="n"/>
+      <c r="AG101" s="12" t="n"/>
+      <c r="AH101" s="7" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="6" t="n"/>
@@ -3798,25 +4634,32 @@
       <c r="F102" s="7" t="n"/>
       <c r="G102" s="7" t="n"/>
       <c r="H102" s="7" t="n"/>
-      <c r="I102" s="7" t="n"/>
-      <c r="J102" s="7" t="n"/>
-      <c r="K102" s="7" t="n"/>
+      <c r="I102" s="8" t="n"/>
+      <c r="J102" s="8" t="n"/>
+      <c r="K102" s="8" t="n"/>
       <c r="L102" s="8" t="n"/>
       <c r="M102" s="8" t="n"/>
       <c r="N102" s="8" t="n"/>
       <c r="O102" s="8" t="n"/>
-      <c r="P102" s="9" t="n"/>
-      <c r="Q102" s="9" t="n"/>
+      <c r="P102" s="8" t="n"/>
+      <c r="Q102" s="8" t="n"/>
       <c r="R102" s="9" t="n"/>
       <c r="S102" s="9" t="n"/>
       <c r="T102" s="9" t="n"/>
       <c r="U102" s="9" t="n"/>
-      <c r="V102" s="9" t="n"/>
+      <c r="V102" s="10" t="n"/>
       <c r="W102" s="10" t="n"/>
       <c r="X102" s="10" t="n"/>
       <c r="Y102" s="10" t="n"/>
-      <c r="Z102" s="11" t="n"/>
-      <c r="AA102" s="11" t="n"/>
+      <c r="Z102" s="10" t="n"/>
+      <c r="AA102" s="10" t="n"/>
+      <c r="AB102" s="10" t="n"/>
+      <c r="AC102" s="11" t="n"/>
+      <c r="AD102" s="11" t="n"/>
+      <c r="AE102" s="11" t="n"/>
+      <c r="AF102" s="12" t="n"/>
+      <c r="AG102" s="12" t="n"/>
+      <c r="AH102" s="7" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="6" t="n"/>
@@ -3826,25 +4669,32 @@
       <c r="F103" s="7" t="n"/>
       <c r="G103" s="7" t="n"/>
       <c r="H103" s="7" t="n"/>
-      <c r="I103" s="7" t="n"/>
-      <c r="J103" s="7" t="n"/>
-      <c r="K103" s="7" t="n"/>
+      <c r="I103" s="8" t="n"/>
+      <c r="J103" s="8" t="n"/>
+      <c r="K103" s="8" t="n"/>
       <c r="L103" s="8" t="n"/>
       <c r="M103" s="8" t="n"/>
       <c r="N103" s="8" t="n"/>
       <c r="O103" s="8" t="n"/>
-      <c r="P103" s="9" t="n"/>
-      <c r="Q103" s="9" t="n"/>
+      <c r="P103" s="8" t="n"/>
+      <c r="Q103" s="8" t="n"/>
       <c r="R103" s="9" t="n"/>
       <c r="S103" s="9" t="n"/>
       <c r="T103" s="9" t="n"/>
       <c r="U103" s="9" t="n"/>
-      <c r="V103" s="9" t="n"/>
+      <c r="V103" s="10" t="n"/>
       <c r="W103" s="10" t="n"/>
       <c r="X103" s="10" t="n"/>
       <c r="Y103" s="10" t="n"/>
-      <c r="Z103" s="11" t="n"/>
-      <c r="AA103" s="11" t="n"/>
+      <c r="Z103" s="10" t="n"/>
+      <c r="AA103" s="10" t="n"/>
+      <c r="AB103" s="10" t="n"/>
+      <c r="AC103" s="11" t="n"/>
+      <c r="AD103" s="11" t="n"/>
+      <c r="AE103" s="11" t="n"/>
+      <c r="AF103" s="12" t="n"/>
+      <c r="AG103" s="12" t="n"/>
+      <c r="AH103" s="7" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="6" t="n"/>
@@ -3854,25 +4704,32 @@
       <c r="F104" s="7" t="n"/>
       <c r="G104" s="7" t="n"/>
       <c r="H104" s="7" t="n"/>
-      <c r="I104" s="7" t="n"/>
-      <c r="J104" s="7" t="n"/>
-      <c r="K104" s="7" t="n"/>
+      <c r="I104" s="8" t="n"/>
+      <c r="J104" s="8" t="n"/>
+      <c r="K104" s="8" t="n"/>
       <c r="L104" s="8" t="n"/>
       <c r="M104" s="8" t="n"/>
       <c r="N104" s="8" t="n"/>
       <c r="O104" s="8" t="n"/>
-      <c r="P104" s="9" t="n"/>
-      <c r="Q104" s="9" t="n"/>
+      <c r="P104" s="8" t="n"/>
+      <c r="Q104" s="8" t="n"/>
       <c r="R104" s="9" t="n"/>
       <c r="S104" s="9" t="n"/>
       <c r="T104" s="9" t="n"/>
       <c r="U104" s="9" t="n"/>
-      <c r="V104" s="9" t="n"/>
+      <c r="V104" s="10" t="n"/>
       <c r="W104" s="10" t="n"/>
       <c r="X104" s="10" t="n"/>
       <c r="Y104" s="10" t="n"/>
-      <c r="Z104" s="11" t="n"/>
-      <c r="AA104" s="11" t="n"/>
+      <c r="Z104" s="10" t="n"/>
+      <c r="AA104" s="10" t="n"/>
+      <c r="AB104" s="10" t="n"/>
+      <c r="AC104" s="11" t="n"/>
+      <c r="AD104" s="11" t="n"/>
+      <c r="AE104" s="11" t="n"/>
+      <c r="AF104" s="12" t="n"/>
+      <c r="AG104" s="12" t="n"/>
+      <c r="AH104" s="7" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="6" t="n"/>
@@ -3882,25 +4739,32 @@
       <c r="F105" s="7" t="n"/>
       <c r="G105" s="7" t="n"/>
       <c r="H105" s="7" t="n"/>
-      <c r="I105" s="7" t="n"/>
-      <c r="J105" s="7" t="n"/>
-      <c r="K105" s="7" t="n"/>
+      <c r="I105" s="8" t="n"/>
+      <c r="J105" s="8" t="n"/>
+      <c r="K105" s="8" t="n"/>
       <c r="L105" s="8" t="n"/>
       <c r="M105" s="8" t="n"/>
       <c r="N105" s="8" t="n"/>
       <c r="O105" s="8" t="n"/>
-      <c r="P105" s="9" t="n"/>
-      <c r="Q105" s="9" t="n"/>
+      <c r="P105" s="8" t="n"/>
+      <c r="Q105" s="8" t="n"/>
       <c r="R105" s="9" t="n"/>
       <c r="S105" s="9" t="n"/>
       <c r="T105" s="9" t="n"/>
       <c r="U105" s="9" t="n"/>
-      <c r="V105" s="9" t="n"/>
+      <c r="V105" s="10" t="n"/>
       <c r="W105" s="10" t="n"/>
       <c r="X105" s="10" t="n"/>
       <c r="Y105" s="10" t="n"/>
-      <c r="Z105" s="11" t="n"/>
-      <c r="AA105" s="11" t="n"/>
+      <c r="Z105" s="10" t="n"/>
+      <c r="AA105" s="10" t="n"/>
+      <c r="AB105" s="10" t="n"/>
+      <c r="AC105" s="11" t="n"/>
+      <c r="AD105" s="11" t="n"/>
+      <c r="AE105" s="11" t="n"/>
+      <c r="AF105" s="12" t="n"/>
+      <c r="AG105" s="12" t="n"/>
+      <c r="AH105" s="7" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="6" t="n"/>
@@ -3910,25 +4774,32 @@
       <c r="F106" s="7" t="n"/>
       <c r="G106" s="7" t="n"/>
       <c r="H106" s="7" t="n"/>
-      <c r="I106" s="7" t="n"/>
-      <c r="J106" s="7" t="n"/>
-      <c r="K106" s="7" t="n"/>
+      <c r="I106" s="8" t="n"/>
+      <c r="J106" s="8" t="n"/>
+      <c r="K106" s="8" t="n"/>
       <c r="L106" s="8" t="n"/>
       <c r="M106" s="8" t="n"/>
       <c r="N106" s="8" t="n"/>
       <c r="O106" s="8" t="n"/>
-      <c r="P106" s="9" t="n"/>
-      <c r="Q106" s="9" t="n"/>
+      <c r="P106" s="8" t="n"/>
+      <c r="Q106" s="8" t="n"/>
       <c r="R106" s="9" t="n"/>
       <c r="S106" s="9" t="n"/>
       <c r="T106" s="9" t="n"/>
       <c r="U106" s="9" t="n"/>
-      <c r="V106" s="9" t="n"/>
+      <c r="V106" s="10" t="n"/>
       <c r="W106" s="10" t="n"/>
       <c r="X106" s="10" t="n"/>
       <c r="Y106" s="10" t="n"/>
-      <c r="Z106" s="11" t="n"/>
-      <c r="AA106" s="11" t="n"/>
+      <c r="Z106" s="10" t="n"/>
+      <c r="AA106" s="10" t="n"/>
+      <c r="AB106" s="10" t="n"/>
+      <c r="AC106" s="11" t="n"/>
+      <c r="AD106" s="11" t="n"/>
+      <c r="AE106" s="11" t="n"/>
+      <c r="AF106" s="12" t="n"/>
+      <c r="AG106" s="12" t="n"/>
+      <c r="AH106" s="7" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="6" t="n"/>
@@ -3938,25 +4809,32 @@
       <c r="F107" s="7" t="n"/>
       <c r="G107" s="7" t="n"/>
       <c r="H107" s="7" t="n"/>
-      <c r="I107" s="7" t="n"/>
-      <c r="J107" s="7" t="n"/>
-      <c r="K107" s="7" t="n"/>
+      <c r="I107" s="8" t="n"/>
+      <c r="J107" s="8" t="n"/>
+      <c r="K107" s="8" t="n"/>
       <c r="L107" s="8" t="n"/>
       <c r="M107" s="8" t="n"/>
       <c r="N107" s="8" t="n"/>
       <c r="O107" s="8" t="n"/>
-      <c r="P107" s="9" t="n"/>
-      <c r="Q107" s="9" t="n"/>
+      <c r="P107" s="8" t="n"/>
+      <c r="Q107" s="8" t="n"/>
       <c r="R107" s="9" t="n"/>
       <c r="S107" s="9" t="n"/>
       <c r="T107" s="9" t="n"/>
       <c r="U107" s="9" t="n"/>
-      <c r="V107" s="9" t="n"/>
+      <c r="V107" s="10" t="n"/>
       <c r="W107" s="10" t="n"/>
       <c r="X107" s="10" t="n"/>
       <c r="Y107" s="10" t="n"/>
-      <c r="Z107" s="11" t="n"/>
-      <c r="AA107" s="11" t="n"/>
+      <c r="Z107" s="10" t="n"/>
+      <c r="AA107" s="10" t="n"/>
+      <c r="AB107" s="10" t="n"/>
+      <c r="AC107" s="11" t="n"/>
+      <c r="AD107" s="11" t="n"/>
+      <c r="AE107" s="11" t="n"/>
+      <c r="AF107" s="12" t="n"/>
+      <c r="AG107" s="12" t="n"/>
+      <c r="AH107" s="7" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="6" t="n"/>
@@ -3966,25 +4844,32 @@
       <c r="F108" s="7" t="n"/>
       <c r="G108" s="7" t="n"/>
       <c r="H108" s="7" t="n"/>
-      <c r="I108" s="7" t="n"/>
-      <c r="J108" s="7" t="n"/>
-      <c r="K108" s="7" t="n"/>
+      <c r="I108" s="8" t="n"/>
+      <c r="J108" s="8" t="n"/>
+      <c r="K108" s="8" t="n"/>
       <c r="L108" s="8" t="n"/>
       <c r="M108" s="8" t="n"/>
       <c r="N108" s="8" t="n"/>
       <c r="O108" s="8" t="n"/>
-      <c r="P108" s="9" t="n"/>
-      <c r="Q108" s="9" t="n"/>
+      <c r="P108" s="8" t="n"/>
+      <c r="Q108" s="8" t="n"/>
       <c r="R108" s="9" t="n"/>
       <c r="S108" s="9" t="n"/>
       <c r="T108" s="9" t="n"/>
       <c r="U108" s="9" t="n"/>
-      <c r="V108" s="9" t="n"/>
+      <c r="V108" s="10" t="n"/>
       <c r="W108" s="10" t="n"/>
       <c r="X108" s="10" t="n"/>
       <c r="Y108" s="10" t="n"/>
-      <c r="Z108" s="11" t="n"/>
-      <c r="AA108" s="11" t="n"/>
+      <c r="Z108" s="10" t="n"/>
+      <c r="AA108" s="10" t="n"/>
+      <c r="AB108" s="10" t="n"/>
+      <c r="AC108" s="11" t="n"/>
+      <c r="AD108" s="11" t="n"/>
+      <c r="AE108" s="11" t="n"/>
+      <c r="AF108" s="12" t="n"/>
+      <c r="AG108" s="12" t="n"/>
+      <c r="AH108" s="7" t="n"/>
     </row>
     <row r="109">
       <c r="A109" s="6" t="n"/>
@@ -3994,25 +4879,32 @@
       <c r="F109" s="7" t="n"/>
       <c r="G109" s="7" t="n"/>
       <c r="H109" s="7" t="n"/>
-      <c r="I109" s="7" t="n"/>
-      <c r="J109" s="7" t="n"/>
-      <c r="K109" s="7" t="n"/>
+      <c r="I109" s="8" t="n"/>
+      <c r="J109" s="8" t="n"/>
+      <c r="K109" s="8" t="n"/>
       <c r="L109" s="8" t="n"/>
       <c r="M109" s="8" t="n"/>
       <c r="N109" s="8" t="n"/>
       <c r="O109" s="8" t="n"/>
-      <c r="P109" s="9" t="n"/>
-      <c r="Q109" s="9" t="n"/>
+      <c r="P109" s="8" t="n"/>
+      <c r="Q109" s="8" t="n"/>
       <c r="R109" s="9" t="n"/>
       <c r="S109" s="9" t="n"/>
       <c r="T109" s="9" t="n"/>
       <c r="U109" s="9" t="n"/>
-      <c r="V109" s="9" t="n"/>
+      <c r="V109" s="10" t="n"/>
       <c r="W109" s="10" t="n"/>
       <c r="X109" s="10" t="n"/>
       <c r="Y109" s="10" t="n"/>
-      <c r="Z109" s="11" t="n"/>
-      <c r="AA109" s="11" t="n"/>
+      <c r="Z109" s="10" t="n"/>
+      <c r="AA109" s="10" t="n"/>
+      <c r="AB109" s="10" t="n"/>
+      <c r="AC109" s="11" t="n"/>
+      <c r="AD109" s="11" t="n"/>
+      <c r="AE109" s="11" t="n"/>
+      <c r="AF109" s="12" t="n"/>
+      <c r="AG109" s="12" t="n"/>
+      <c r="AH109" s="7" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="6" t="n"/>
@@ -4022,25 +4914,32 @@
       <c r="F110" s="7" t="n"/>
       <c r="G110" s="7" t="n"/>
       <c r="H110" s="7" t="n"/>
-      <c r="I110" s="7" t="n"/>
-      <c r="J110" s="7" t="n"/>
-      <c r="K110" s="7" t="n"/>
+      <c r="I110" s="8" t="n"/>
+      <c r="J110" s="8" t="n"/>
+      <c r="K110" s="8" t="n"/>
       <c r="L110" s="8" t="n"/>
       <c r="M110" s="8" t="n"/>
       <c r="N110" s="8" t="n"/>
       <c r="O110" s="8" t="n"/>
-      <c r="P110" s="9" t="n"/>
-      <c r="Q110" s="9" t="n"/>
+      <c r="P110" s="8" t="n"/>
+      <c r="Q110" s="8" t="n"/>
       <c r="R110" s="9" t="n"/>
       <c r="S110" s="9" t="n"/>
       <c r="T110" s="9" t="n"/>
       <c r="U110" s="9" t="n"/>
-      <c r="V110" s="9" t="n"/>
+      <c r="V110" s="10" t="n"/>
       <c r="W110" s="10" t="n"/>
       <c r="X110" s="10" t="n"/>
       <c r="Y110" s="10" t="n"/>
-      <c r="Z110" s="11" t="n"/>
-      <c r="AA110" s="11" t="n"/>
+      <c r="Z110" s="10" t="n"/>
+      <c r="AA110" s="10" t="n"/>
+      <c r="AB110" s="10" t="n"/>
+      <c r="AC110" s="11" t="n"/>
+      <c r="AD110" s="11" t="n"/>
+      <c r="AE110" s="11" t="n"/>
+      <c r="AF110" s="12" t="n"/>
+      <c r="AG110" s="12" t="n"/>
+      <c r="AH110" s="7" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="6" t="n"/>
@@ -4050,25 +4949,32 @@
       <c r="F111" s="7" t="n"/>
       <c r="G111" s="7" t="n"/>
       <c r="H111" s="7" t="n"/>
-      <c r="I111" s="7" t="n"/>
-      <c r="J111" s="7" t="n"/>
-      <c r="K111" s="7" t="n"/>
+      <c r="I111" s="8" t="n"/>
+      <c r="J111" s="8" t="n"/>
+      <c r="K111" s="8" t="n"/>
       <c r="L111" s="8" t="n"/>
       <c r="M111" s="8" t="n"/>
       <c r="N111" s="8" t="n"/>
       <c r="O111" s="8" t="n"/>
-      <c r="P111" s="9" t="n"/>
-      <c r="Q111" s="9" t="n"/>
+      <c r="P111" s="8" t="n"/>
+      <c r="Q111" s="8" t="n"/>
       <c r="R111" s="9" t="n"/>
       <c r="S111" s="9" t="n"/>
       <c r="T111" s="9" t="n"/>
       <c r="U111" s="9" t="n"/>
-      <c r="V111" s="9" t="n"/>
+      <c r="V111" s="10" t="n"/>
       <c r="W111" s="10" t="n"/>
       <c r="X111" s="10" t="n"/>
       <c r="Y111" s="10" t="n"/>
-      <c r="Z111" s="11" t="n"/>
-      <c r="AA111" s="11" t="n"/>
+      <c r="Z111" s="10" t="n"/>
+      <c r="AA111" s="10" t="n"/>
+      <c r="AB111" s="10" t="n"/>
+      <c r="AC111" s="11" t="n"/>
+      <c r="AD111" s="11" t="n"/>
+      <c r="AE111" s="11" t="n"/>
+      <c r="AF111" s="12" t="n"/>
+      <c r="AG111" s="12" t="n"/>
+      <c r="AH111" s="7" t="n"/>
     </row>
     <row r="112">
       <c r="A112" s="6" t="n"/>
@@ -4078,25 +4984,32 @@
       <c r="F112" s="7" t="n"/>
       <c r="G112" s="7" t="n"/>
       <c r="H112" s="7" t="n"/>
-      <c r="I112" s="7" t="n"/>
-      <c r="J112" s="7" t="n"/>
-      <c r="K112" s="7" t="n"/>
+      <c r="I112" s="8" t="n"/>
+      <c r="J112" s="8" t="n"/>
+      <c r="K112" s="8" t="n"/>
       <c r="L112" s="8" t="n"/>
       <c r="M112" s="8" t="n"/>
       <c r="N112" s="8" t="n"/>
       <c r="O112" s="8" t="n"/>
-      <c r="P112" s="9" t="n"/>
-      <c r="Q112" s="9" t="n"/>
+      <c r="P112" s="8" t="n"/>
+      <c r="Q112" s="8" t="n"/>
       <c r="R112" s="9" t="n"/>
       <c r="S112" s="9" t="n"/>
       <c r="T112" s="9" t="n"/>
       <c r="U112" s="9" t="n"/>
-      <c r="V112" s="9" t="n"/>
+      <c r="V112" s="10" t="n"/>
       <c r="W112" s="10" t="n"/>
       <c r="X112" s="10" t="n"/>
       <c r="Y112" s="10" t="n"/>
-      <c r="Z112" s="11" t="n"/>
-      <c r="AA112" s="11" t="n"/>
+      <c r="Z112" s="10" t="n"/>
+      <c r="AA112" s="10" t="n"/>
+      <c r="AB112" s="10" t="n"/>
+      <c r="AC112" s="11" t="n"/>
+      <c r="AD112" s="11" t="n"/>
+      <c r="AE112" s="11" t="n"/>
+      <c r="AF112" s="12" t="n"/>
+      <c r="AG112" s="12" t="n"/>
+      <c r="AH112" s="7" t="n"/>
     </row>
     <row r="113">
       <c r="A113" s="6" t="n"/>
@@ -4106,25 +5019,32 @@
       <c r="F113" s="7" t="n"/>
       <c r="G113" s="7" t="n"/>
       <c r="H113" s="7" t="n"/>
-      <c r="I113" s="7" t="n"/>
-      <c r="J113" s="7" t="n"/>
-      <c r="K113" s="7" t="n"/>
+      <c r="I113" s="8" t="n"/>
+      <c r="J113" s="8" t="n"/>
+      <c r="K113" s="8" t="n"/>
       <c r="L113" s="8" t="n"/>
       <c r="M113" s="8" t="n"/>
       <c r="N113" s="8" t="n"/>
       <c r="O113" s="8" t="n"/>
-      <c r="P113" s="9" t="n"/>
-      <c r="Q113" s="9" t="n"/>
+      <c r="P113" s="8" t="n"/>
+      <c r="Q113" s="8" t="n"/>
       <c r="R113" s="9" t="n"/>
       <c r="S113" s="9" t="n"/>
       <c r="T113" s="9" t="n"/>
       <c r="U113" s="9" t="n"/>
-      <c r="V113" s="9" t="n"/>
+      <c r="V113" s="10" t="n"/>
       <c r="W113" s="10" t="n"/>
       <c r="X113" s="10" t="n"/>
       <c r="Y113" s="10" t="n"/>
-      <c r="Z113" s="11" t="n"/>
-      <c r="AA113" s="11" t="n"/>
+      <c r="Z113" s="10" t="n"/>
+      <c r="AA113" s="10" t="n"/>
+      <c r="AB113" s="10" t="n"/>
+      <c r="AC113" s="11" t="n"/>
+      <c r="AD113" s="11" t="n"/>
+      <c r="AE113" s="11" t="n"/>
+      <c r="AF113" s="12" t="n"/>
+      <c r="AG113" s="12" t="n"/>
+      <c r="AH113" s="7" t="n"/>
     </row>
     <row r="114">
       <c r="A114" s="6" t="n"/>
@@ -4134,25 +5054,32 @@
       <c r="F114" s="7" t="n"/>
       <c r="G114" s="7" t="n"/>
       <c r="H114" s="7" t="n"/>
-      <c r="I114" s="7" t="n"/>
-      <c r="J114" s="7" t="n"/>
-      <c r="K114" s="7" t="n"/>
+      <c r="I114" s="8" t="n"/>
+      <c r="J114" s="8" t="n"/>
+      <c r="K114" s="8" t="n"/>
       <c r="L114" s="8" t="n"/>
       <c r="M114" s="8" t="n"/>
       <c r="N114" s="8" t="n"/>
       <c r="O114" s="8" t="n"/>
-      <c r="P114" s="9" t="n"/>
-      <c r="Q114" s="9" t="n"/>
+      <c r="P114" s="8" t="n"/>
+      <c r="Q114" s="8" t="n"/>
       <c r="R114" s="9" t="n"/>
       <c r="S114" s="9" t="n"/>
       <c r="T114" s="9" t="n"/>
       <c r="U114" s="9" t="n"/>
-      <c r="V114" s="9" t="n"/>
+      <c r="V114" s="10" t="n"/>
       <c r="W114" s="10" t="n"/>
       <c r="X114" s="10" t="n"/>
       <c r="Y114" s="10" t="n"/>
-      <c r="Z114" s="11" t="n"/>
-      <c r="AA114" s="11" t="n"/>
+      <c r="Z114" s="10" t="n"/>
+      <c r="AA114" s="10" t="n"/>
+      <c r="AB114" s="10" t="n"/>
+      <c r="AC114" s="11" t="n"/>
+      <c r="AD114" s="11" t="n"/>
+      <c r="AE114" s="11" t="n"/>
+      <c r="AF114" s="12" t="n"/>
+      <c r="AG114" s="12" t="n"/>
+      <c r="AH114" s="7" t="n"/>
     </row>
     <row r="115">
       <c r="A115" s="6" t="n"/>
@@ -4162,25 +5089,32 @@
       <c r="F115" s="7" t="n"/>
       <c r="G115" s="7" t="n"/>
       <c r="H115" s="7" t="n"/>
-      <c r="I115" s="7" t="n"/>
-      <c r="J115" s="7" t="n"/>
-      <c r="K115" s="7" t="n"/>
+      <c r="I115" s="8" t="n"/>
+      <c r="J115" s="8" t="n"/>
+      <c r="K115" s="8" t="n"/>
       <c r="L115" s="8" t="n"/>
       <c r="M115" s="8" t="n"/>
       <c r="N115" s="8" t="n"/>
       <c r="O115" s="8" t="n"/>
-      <c r="P115" s="9" t="n"/>
-      <c r="Q115" s="9" t="n"/>
+      <c r="P115" s="8" t="n"/>
+      <c r="Q115" s="8" t="n"/>
       <c r="R115" s="9" t="n"/>
       <c r="S115" s="9" t="n"/>
       <c r="T115" s="9" t="n"/>
       <c r="U115" s="9" t="n"/>
-      <c r="V115" s="9" t="n"/>
+      <c r="V115" s="10" t="n"/>
       <c r="W115" s="10" t="n"/>
       <c r="X115" s="10" t="n"/>
       <c r="Y115" s="10" t="n"/>
-      <c r="Z115" s="11" t="n"/>
-      <c r="AA115" s="11" t="n"/>
+      <c r="Z115" s="10" t="n"/>
+      <c r="AA115" s="10" t="n"/>
+      <c r="AB115" s="10" t="n"/>
+      <c r="AC115" s="11" t="n"/>
+      <c r="AD115" s="11" t="n"/>
+      <c r="AE115" s="11" t="n"/>
+      <c r="AF115" s="12" t="n"/>
+      <c r="AG115" s="12" t="n"/>
+      <c r="AH115" s="7" t="n"/>
     </row>
     <row r="116">
       <c r="A116" s="6" t="n"/>
@@ -4190,25 +5124,32 @@
       <c r="F116" s="7" t="n"/>
       <c r="G116" s="7" t="n"/>
       <c r="H116" s="7" t="n"/>
-      <c r="I116" s="7" t="n"/>
-      <c r="J116" s="7" t="n"/>
-      <c r="K116" s="7" t="n"/>
+      <c r="I116" s="8" t="n"/>
+      <c r="J116" s="8" t="n"/>
+      <c r="K116" s="8" t="n"/>
       <c r="L116" s="8" t="n"/>
       <c r="M116" s="8" t="n"/>
       <c r="N116" s="8" t="n"/>
       <c r="O116" s="8" t="n"/>
-      <c r="P116" s="9" t="n"/>
-      <c r="Q116" s="9" t="n"/>
+      <c r="P116" s="8" t="n"/>
+      <c r="Q116" s="8" t="n"/>
       <c r="R116" s="9" t="n"/>
       <c r="S116" s="9" t="n"/>
       <c r="T116" s="9" t="n"/>
       <c r="U116" s="9" t="n"/>
-      <c r="V116" s="9" t="n"/>
+      <c r="V116" s="10" t="n"/>
       <c r="W116" s="10" t="n"/>
       <c r="X116" s="10" t="n"/>
       <c r="Y116" s="10" t="n"/>
-      <c r="Z116" s="11" t="n"/>
-      <c r="AA116" s="11" t="n"/>
+      <c r="Z116" s="10" t="n"/>
+      <c r="AA116" s="10" t="n"/>
+      <c r="AB116" s="10" t="n"/>
+      <c r="AC116" s="11" t="n"/>
+      <c r="AD116" s="11" t="n"/>
+      <c r="AE116" s="11" t="n"/>
+      <c r="AF116" s="12" t="n"/>
+      <c r="AG116" s="12" t="n"/>
+      <c r="AH116" s="7" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="6" t="n"/>
@@ -4218,25 +5159,32 @@
       <c r="F117" s="7" t="n"/>
       <c r="G117" s="7" t="n"/>
       <c r="H117" s="7" t="n"/>
-      <c r="I117" s="7" t="n"/>
-      <c r="J117" s="7" t="n"/>
-      <c r="K117" s="7" t="n"/>
+      <c r="I117" s="8" t="n"/>
+      <c r="J117" s="8" t="n"/>
+      <c r="K117" s="8" t="n"/>
       <c r="L117" s="8" t="n"/>
       <c r="M117" s="8" t="n"/>
       <c r="N117" s="8" t="n"/>
       <c r="O117" s="8" t="n"/>
-      <c r="P117" s="9" t="n"/>
-      <c r="Q117" s="9" t="n"/>
+      <c r="P117" s="8" t="n"/>
+      <c r="Q117" s="8" t="n"/>
       <c r="R117" s="9" t="n"/>
       <c r="S117" s="9" t="n"/>
       <c r="T117" s="9" t="n"/>
       <c r="U117" s="9" t="n"/>
-      <c r="V117" s="9" t="n"/>
+      <c r="V117" s="10" t="n"/>
       <c r="W117" s="10" t="n"/>
       <c r="X117" s="10" t="n"/>
       <c r="Y117" s="10" t="n"/>
-      <c r="Z117" s="11" t="n"/>
-      <c r="AA117" s="11" t="n"/>
+      <c r="Z117" s="10" t="n"/>
+      <c r="AA117" s="10" t="n"/>
+      <c r="AB117" s="10" t="n"/>
+      <c r="AC117" s="11" t="n"/>
+      <c r="AD117" s="11" t="n"/>
+      <c r="AE117" s="11" t="n"/>
+      <c r="AF117" s="12" t="n"/>
+      <c r="AG117" s="12" t="n"/>
+      <c r="AH117" s="7" t="n"/>
     </row>
     <row r="118">
       <c r="A118" s="6" t="n"/>
@@ -4246,25 +5194,32 @@
       <c r="F118" s="7" t="n"/>
       <c r="G118" s="7" t="n"/>
       <c r="H118" s="7" t="n"/>
-      <c r="I118" s="7" t="n"/>
-      <c r="J118" s="7" t="n"/>
-      <c r="K118" s="7" t="n"/>
+      <c r="I118" s="8" t="n"/>
+      <c r="J118" s="8" t="n"/>
+      <c r="K118" s="8" t="n"/>
       <c r="L118" s="8" t="n"/>
       <c r="M118" s="8" t="n"/>
       <c r="N118" s="8" t="n"/>
       <c r="O118" s="8" t="n"/>
-      <c r="P118" s="9" t="n"/>
-      <c r="Q118" s="9" t="n"/>
+      <c r="P118" s="8" t="n"/>
+      <c r="Q118" s="8" t="n"/>
       <c r="R118" s="9" t="n"/>
       <c r="S118" s="9" t="n"/>
       <c r="T118" s="9" t="n"/>
       <c r="U118" s="9" t="n"/>
-      <c r="V118" s="9" t="n"/>
+      <c r="V118" s="10" t="n"/>
       <c r="W118" s="10" t="n"/>
       <c r="X118" s="10" t="n"/>
       <c r="Y118" s="10" t="n"/>
-      <c r="Z118" s="11" t="n"/>
-      <c r="AA118" s="11" t="n"/>
+      <c r="Z118" s="10" t="n"/>
+      <c r="AA118" s="10" t="n"/>
+      <c r="AB118" s="10" t="n"/>
+      <c r="AC118" s="11" t="n"/>
+      <c r="AD118" s="11" t="n"/>
+      <c r="AE118" s="11" t="n"/>
+      <c r="AF118" s="12" t="n"/>
+      <c r="AG118" s="12" t="n"/>
+      <c r="AH118" s="7" t="n"/>
     </row>
     <row r="119">
       <c r="A119" s="6" t="n"/>
@@ -4274,25 +5229,32 @@
       <c r="F119" s="7" t="n"/>
       <c r="G119" s="7" t="n"/>
       <c r="H119" s="7" t="n"/>
-      <c r="I119" s="7" t="n"/>
-      <c r="J119" s="7" t="n"/>
-      <c r="K119" s="7" t="n"/>
+      <c r="I119" s="8" t="n"/>
+      <c r="J119" s="8" t="n"/>
+      <c r="K119" s="8" t="n"/>
       <c r="L119" s="8" t="n"/>
       <c r="M119" s="8" t="n"/>
       <c r="N119" s="8" t="n"/>
       <c r="O119" s="8" t="n"/>
-      <c r="P119" s="9" t="n"/>
-      <c r="Q119" s="9" t="n"/>
+      <c r="P119" s="8" t="n"/>
+      <c r="Q119" s="8" t="n"/>
       <c r="R119" s="9" t="n"/>
       <c r="S119" s="9" t="n"/>
       <c r="T119" s="9" t="n"/>
       <c r="U119" s="9" t="n"/>
-      <c r="V119" s="9" t="n"/>
+      <c r="V119" s="10" t="n"/>
       <c r="W119" s="10" t="n"/>
       <c r="X119" s="10" t="n"/>
       <c r="Y119" s="10" t="n"/>
-      <c r="Z119" s="11" t="n"/>
-      <c r="AA119" s="11" t="n"/>
+      <c r="Z119" s="10" t="n"/>
+      <c r="AA119" s="10" t="n"/>
+      <c r="AB119" s="10" t="n"/>
+      <c r="AC119" s="11" t="n"/>
+      <c r="AD119" s="11" t="n"/>
+      <c r="AE119" s="11" t="n"/>
+      <c r="AF119" s="12" t="n"/>
+      <c r="AG119" s="12" t="n"/>
+      <c r="AH119" s="7" t="n"/>
     </row>
     <row r="120">
       <c r="A120" s="6" t="n"/>
@@ -4302,25 +5264,32 @@
       <c r="F120" s="7" t="n"/>
       <c r="G120" s="7" t="n"/>
       <c r="H120" s="7" t="n"/>
-      <c r="I120" s="7" t="n"/>
-      <c r="J120" s="7" t="n"/>
-      <c r="K120" s="7" t="n"/>
+      <c r="I120" s="8" t="n"/>
+      <c r="J120" s="8" t="n"/>
+      <c r="K120" s="8" t="n"/>
       <c r="L120" s="8" t="n"/>
       <c r="M120" s="8" t="n"/>
       <c r="N120" s="8" t="n"/>
       <c r="O120" s="8" t="n"/>
-      <c r="P120" s="9" t="n"/>
-      <c r="Q120" s="9" t="n"/>
+      <c r="P120" s="8" t="n"/>
+      <c r="Q120" s="8" t="n"/>
       <c r="R120" s="9" t="n"/>
       <c r="S120" s="9" t="n"/>
       <c r="T120" s="9" t="n"/>
       <c r="U120" s="9" t="n"/>
-      <c r="V120" s="9" t="n"/>
+      <c r="V120" s="10" t="n"/>
       <c r="W120" s="10" t="n"/>
       <c r="X120" s="10" t="n"/>
       <c r="Y120" s="10" t="n"/>
-      <c r="Z120" s="11" t="n"/>
-      <c r="AA120" s="11" t="n"/>
+      <c r="Z120" s="10" t="n"/>
+      <c r="AA120" s="10" t="n"/>
+      <c r="AB120" s="10" t="n"/>
+      <c r="AC120" s="11" t="n"/>
+      <c r="AD120" s="11" t="n"/>
+      <c r="AE120" s="11" t="n"/>
+      <c r="AF120" s="12" t="n"/>
+      <c r="AG120" s="12" t="n"/>
+      <c r="AH120" s="7" t="n"/>
     </row>
     <row r="121">
       <c r="A121" s="6" t="n"/>
@@ -4330,25 +5299,32 @@
       <c r="F121" s="7" t="n"/>
       <c r="G121" s="7" t="n"/>
       <c r="H121" s="7" t="n"/>
-      <c r="I121" s="7" t="n"/>
-      <c r="J121" s="7" t="n"/>
-      <c r="K121" s="7" t="n"/>
+      <c r="I121" s="8" t="n"/>
+      <c r="J121" s="8" t="n"/>
+      <c r="K121" s="8" t="n"/>
       <c r="L121" s="8" t="n"/>
       <c r="M121" s="8" t="n"/>
       <c r="N121" s="8" t="n"/>
       <c r="O121" s="8" t="n"/>
-      <c r="P121" s="9" t="n"/>
-      <c r="Q121" s="9" t="n"/>
+      <c r="P121" s="8" t="n"/>
+      <c r="Q121" s="8" t="n"/>
       <c r="R121" s="9" t="n"/>
       <c r="S121" s="9" t="n"/>
       <c r="T121" s="9" t="n"/>
       <c r="U121" s="9" t="n"/>
-      <c r="V121" s="9" t="n"/>
+      <c r="V121" s="10" t="n"/>
       <c r="W121" s="10" t="n"/>
       <c r="X121" s="10" t="n"/>
       <c r="Y121" s="10" t="n"/>
-      <c r="Z121" s="11" t="n"/>
-      <c r="AA121" s="11" t="n"/>
+      <c r="Z121" s="10" t="n"/>
+      <c r="AA121" s="10" t="n"/>
+      <c r="AB121" s="10" t="n"/>
+      <c r="AC121" s="11" t="n"/>
+      <c r="AD121" s="11" t="n"/>
+      <c r="AE121" s="11" t="n"/>
+      <c r="AF121" s="12" t="n"/>
+      <c r="AG121" s="12" t="n"/>
+      <c r="AH121" s="7" t="n"/>
     </row>
     <row r="122">
       <c r="A122" s="6" t="n"/>
@@ -4358,25 +5334,32 @@
       <c r="F122" s="7" t="n"/>
       <c r="G122" s="7" t="n"/>
       <c r="H122" s="7" t="n"/>
-      <c r="I122" s="7" t="n"/>
-      <c r="J122" s="7" t="n"/>
-      <c r="K122" s="7" t="n"/>
+      <c r="I122" s="8" t="n"/>
+      <c r="J122" s="8" t="n"/>
+      <c r="K122" s="8" t="n"/>
       <c r="L122" s="8" t="n"/>
       <c r="M122" s="8" t="n"/>
       <c r="N122" s="8" t="n"/>
       <c r="O122" s="8" t="n"/>
-      <c r="P122" s="9" t="n"/>
-      <c r="Q122" s="9" t="n"/>
+      <c r="P122" s="8" t="n"/>
+      <c r="Q122" s="8" t="n"/>
       <c r="R122" s="9" t="n"/>
       <c r="S122" s="9" t="n"/>
       <c r="T122" s="9" t="n"/>
       <c r="U122" s="9" t="n"/>
-      <c r="V122" s="9" t="n"/>
+      <c r="V122" s="10" t="n"/>
       <c r="W122" s="10" t="n"/>
       <c r="X122" s="10" t="n"/>
       <c r="Y122" s="10" t="n"/>
-      <c r="Z122" s="11" t="n"/>
-      <c r="AA122" s="11" t="n"/>
+      <c r="Z122" s="10" t="n"/>
+      <c r="AA122" s="10" t="n"/>
+      <c r="AB122" s="10" t="n"/>
+      <c r="AC122" s="11" t="n"/>
+      <c r="AD122" s="11" t="n"/>
+      <c r="AE122" s="11" t="n"/>
+      <c r="AF122" s="12" t="n"/>
+      <c r="AG122" s="12" t="n"/>
+      <c r="AH122" s="7" t="n"/>
     </row>
     <row r="123">
       <c r="A123" s="6" t="n"/>
@@ -4386,25 +5369,32 @@
       <c r="F123" s="7" t="n"/>
       <c r="G123" s="7" t="n"/>
       <c r="H123" s="7" t="n"/>
-      <c r="I123" s="7" t="n"/>
-      <c r="J123" s="7" t="n"/>
-      <c r="K123" s="7" t="n"/>
+      <c r="I123" s="8" t="n"/>
+      <c r="J123" s="8" t="n"/>
+      <c r="K123" s="8" t="n"/>
       <c r="L123" s="8" t="n"/>
       <c r="M123" s="8" t="n"/>
       <c r="N123" s="8" t="n"/>
       <c r="O123" s="8" t="n"/>
-      <c r="P123" s="9" t="n"/>
-      <c r="Q123" s="9" t="n"/>
+      <c r="P123" s="8" t="n"/>
+      <c r="Q123" s="8" t="n"/>
       <c r="R123" s="9" t="n"/>
       <c r="S123" s="9" t="n"/>
       <c r="T123" s="9" t="n"/>
       <c r="U123" s="9" t="n"/>
-      <c r="V123" s="9" t="n"/>
+      <c r="V123" s="10" t="n"/>
       <c r="W123" s="10" t="n"/>
       <c r="X123" s="10" t="n"/>
       <c r="Y123" s="10" t="n"/>
-      <c r="Z123" s="11" t="n"/>
-      <c r="AA123" s="11" t="n"/>
+      <c r="Z123" s="10" t="n"/>
+      <c r="AA123" s="10" t="n"/>
+      <c r="AB123" s="10" t="n"/>
+      <c r="AC123" s="11" t="n"/>
+      <c r="AD123" s="11" t="n"/>
+      <c r="AE123" s="11" t="n"/>
+      <c r="AF123" s="12" t="n"/>
+      <c r="AG123" s="12" t="n"/>
+      <c r="AH123" s="7" t="n"/>
     </row>
     <row r="124">
       <c r="A124" s="6" t="n"/>
@@ -4414,25 +5404,32 @@
       <c r="F124" s="7" t="n"/>
       <c r="G124" s="7" t="n"/>
       <c r="H124" s="7" t="n"/>
-      <c r="I124" s="7" t="n"/>
-      <c r="J124" s="7" t="n"/>
-      <c r="K124" s="7" t="n"/>
+      <c r="I124" s="8" t="n"/>
+      <c r="J124" s="8" t="n"/>
+      <c r="K124" s="8" t="n"/>
       <c r="L124" s="8" t="n"/>
       <c r="M124" s="8" t="n"/>
       <c r="N124" s="8" t="n"/>
       <c r="O124" s="8" t="n"/>
-      <c r="P124" s="9" t="n"/>
-      <c r="Q124" s="9" t="n"/>
+      <c r="P124" s="8" t="n"/>
+      <c r="Q124" s="8" t="n"/>
       <c r="R124" s="9" t="n"/>
       <c r="S124" s="9" t="n"/>
       <c r="T124" s="9" t="n"/>
       <c r="U124" s="9" t="n"/>
-      <c r="V124" s="9" t="n"/>
+      <c r="V124" s="10" t="n"/>
       <c r="W124" s="10" t="n"/>
       <c r="X124" s="10" t="n"/>
       <c r="Y124" s="10" t="n"/>
-      <c r="Z124" s="11" t="n"/>
-      <c r="AA124" s="11" t="n"/>
+      <c r="Z124" s="10" t="n"/>
+      <c r="AA124" s="10" t="n"/>
+      <c r="AB124" s="10" t="n"/>
+      <c r="AC124" s="11" t="n"/>
+      <c r="AD124" s="11" t="n"/>
+      <c r="AE124" s="11" t="n"/>
+      <c r="AF124" s="12" t="n"/>
+      <c r="AG124" s="12" t="n"/>
+      <c r="AH124" s="7" t="n"/>
     </row>
     <row r="125">
       <c r="A125" s="6" t="n"/>
@@ -4442,25 +5439,32 @@
       <c r="F125" s="7" t="n"/>
       <c r="G125" s="7" t="n"/>
       <c r="H125" s="7" t="n"/>
-      <c r="I125" s="7" t="n"/>
-      <c r="J125" s="7" t="n"/>
-      <c r="K125" s="7" t="n"/>
+      <c r="I125" s="8" t="n"/>
+      <c r="J125" s="8" t="n"/>
+      <c r="K125" s="8" t="n"/>
       <c r="L125" s="8" t="n"/>
       <c r="M125" s="8" t="n"/>
       <c r="N125" s="8" t="n"/>
       <c r="O125" s="8" t="n"/>
-      <c r="P125" s="9" t="n"/>
-      <c r="Q125" s="9" t="n"/>
+      <c r="P125" s="8" t="n"/>
+      <c r="Q125" s="8" t="n"/>
       <c r="R125" s="9" t="n"/>
       <c r="S125" s="9" t="n"/>
       <c r="T125" s="9" t="n"/>
       <c r="U125" s="9" t="n"/>
-      <c r="V125" s="9" t="n"/>
+      <c r="V125" s="10" t="n"/>
       <c r="W125" s="10" t="n"/>
       <c r="X125" s="10" t="n"/>
       <c r="Y125" s="10" t="n"/>
-      <c r="Z125" s="11" t="n"/>
-      <c r="AA125" s="11" t="n"/>
+      <c r="Z125" s="10" t="n"/>
+      <c r="AA125" s="10" t="n"/>
+      <c r="AB125" s="10" t="n"/>
+      <c r="AC125" s="11" t="n"/>
+      <c r="AD125" s="11" t="n"/>
+      <c r="AE125" s="11" t="n"/>
+      <c r="AF125" s="12" t="n"/>
+      <c r="AG125" s="12" t="n"/>
+      <c r="AH125" s="7" t="n"/>
     </row>
     <row r="126">
       <c r="A126" s="6" t="n"/>
@@ -4470,25 +5474,32 @@
       <c r="F126" s="7" t="n"/>
       <c r="G126" s="7" t="n"/>
       <c r="H126" s="7" t="n"/>
-      <c r="I126" s="7" t="n"/>
-      <c r="J126" s="7" t="n"/>
-      <c r="K126" s="7" t="n"/>
+      <c r="I126" s="8" t="n"/>
+      <c r="J126" s="8" t="n"/>
+      <c r="K126" s="8" t="n"/>
       <c r="L126" s="8" t="n"/>
       <c r="M126" s="8" t="n"/>
       <c r="N126" s="8" t="n"/>
       <c r="O126" s="8" t="n"/>
-      <c r="P126" s="9" t="n"/>
-      <c r="Q126" s="9" t="n"/>
+      <c r="P126" s="8" t="n"/>
+      <c r="Q126" s="8" t="n"/>
       <c r="R126" s="9" t="n"/>
       <c r="S126" s="9" t="n"/>
       <c r="T126" s="9" t="n"/>
       <c r="U126" s="9" t="n"/>
-      <c r="V126" s="9" t="n"/>
+      <c r="V126" s="10" t="n"/>
       <c r="W126" s="10" t="n"/>
       <c r="X126" s="10" t="n"/>
       <c r="Y126" s="10" t="n"/>
-      <c r="Z126" s="11" t="n"/>
-      <c r="AA126" s="11" t="n"/>
+      <c r="Z126" s="10" t="n"/>
+      <c r="AA126" s="10" t="n"/>
+      <c r="AB126" s="10" t="n"/>
+      <c r="AC126" s="11" t="n"/>
+      <c r="AD126" s="11" t="n"/>
+      <c r="AE126" s="11" t="n"/>
+      <c r="AF126" s="12" t="n"/>
+      <c r="AG126" s="12" t="n"/>
+      <c r="AH126" s="7" t="n"/>
     </row>
     <row r="127">
       <c r="A127" s="6" t="n"/>
@@ -4498,25 +5509,32 @@
       <c r="F127" s="7" t="n"/>
       <c r="G127" s="7" t="n"/>
       <c r="H127" s="7" t="n"/>
-      <c r="I127" s="7" t="n"/>
-      <c r="J127" s="7" t="n"/>
-      <c r="K127" s="7" t="n"/>
+      <c r="I127" s="8" t="n"/>
+      <c r="J127" s="8" t="n"/>
+      <c r="K127" s="8" t="n"/>
       <c r="L127" s="8" t="n"/>
       <c r="M127" s="8" t="n"/>
       <c r="N127" s="8" t="n"/>
       <c r="O127" s="8" t="n"/>
-      <c r="P127" s="9" t="n"/>
-      <c r="Q127" s="9" t="n"/>
+      <c r="P127" s="8" t="n"/>
+      <c r="Q127" s="8" t="n"/>
       <c r="R127" s="9" t="n"/>
       <c r="S127" s="9" t="n"/>
       <c r="T127" s="9" t="n"/>
       <c r="U127" s="9" t="n"/>
-      <c r="V127" s="9" t="n"/>
+      <c r="V127" s="10" t="n"/>
       <c r="W127" s="10" t="n"/>
       <c r="X127" s="10" t="n"/>
       <c r="Y127" s="10" t="n"/>
-      <c r="Z127" s="11" t="n"/>
-      <c r="AA127" s="11" t="n"/>
+      <c r="Z127" s="10" t="n"/>
+      <c r="AA127" s="10" t="n"/>
+      <c r="AB127" s="10" t="n"/>
+      <c r="AC127" s="11" t="n"/>
+      <c r="AD127" s="11" t="n"/>
+      <c r="AE127" s="11" t="n"/>
+      <c r="AF127" s="12" t="n"/>
+      <c r="AG127" s="12" t="n"/>
+      <c r="AH127" s="7" t="n"/>
     </row>
     <row r="128">
       <c r="A128" s="6" t="n"/>
@@ -4526,25 +5544,32 @@
       <c r="F128" s="7" t="n"/>
       <c r="G128" s="7" t="n"/>
       <c r="H128" s="7" t="n"/>
-      <c r="I128" s="7" t="n"/>
-      <c r="J128" s="7" t="n"/>
-      <c r="K128" s="7" t="n"/>
+      <c r="I128" s="8" t="n"/>
+      <c r="J128" s="8" t="n"/>
+      <c r="K128" s="8" t="n"/>
       <c r="L128" s="8" t="n"/>
       <c r="M128" s="8" t="n"/>
       <c r="N128" s="8" t="n"/>
       <c r="O128" s="8" t="n"/>
-      <c r="P128" s="9" t="n"/>
-      <c r="Q128" s="9" t="n"/>
+      <c r="P128" s="8" t="n"/>
+      <c r="Q128" s="8" t="n"/>
       <c r="R128" s="9" t="n"/>
       <c r="S128" s="9" t="n"/>
       <c r="T128" s="9" t="n"/>
       <c r="U128" s="9" t="n"/>
-      <c r="V128" s="9" t="n"/>
+      <c r="V128" s="10" t="n"/>
       <c r="W128" s="10" t="n"/>
       <c r="X128" s="10" t="n"/>
       <c r="Y128" s="10" t="n"/>
-      <c r="Z128" s="11" t="n"/>
-      <c r="AA128" s="11" t="n"/>
+      <c r="Z128" s="10" t="n"/>
+      <c r="AA128" s="10" t="n"/>
+      <c r="AB128" s="10" t="n"/>
+      <c r="AC128" s="11" t="n"/>
+      <c r="AD128" s="11" t="n"/>
+      <c r="AE128" s="11" t="n"/>
+      <c r="AF128" s="12" t="n"/>
+      <c r="AG128" s="12" t="n"/>
+      <c r="AH128" s="7" t="n"/>
     </row>
     <row r="129">
       <c r="A129" s="6" t="n"/>
@@ -4554,25 +5579,32 @@
       <c r="F129" s="7" t="n"/>
       <c r="G129" s="7" t="n"/>
       <c r="H129" s="7" t="n"/>
-      <c r="I129" s="7" t="n"/>
-      <c r="J129" s="7" t="n"/>
-      <c r="K129" s="7" t="n"/>
+      <c r="I129" s="8" t="n"/>
+      <c r="J129" s="8" t="n"/>
+      <c r="K129" s="8" t="n"/>
       <c r="L129" s="8" t="n"/>
       <c r="M129" s="8" t="n"/>
       <c r="N129" s="8" t="n"/>
       <c r="O129" s="8" t="n"/>
-      <c r="P129" s="9" t="n"/>
-      <c r="Q129" s="9" t="n"/>
+      <c r="P129" s="8" t="n"/>
+      <c r="Q129" s="8" t="n"/>
       <c r="R129" s="9" t="n"/>
       <c r="S129" s="9" t="n"/>
       <c r="T129" s="9" t="n"/>
       <c r="U129" s="9" t="n"/>
-      <c r="V129" s="9" t="n"/>
+      <c r="V129" s="10" t="n"/>
       <c r="W129" s="10" t="n"/>
       <c r="X129" s="10" t="n"/>
       <c r="Y129" s="10" t="n"/>
-      <c r="Z129" s="11" t="n"/>
-      <c r="AA129" s="11" t="n"/>
+      <c r="Z129" s="10" t="n"/>
+      <c r="AA129" s="10" t="n"/>
+      <c r="AB129" s="10" t="n"/>
+      <c r="AC129" s="11" t="n"/>
+      <c r="AD129" s="11" t="n"/>
+      <c r="AE129" s="11" t="n"/>
+      <c r="AF129" s="12" t="n"/>
+      <c r="AG129" s="12" t="n"/>
+      <c r="AH129" s="7" t="n"/>
     </row>
     <row r="130">
       <c r="A130" s="6" t="n"/>
@@ -4582,25 +5614,32 @@
       <c r="F130" s="7" t="n"/>
       <c r="G130" s="7" t="n"/>
       <c r="H130" s="7" t="n"/>
-      <c r="I130" s="7" t="n"/>
-      <c r="J130" s="7" t="n"/>
-      <c r="K130" s="7" t="n"/>
+      <c r="I130" s="8" t="n"/>
+      <c r="J130" s="8" t="n"/>
+      <c r="K130" s="8" t="n"/>
       <c r="L130" s="8" t="n"/>
       <c r="M130" s="8" t="n"/>
       <c r="N130" s="8" t="n"/>
       <c r="O130" s="8" t="n"/>
-      <c r="P130" s="9" t="n"/>
-      <c r="Q130" s="9" t="n"/>
+      <c r="P130" s="8" t="n"/>
+      <c r="Q130" s="8" t="n"/>
       <c r="R130" s="9" t="n"/>
       <c r="S130" s="9" t="n"/>
       <c r="T130" s="9" t="n"/>
       <c r="U130" s="9" t="n"/>
-      <c r="V130" s="9" t="n"/>
+      <c r="V130" s="10" t="n"/>
       <c r="W130" s="10" t="n"/>
       <c r="X130" s="10" t="n"/>
       <c r="Y130" s="10" t="n"/>
-      <c r="Z130" s="11" t="n"/>
-      <c r="AA130" s="11" t="n"/>
+      <c r="Z130" s="10" t="n"/>
+      <c r="AA130" s="10" t="n"/>
+      <c r="AB130" s="10" t="n"/>
+      <c r="AC130" s="11" t="n"/>
+      <c r="AD130" s="11" t="n"/>
+      <c r="AE130" s="11" t="n"/>
+      <c r="AF130" s="12" t="n"/>
+      <c r="AG130" s="12" t="n"/>
+      <c r="AH130" s="7" t="n"/>
     </row>
     <row r="131">
       <c r="A131" s="6" t="n"/>
@@ -4610,25 +5649,32 @@
       <c r="F131" s="7" t="n"/>
       <c r="G131" s="7" t="n"/>
       <c r="H131" s="7" t="n"/>
-      <c r="I131" s="7" t="n"/>
-      <c r="J131" s="7" t="n"/>
-      <c r="K131" s="7" t="n"/>
+      <c r="I131" s="8" t="n"/>
+      <c r="J131" s="8" t="n"/>
+      <c r="K131" s="8" t="n"/>
       <c r="L131" s="8" t="n"/>
       <c r="M131" s="8" t="n"/>
       <c r="N131" s="8" t="n"/>
       <c r="O131" s="8" t="n"/>
-      <c r="P131" s="9" t="n"/>
-      <c r="Q131" s="9" t="n"/>
+      <c r="P131" s="8" t="n"/>
+      <c r="Q131" s="8" t="n"/>
       <c r="R131" s="9" t="n"/>
       <c r="S131" s="9" t="n"/>
       <c r="T131" s="9" t="n"/>
       <c r="U131" s="9" t="n"/>
-      <c r="V131" s="9" t="n"/>
+      <c r="V131" s="10" t="n"/>
       <c r="W131" s="10" t="n"/>
       <c r="X131" s="10" t="n"/>
       <c r="Y131" s="10" t="n"/>
-      <c r="Z131" s="11" t="n"/>
-      <c r="AA131" s="11" t="n"/>
+      <c r="Z131" s="10" t="n"/>
+      <c r="AA131" s="10" t="n"/>
+      <c r="AB131" s="10" t="n"/>
+      <c r="AC131" s="11" t="n"/>
+      <c r="AD131" s="11" t="n"/>
+      <c r="AE131" s="11" t="n"/>
+      <c r="AF131" s="12" t="n"/>
+      <c r="AG131" s="12" t="n"/>
+      <c r="AH131" s="7" t="n"/>
     </row>
     <row r="132">
       <c r="A132" s="6" t="n"/>
@@ -4638,25 +5684,32 @@
       <c r="F132" s="7" t="n"/>
       <c r="G132" s="7" t="n"/>
       <c r="H132" s="7" t="n"/>
-      <c r="I132" s="7" t="n"/>
-      <c r="J132" s="7" t="n"/>
-      <c r="K132" s="7" t="n"/>
+      <c r="I132" s="8" t="n"/>
+      <c r="J132" s="8" t="n"/>
+      <c r="K132" s="8" t="n"/>
       <c r="L132" s="8" t="n"/>
       <c r="M132" s="8" t="n"/>
       <c r="N132" s="8" t="n"/>
       <c r="O132" s="8" t="n"/>
-      <c r="P132" s="9" t="n"/>
-      <c r="Q132" s="9" t="n"/>
+      <c r="P132" s="8" t="n"/>
+      <c r="Q132" s="8" t="n"/>
       <c r="R132" s="9" t="n"/>
       <c r="S132" s="9" t="n"/>
       <c r="T132" s="9" t="n"/>
       <c r="U132" s="9" t="n"/>
-      <c r="V132" s="9" t="n"/>
+      <c r="V132" s="10" t="n"/>
       <c r="W132" s="10" t="n"/>
       <c r="X132" s="10" t="n"/>
       <c r="Y132" s="10" t="n"/>
-      <c r="Z132" s="11" t="n"/>
-      <c r="AA132" s="11" t="n"/>
+      <c r="Z132" s="10" t="n"/>
+      <c r="AA132" s="10" t="n"/>
+      <c r="AB132" s="10" t="n"/>
+      <c r="AC132" s="11" t="n"/>
+      <c r="AD132" s="11" t="n"/>
+      <c r="AE132" s="11" t="n"/>
+      <c r="AF132" s="12" t="n"/>
+      <c r="AG132" s="12" t="n"/>
+      <c r="AH132" s="7" t="n"/>
     </row>
     <row r="133">
       <c r="A133" s="6" t="n"/>
@@ -4666,25 +5719,32 @@
       <c r="F133" s="7" t="n"/>
       <c r="G133" s="7" t="n"/>
       <c r="H133" s="7" t="n"/>
-      <c r="I133" s="7" t="n"/>
-      <c r="J133" s="7" t="n"/>
-      <c r="K133" s="7" t="n"/>
+      <c r="I133" s="8" t="n"/>
+      <c r="J133" s="8" t="n"/>
+      <c r="K133" s="8" t="n"/>
       <c r="L133" s="8" t="n"/>
       <c r="M133" s="8" t="n"/>
       <c r="N133" s="8" t="n"/>
       <c r="O133" s="8" t="n"/>
-      <c r="P133" s="9" t="n"/>
-      <c r="Q133" s="9" t="n"/>
+      <c r="P133" s="8" t="n"/>
+      <c r="Q133" s="8" t="n"/>
       <c r="R133" s="9" t="n"/>
       <c r="S133" s="9" t="n"/>
       <c r="T133" s="9" t="n"/>
       <c r="U133" s="9" t="n"/>
-      <c r="V133" s="9" t="n"/>
+      <c r="V133" s="10" t="n"/>
       <c r="W133" s="10" t="n"/>
       <c r="X133" s="10" t="n"/>
       <c r="Y133" s="10" t="n"/>
-      <c r="Z133" s="11" t="n"/>
-      <c r="AA133" s="11" t="n"/>
+      <c r="Z133" s="10" t="n"/>
+      <c r="AA133" s="10" t="n"/>
+      <c r="AB133" s="10" t="n"/>
+      <c r="AC133" s="11" t="n"/>
+      <c r="AD133" s="11" t="n"/>
+      <c r="AE133" s="11" t="n"/>
+      <c r="AF133" s="12" t="n"/>
+      <c r="AG133" s="12" t="n"/>
+      <c r="AH133" s="7" t="n"/>
     </row>
     <row r="134">
       <c r="A134" s="6" t="n"/>
@@ -4694,25 +5754,32 @@
       <c r="F134" s="7" t="n"/>
       <c r="G134" s="7" t="n"/>
       <c r="H134" s="7" t="n"/>
-      <c r="I134" s="7" t="n"/>
-      <c r="J134" s="7" t="n"/>
-      <c r="K134" s="7" t="n"/>
+      <c r="I134" s="8" t="n"/>
+      <c r="J134" s="8" t="n"/>
+      <c r="K134" s="8" t="n"/>
       <c r="L134" s="8" t="n"/>
       <c r="M134" s="8" t="n"/>
       <c r="N134" s="8" t="n"/>
       <c r="O134" s="8" t="n"/>
-      <c r="P134" s="9" t="n"/>
-      <c r="Q134" s="9" t="n"/>
+      <c r="P134" s="8" t="n"/>
+      <c r="Q134" s="8" t="n"/>
       <c r="R134" s="9" t="n"/>
       <c r="S134" s="9" t="n"/>
       <c r="T134" s="9" t="n"/>
       <c r="U134" s="9" t="n"/>
-      <c r="V134" s="9" t="n"/>
+      <c r="V134" s="10" t="n"/>
       <c r="W134" s="10" t="n"/>
       <c r="X134" s="10" t="n"/>
       <c r="Y134" s="10" t="n"/>
-      <c r="Z134" s="11" t="n"/>
-      <c r="AA134" s="11" t="n"/>
+      <c r="Z134" s="10" t="n"/>
+      <c r="AA134" s="10" t="n"/>
+      <c r="AB134" s="10" t="n"/>
+      <c r="AC134" s="11" t="n"/>
+      <c r="AD134" s="11" t="n"/>
+      <c r="AE134" s="11" t="n"/>
+      <c r="AF134" s="12" t="n"/>
+      <c r="AG134" s="12" t="n"/>
+      <c r="AH134" s="7" t="n"/>
     </row>
     <row r="135">
       <c r="A135" s="6" t="n"/>
@@ -4722,25 +5789,32 @@
       <c r="F135" s="7" t="n"/>
       <c r="G135" s="7" t="n"/>
       <c r="H135" s="7" t="n"/>
-      <c r="I135" s="7" t="n"/>
-      <c r="J135" s="7" t="n"/>
-      <c r="K135" s="7" t="n"/>
+      <c r="I135" s="8" t="n"/>
+      <c r="J135" s="8" t="n"/>
+      <c r="K135" s="8" t="n"/>
       <c r="L135" s="8" t="n"/>
       <c r="M135" s="8" t="n"/>
       <c r="N135" s="8" t="n"/>
       <c r="O135" s="8" t="n"/>
-      <c r="P135" s="9" t="n"/>
-      <c r="Q135" s="9" t="n"/>
+      <c r="P135" s="8" t="n"/>
+      <c r="Q135" s="8" t="n"/>
       <c r="R135" s="9" t="n"/>
       <c r="S135" s="9" t="n"/>
       <c r="T135" s="9" t="n"/>
       <c r="U135" s="9" t="n"/>
-      <c r="V135" s="9" t="n"/>
+      <c r="V135" s="10" t="n"/>
       <c r="W135" s="10" t="n"/>
       <c r="X135" s="10" t="n"/>
       <c r="Y135" s="10" t="n"/>
-      <c r="Z135" s="11" t="n"/>
-      <c r="AA135" s="11" t="n"/>
+      <c r="Z135" s="10" t="n"/>
+      <c r="AA135" s="10" t="n"/>
+      <c r="AB135" s="10" t="n"/>
+      <c r="AC135" s="11" t="n"/>
+      <c r="AD135" s="11" t="n"/>
+      <c r="AE135" s="11" t="n"/>
+      <c r="AF135" s="12" t="n"/>
+      <c r="AG135" s="12" t="n"/>
+      <c r="AH135" s="7" t="n"/>
     </row>
     <row r="136">
       <c r="A136" s="6" t="n"/>
@@ -4750,25 +5824,32 @@
       <c r="F136" s="7" t="n"/>
       <c r="G136" s="7" t="n"/>
       <c r="H136" s="7" t="n"/>
-      <c r="I136" s="7" t="n"/>
-      <c r="J136" s="7" t="n"/>
-      <c r="K136" s="7" t="n"/>
+      <c r="I136" s="8" t="n"/>
+      <c r="J136" s="8" t="n"/>
+      <c r="K136" s="8" t="n"/>
       <c r="L136" s="8" t="n"/>
       <c r="M136" s="8" t="n"/>
       <c r="N136" s="8" t="n"/>
       <c r="O136" s="8" t="n"/>
-      <c r="P136" s="9" t="n"/>
-      <c r="Q136" s="9" t="n"/>
+      <c r="P136" s="8" t="n"/>
+      <c r="Q136" s="8" t="n"/>
       <c r="R136" s="9" t="n"/>
       <c r="S136" s="9" t="n"/>
       <c r="T136" s="9" t="n"/>
       <c r="U136" s="9" t="n"/>
-      <c r="V136" s="9" t="n"/>
+      <c r="V136" s="10" t="n"/>
       <c r="W136" s="10" t="n"/>
       <c r="X136" s="10" t="n"/>
       <c r="Y136" s="10" t="n"/>
-      <c r="Z136" s="11" t="n"/>
-      <c r="AA136" s="11" t="n"/>
+      <c r="Z136" s="10" t="n"/>
+      <c r="AA136" s="10" t="n"/>
+      <c r="AB136" s="10" t="n"/>
+      <c r="AC136" s="11" t="n"/>
+      <c r="AD136" s="11" t="n"/>
+      <c r="AE136" s="11" t="n"/>
+      <c r="AF136" s="12" t="n"/>
+      <c r="AG136" s="12" t="n"/>
+      <c r="AH136" s="7" t="n"/>
     </row>
     <row r="137">
       <c r="A137" s="6" t="n"/>
@@ -4778,25 +5859,32 @@
       <c r="F137" s="7" t="n"/>
       <c r="G137" s="7" t="n"/>
       <c r="H137" s="7" t="n"/>
-      <c r="I137" s="7" t="n"/>
-      <c r="J137" s="7" t="n"/>
-      <c r="K137" s="7" t="n"/>
+      <c r="I137" s="8" t="n"/>
+      <c r="J137" s="8" t="n"/>
+      <c r="K137" s="8" t="n"/>
       <c r="L137" s="8" t="n"/>
       <c r="M137" s="8" t="n"/>
       <c r="N137" s="8" t="n"/>
       <c r="O137" s="8" t="n"/>
-      <c r="P137" s="9" t="n"/>
-      <c r="Q137" s="9" t="n"/>
+      <c r="P137" s="8" t="n"/>
+      <c r="Q137" s="8" t="n"/>
       <c r="R137" s="9" t="n"/>
       <c r="S137" s="9" t="n"/>
       <c r="T137" s="9" t="n"/>
       <c r="U137" s="9" t="n"/>
-      <c r="V137" s="9" t="n"/>
+      <c r="V137" s="10" t="n"/>
       <c r="W137" s="10" t="n"/>
       <c r="X137" s="10" t="n"/>
       <c r="Y137" s="10" t="n"/>
-      <c r="Z137" s="11" t="n"/>
-      <c r="AA137" s="11" t="n"/>
+      <c r="Z137" s="10" t="n"/>
+      <c r="AA137" s="10" t="n"/>
+      <c r="AB137" s="10" t="n"/>
+      <c r="AC137" s="11" t="n"/>
+      <c r="AD137" s="11" t="n"/>
+      <c r="AE137" s="11" t="n"/>
+      <c r="AF137" s="12" t="n"/>
+      <c r="AG137" s="12" t="n"/>
+      <c r="AH137" s="7" t="n"/>
     </row>
     <row r="138">
       <c r="A138" s="6" t="n"/>
@@ -4806,25 +5894,32 @@
       <c r="F138" s="7" t="n"/>
       <c r="G138" s="7" t="n"/>
       <c r="H138" s="7" t="n"/>
-      <c r="I138" s="7" t="n"/>
-      <c r="J138" s="7" t="n"/>
-      <c r="K138" s="7" t="n"/>
+      <c r="I138" s="8" t="n"/>
+      <c r="J138" s="8" t="n"/>
+      <c r="K138" s="8" t="n"/>
       <c r="L138" s="8" t="n"/>
       <c r="M138" s="8" t="n"/>
       <c r="N138" s="8" t="n"/>
       <c r="O138" s="8" t="n"/>
-      <c r="P138" s="9" t="n"/>
-      <c r="Q138" s="9" t="n"/>
+      <c r="P138" s="8" t="n"/>
+      <c r="Q138" s="8" t="n"/>
       <c r="R138" s="9" t="n"/>
       <c r="S138" s="9" t="n"/>
       <c r="T138" s="9" t="n"/>
       <c r="U138" s="9" t="n"/>
-      <c r="V138" s="9" t="n"/>
+      <c r="V138" s="10" t="n"/>
       <c r="W138" s="10" t="n"/>
       <c r="X138" s="10" t="n"/>
       <c r="Y138" s="10" t="n"/>
-      <c r="Z138" s="11" t="n"/>
-      <c r="AA138" s="11" t="n"/>
+      <c r="Z138" s="10" t="n"/>
+      <c r="AA138" s="10" t="n"/>
+      <c r="AB138" s="10" t="n"/>
+      <c r="AC138" s="11" t="n"/>
+      <c r="AD138" s="11" t="n"/>
+      <c r="AE138" s="11" t="n"/>
+      <c r="AF138" s="12" t="n"/>
+      <c r="AG138" s="12" t="n"/>
+      <c r="AH138" s="7" t="n"/>
     </row>
     <row r="139">
       <c r="A139" s="6" t="n"/>
@@ -4834,25 +5929,32 @@
       <c r="F139" s="7" t="n"/>
       <c r="G139" s="7" t="n"/>
       <c r="H139" s="7" t="n"/>
-      <c r="I139" s="7" t="n"/>
-      <c r="J139" s="7" t="n"/>
-      <c r="K139" s="7" t="n"/>
+      <c r="I139" s="8" t="n"/>
+      <c r="J139" s="8" t="n"/>
+      <c r="K139" s="8" t="n"/>
       <c r="L139" s="8" t="n"/>
       <c r="M139" s="8" t="n"/>
       <c r="N139" s="8" t="n"/>
       <c r="O139" s="8" t="n"/>
-      <c r="P139" s="9" t="n"/>
-      <c r="Q139" s="9" t="n"/>
+      <c r="P139" s="8" t="n"/>
+      <c r="Q139" s="8" t="n"/>
       <c r="R139" s="9" t="n"/>
       <c r="S139" s="9" t="n"/>
       <c r="T139" s="9" t="n"/>
       <c r="U139" s="9" t="n"/>
-      <c r="V139" s="9" t="n"/>
+      <c r="V139" s="10" t="n"/>
       <c r="W139" s="10" t="n"/>
       <c r="X139" s="10" t="n"/>
       <c r="Y139" s="10" t="n"/>
-      <c r="Z139" s="11" t="n"/>
-      <c r="AA139" s="11" t="n"/>
+      <c r="Z139" s="10" t="n"/>
+      <c r="AA139" s="10" t="n"/>
+      <c r="AB139" s="10" t="n"/>
+      <c r="AC139" s="11" t="n"/>
+      <c r="AD139" s="11" t="n"/>
+      <c r="AE139" s="11" t="n"/>
+      <c r="AF139" s="12" t="n"/>
+      <c r="AG139" s="12" t="n"/>
+      <c r="AH139" s="7" t="n"/>
     </row>
     <row r="140">
       <c r="A140" s="6" t="n"/>
@@ -4862,25 +5964,32 @@
       <c r="F140" s="7" t="n"/>
       <c r="G140" s="7" t="n"/>
       <c r="H140" s="7" t="n"/>
-      <c r="I140" s="7" t="n"/>
-      <c r="J140" s="7" t="n"/>
-      <c r="K140" s="7" t="n"/>
+      <c r="I140" s="8" t="n"/>
+      <c r="J140" s="8" t="n"/>
+      <c r="K140" s="8" t="n"/>
       <c r="L140" s="8" t="n"/>
       <c r="M140" s="8" t="n"/>
       <c r="N140" s="8" t="n"/>
       <c r="O140" s="8" t="n"/>
-      <c r="P140" s="9" t="n"/>
-      <c r="Q140" s="9" t="n"/>
+      <c r="P140" s="8" t="n"/>
+      <c r="Q140" s="8" t="n"/>
       <c r="R140" s="9" t="n"/>
       <c r="S140" s="9" t="n"/>
       <c r="T140" s="9" t="n"/>
       <c r="U140" s="9" t="n"/>
-      <c r="V140" s="9" t="n"/>
+      <c r="V140" s="10" t="n"/>
       <c r="W140" s="10" t="n"/>
       <c r="X140" s="10" t="n"/>
       <c r="Y140" s="10" t="n"/>
-      <c r="Z140" s="11" t="n"/>
-      <c r="AA140" s="11" t="n"/>
+      <c r="Z140" s="10" t="n"/>
+      <c r="AA140" s="10" t="n"/>
+      <c r="AB140" s="10" t="n"/>
+      <c r="AC140" s="11" t="n"/>
+      <c r="AD140" s="11" t="n"/>
+      <c r="AE140" s="11" t="n"/>
+      <c r="AF140" s="12" t="n"/>
+      <c r="AG140" s="12" t="n"/>
+      <c r="AH140" s="7" t="n"/>
     </row>
     <row r="141">
       <c r="A141" s="6" t="n"/>
@@ -4890,25 +5999,32 @@
       <c r="F141" s="7" t="n"/>
       <c r="G141" s="7" t="n"/>
       <c r="H141" s="7" t="n"/>
-      <c r="I141" s="7" t="n"/>
-      <c r="J141" s="7" t="n"/>
-      <c r="K141" s="7" t="n"/>
+      <c r="I141" s="8" t="n"/>
+      <c r="J141" s="8" t="n"/>
+      <c r="K141" s="8" t="n"/>
       <c r="L141" s="8" t="n"/>
       <c r="M141" s="8" t="n"/>
       <c r="N141" s="8" t="n"/>
       <c r="O141" s="8" t="n"/>
-      <c r="P141" s="9" t="n"/>
-      <c r="Q141" s="9" t="n"/>
+      <c r="P141" s="8" t="n"/>
+      <c r="Q141" s="8" t="n"/>
       <c r="R141" s="9" t="n"/>
       <c r="S141" s="9" t="n"/>
       <c r="T141" s="9" t="n"/>
       <c r="U141" s="9" t="n"/>
-      <c r="V141" s="9" t="n"/>
+      <c r="V141" s="10" t="n"/>
       <c r="W141" s="10" t="n"/>
       <c r="X141" s="10" t="n"/>
       <c r="Y141" s="10" t="n"/>
-      <c r="Z141" s="11" t="n"/>
-      <c r="AA141" s="11" t="n"/>
+      <c r="Z141" s="10" t="n"/>
+      <c r="AA141" s="10" t="n"/>
+      <c r="AB141" s="10" t="n"/>
+      <c r="AC141" s="11" t="n"/>
+      <c r="AD141" s="11" t="n"/>
+      <c r="AE141" s="11" t="n"/>
+      <c r="AF141" s="12" t="n"/>
+      <c r="AG141" s="12" t="n"/>
+      <c r="AH141" s="7" t="n"/>
     </row>
     <row r="142">
       <c r="A142" s="6" t="n"/>
@@ -4918,25 +6034,32 @@
       <c r="F142" s="7" t="n"/>
       <c r="G142" s="7" t="n"/>
       <c r="H142" s="7" t="n"/>
-      <c r="I142" s="7" t="n"/>
-      <c r="J142" s="7" t="n"/>
-      <c r="K142" s="7" t="n"/>
+      <c r="I142" s="8" t="n"/>
+      <c r="J142" s="8" t="n"/>
+      <c r="K142" s="8" t="n"/>
       <c r="L142" s="8" t="n"/>
       <c r="M142" s="8" t="n"/>
       <c r="N142" s="8" t="n"/>
       <c r="O142" s="8" t="n"/>
-      <c r="P142" s="9" t="n"/>
-      <c r="Q142" s="9" t="n"/>
+      <c r="P142" s="8" t="n"/>
+      <c r="Q142" s="8" t="n"/>
       <c r="R142" s="9" t="n"/>
       <c r="S142" s="9" t="n"/>
       <c r="T142" s="9" t="n"/>
       <c r="U142" s="9" t="n"/>
-      <c r="V142" s="9" t="n"/>
+      <c r="V142" s="10" t="n"/>
       <c r="W142" s="10" t="n"/>
       <c r="X142" s="10" t="n"/>
       <c r="Y142" s="10" t="n"/>
-      <c r="Z142" s="11" t="n"/>
-      <c r="AA142" s="11" t="n"/>
+      <c r="Z142" s="10" t="n"/>
+      <c r="AA142" s="10" t="n"/>
+      <c r="AB142" s="10" t="n"/>
+      <c r="AC142" s="11" t="n"/>
+      <c r="AD142" s="11" t="n"/>
+      <c r="AE142" s="11" t="n"/>
+      <c r="AF142" s="12" t="n"/>
+      <c r="AG142" s="12" t="n"/>
+      <c r="AH142" s="7" t="n"/>
     </row>
     <row r="143">
       <c r="A143" s="6" t="n"/>
@@ -4946,25 +6069,32 @@
       <c r="F143" s="7" t="n"/>
       <c r="G143" s="7" t="n"/>
       <c r="H143" s="7" t="n"/>
-      <c r="I143" s="7" t="n"/>
-      <c r="J143" s="7" t="n"/>
-      <c r="K143" s="7" t="n"/>
+      <c r="I143" s="8" t="n"/>
+      <c r="J143" s="8" t="n"/>
+      <c r="K143" s="8" t="n"/>
       <c r="L143" s="8" t="n"/>
       <c r="M143" s="8" t="n"/>
       <c r="N143" s="8" t="n"/>
       <c r="O143" s="8" t="n"/>
-      <c r="P143" s="9" t="n"/>
-      <c r="Q143" s="9" t="n"/>
+      <c r="P143" s="8" t="n"/>
+      <c r="Q143" s="8" t="n"/>
       <c r="R143" s="9" t="n"/>
       <c r="S143" s="9" t="n"/>
       <c r="T143" s="9" t="n"/>
       <c r="U143" s="9" t="n"/>
-      <c r="V143" s="9" t="n"/>
+      <c r="V143" s="10" t="n"/>
       <c r="W143" s="10" t="n"/>
       <c r="X143" s="10" t="n"/>
       <c r="Y143" s="10" t="n"/>
-      <c r="Z143" s="11" t="n"/>
-      <c r="AA143" s="11" t="n"/>
+      <c r="Z143" s="10" t="n"/>
+      <c r="AA143" s="10" t="n"/>
+      <c r="AB143" s="10" t="n"/>
+      <c r="AC143" s="11" t="n"/>
+      <c r="AD143" s="11" t="n"/>
+      <c r="AE143" s="11" t="n"/>
+      <c r="AF143" s="12" t="n"/>
+      <c r="AG143" s="12" t="n"/>
+      <c r="AH143" s="7" t="n"/>
     </row>
     <row r="144">
       <c r="A144" s="6" t="n"/>
@@ -4974,25 +6104,32 @@
       <c r="F144" s="7" t="n"/>
       <c r="G144" s="7" t="n"/>
       <c r="H144" s="7" t="n"/>
-      <c r="I144" s="7" t="n"/>
-      <c r="J144" s="7" t="n"/>
-      <c r="K144" s="7" t="n"/>
+      <c r="I144" s="8" t="n"/>
+      <c r="J144" s="8" t="n"/>
+      <c r="K144" s="8" t="n"/>
       <c r="L144" s="8" t="n"/>
       <c r="M144" s="8" t="n"/>
       <c r="N144" s="8" t="n"/>
       <c r="O144" s="8" t="n"/>
-      <c r="P144" s="9" t="n"/>
-      <c r="Q144" s="9" t="n"/>
+      <c r="P144" s="8" t="n"/>
+      <c r="Q144" s="8" t="n"/>
       <c r="R144" s="9" t="n"/>
       <c r="S144" s="9" t="n"/>
       <c r="T144" s="9" t="n"/>
       <c r="U144" s="9" t="n"/>
-      <c r="V144" s="9" t="n"/>
+      <c r="V144" s="10" t="n"/>
       <c r="W144" s="10" t="n"/>
       <c r="X144" s="10" t="n"/>
       <c r="Y144" s="10" t="n"/>
-      <c r="Z144" s="11" t="n"/>
-      <c r="AA144" s="11" t="n"/>
+      <c r="Z144" s="10" t="n"/>
+      <c r="AA144" s="10" t="n"/>
+      <c r="AB144" s="10" t="n"/>
+      <c r="AC144" s="11" t="n"/>
+      <c r="AD144" s="11" t="n"/>
+      <c r="AE144" s="11" t="n"/>
+      <c r="AF144" s="12" t="n"/>
+      <c r="AG144" s="12" t="n"/>
+      <c r="AH144" s="7" t="n"/>
     </row>
     <row r="145">
       <c r="A145" s="6" t="n"/>
@@ -5002,25 +6139,32 @@
       <c r="F145" s="7" t="n"/>
       <c r="G145" s="7" t="n"/>
       <c r="H145" s="7" t="n"/>
-      <c r="I145" s="7" t="n"/>
-      <c r="J145" s="7" t="n"/>
-      <c r="K145" s="7" t="n"/>
+      <c r="I145" s="8" t="n"/>
+      <c r="J145" s="8" t="n"/>
+      <c r="K145" s="8" t="n"/>
       <c r="L145" s="8" t="n"/>
       <c r="M145" s="8" t="n"/>
       <c r="N145" s="8" t="n"/>
       <c r="O145" s="8" t="n"/>
-      <c r="P145" s="9" t="n"/>
-      <c r="Q145" s="9" t="n"/>
+      <c r="P145" s="8" t="n"/>
+      <c r="Q145" s="8" t="n"/>
       <c r="R145" s="9" t="n"/>
       <c r="S145" s="9" t="n"/>
       <c r="T145" s="9" t="n"/>
       <c r="U145" s="9" t="n"/>
-      <c r="V145" s="9" t="n"/>
+      <c r="V145" s="10" t="n"/>
       <c r="W145" s="10" t="n"/>
       <c r="X145" s="10" t="n"/>
       <c r="Y145" s="10" t="n"/>
-      <c r="Z145" s="11" t="n"/>
-      <c r="AA145" s="11" t="n"/>
+      <c r="Z145" s="10" t="n"/>
+      <c r="AA145" s="10" t="n"/>
+      <c r="AB145" s="10" t="n"/>
+      <c r="AC145" s="11" t="n"/>
+      <c r="AD145" s="11" t="n"/>
+      <c r="AE145" s="11" t="n"/>
+      <c r="AF145" s="12" t="n"/>
+      <c r="AG145" s="12" t="n"/>
+      <c r="AH145" s="7" t="n"/>
     </row>
     <row r="146">
       <c r="A146" s="6" t="n"/>
@@ -5030,25 +6174,32 @@
       <c r="F146" s="7" t="n"/>
       <c r="G146" s="7" t="n"/>
       <c r="H146" s="7" t="n"/>
-      <c r="I146" s="7" t="n"/>
-      <c r="J146" s="7" t="n"/>
-      <c r="K146" s="7" t="n"/>
+      <c r="I146" s="8" t="n"/>
+      <c r="J146" s="8" t="n"/>
+      <c r="K146" s="8" t="n"/>
       <c r="L146" s="8" t="n"/>
       <c r="M146" s="8" t="n"/>
       <c r="N146" s="8" t="n"/>
       <c r="O146" s="8" t="n"/>
-      <c r="P146" s="9" t="n"/>
-      <c r="Q146" s="9" t="n"/>
+      <c r="P146" s="8" t="n"/>
+      <c r="Q146" s="8" t="n"/>
       <c r="R146" s="9" t="n"/>
       <c r="S146" s="9" t="n"/>
       <c r="T146" s="9" t="n"/>
       <c r="U146" s="9" t="n"/>
-      <c r="V146" s="9" t="n"/>
+      <c r="V146" s="10" t="n"/>
       <c r="W146" s="10" t="n"/>
       <c r="X146" s="10" t="n"/>
       <c r="Y146" s="10" t="n"/>
-      <c r="Z146" s="11" t="n"/>
-      <c r="AA146" s="11" t="n"/>
+      <c r="Z146" s="10" t="n"/>
+      <c r="AA146" s="10" t="n"/>
+      <c r="AB146" s="10" t="n"/>
+      <c r="AC146" s="11" t="n"/>
+      <c r="AD146" s="11" t="n"/>
+      <c r="AE146" s="11" t="n"/>
+      <c r="AF146" s="12" t="n"/>
+      <c r="AG146" s="12" t="n"/>
+      <c r="AH146" s="7" t="n"/>
     </row>
     <row r="147">
       <c r="A147" s="6" t="n"/>
@@ -5058,25 +6209,32 @@
       <c r="F147" s="7" t="n"/>
       <c r="G147" s="7" t="n"/>
       <c r="H147" s="7" t="n"/>
-      <c r="I147" s="7" t="n"/>
-      <c r="J147" s="7" t="n"/>
-      <c r="K147" s="7" t="n"/>
+      <c r="I147" s="8" t="n"/>
+      <c r="J147" s="8" t="n"/>
+      <c r="K147" s="8" t="n"/>
       <c r="L147" s="8" t="n"/>
       <c r="M147" s="8" t="n"/>
       <c r="N147" s="8" t="n"/>
       <c r="O147" s="8" t="n"/>
-      <c r="P147" s="9" t="n"/>
-      <c r="Q147" s="9" t="n"/>
+      <c r="P147" s="8" t="n"/>
+      <c r="Q147" s="8" t="n"/>
       <c r="R147" s="9" t="n"/>
       <c r="S147" s="9" t="n"/>
       <c r="T147" s="9" t="n"/>
       <c r="U147" s="9" t="n"/>
-      <c r="V147" s="9" t="n"/>
+      <c r="V147" s="10" t="n"/>
       <c r="W147" s="10" t="n"/>
       <c r="X147" s="10" t="n"/>
       <c r="Y147" s="10" t="n"/>
-      <c r="Z147" s="11" t="n"/>
-      <c r="AA147" s="11" t="n"/>
+      <c r="Z147" s="10" t="n"/>
+      <c r="AA147" s="10" t="n"/>
+      <c r="AB147" s="10" t="n"/>
+      <c r="AC147" s="11" t="n"/>
+      <c r="AD147" s="11" t="n"/>
+      <c r="AE147" s="11" t="n"/>
+      <c r="AF147" s="12" t="n"/>
+      <c r="AG147" s="12" t="n"/>
+      <c r="AH147" s="7" t="n"/>
     </row>
     <row r="148">
       <c r="A148" s="6" t="n"/>
@@ -5086,25 +6244,32 @@
       <c r="F148" s="7" t="n"/>
       <c r="G148" s="7" t="n"/>
       <c r="H148" s="7" t="n"/>
-      <c r="I148" s="7" t="n"/>
-      <c r="J148" s="7" t="n"/>
-      <c r="K148" s="7" t="n"/>
+      <c r="I148" s="8" t="n"/>
+      <c r="J148" s="8" t="n"/>
+      <c r="K148" s="8" t="n"/>
       <c r="L148" s="8" t="n"/>
       <c r="M148" s="8" t="n"/>
       <c r="N148" s="8" t="n"/>
       <c r="O148" s="8" t="n"/>
-      <c r="P148" s="9" t="n"/>
-      <c r="Q148" s="9" t="n"/>
+      <c r="P148" s="8" t="n"/>
+      <c r="Q148" s="8" t="n"/>
       <c r="R148" s="9" t="n"/>
       <c r="S148" s="9" t="n"/>
       <c r="T148" s="9" t="n"/>
       <c r="U148" s="9" t="n"/>
-      <c r="V148" s="9" t="n"/>
+      <c r="V148" s="10" t="n"/>
       <c r="W148" s="10" t="n"/>
       <c r="X148" s="10" t="n"/>
       <c r="Y148" s="10" t="n"/>
-      <c r="Z148" s="11" t="n"/>
-      <c r="AA148" s="11" t="n"/>
+      <c r="Z148" s="10" t="n"/>
+      <c r="AA148" s="10" t="n"/>
+      <c r="AB148" s="10" t="n"/>
+      <c r="AC148" s="11" t="n"/>
+      <c r="AD148" s="11" t="n"/>
+      <c r="AE148" s="11" t="n"/>
+      <c r="AF148" s="12" t="n"/>
+      <c r="AG148" s="12" t="n"/>
+      <c r="AH148" s="7" t="n"/>
     </row>
     <row r="149">
       <c r="A149" s="6" t="n"/>
@@ -5114,25 +6279,32 @@
       <c r="F149" s="7" t="n"/>
       <c r="G149" s="7" t="n"/>
       <c r="H149" s="7" t="n"/>
-      <c r="I149" s="7" t="n"/>
-      <c r="J149" s="7" t="n"/>
-      <c r="K149" s="7" t="n"/>
+      <c r="I149" s="8" t="n"/>
+      <c r="J149" s="8" t="n"/>
+      <c r="K149" s="8" t="n"/>
       <c r="L149" s="8" t="n"/>
       <c r="M149" s="8" t="n"/>
       <c r="N149" s="8" t="n"/>
       <c r="O149" s="8" t="n"/>
-      <c r="P149" s="9" t="n"/>
-      <c r="Q149" s="9" t="n"/>
+      <c r="P149" s="8" t="n"/>
+      <c r="Q149" s="8" t="n"/>
       <c r="R149" s="9" t="n"/>
       <c r="S149" s="9" t="n"/>
       <c r="T149" s="9" t="n"/>
       <c r="U149" s="9" t="n"/>
-      <c r="V149" s="9" t="n"/>
+      <c r="V149" s="10" t="n"/>
       <c r="W149" s="10" t="n"/>
       <c r="X149" s="10" t="n"/>
       <c r="Y149" s="10" t="n"/>
-      <c r="Z149" s="11" t="n"/>
-      <c r="AA149" s="11" t="n"/>
+      <c r="Z149" s="10" t="n"/>
+      <c r="AA149" s="10" t="n"/>
+      <c r="AB149" s="10" t="n"/>
+      <c r="AC149" s="11" t="n"/>
+      <c r="AD149" s="11" t="n"/>
+      <c r="AE149" s="11" t="n"/>
+      <c r="AF149" s="12" t="n"/>
+      <c r="AG149" s="12" t="n"/>
+      <c r="AH149" s="7" t="n"/>
     </row>
     <row r="150">
       <c r="A150" s="6" t="n"/>
@@ -5142,25 +6314,32 @@
       <c r="F150" s="7" t="n"/>
       <c r="G150" s="7" t="n"/>
       <c r="H150" s="7" t="n"/>
-      <c r="I150" s="7" t="n"/>
-      <c r="J150" s="7" t="n"/>
-      <c r="K150" s="7" t="n"/>
+      <c r="I150" s="8" t="n"/>
+      <c r="J150" s="8" t="n"/>
+      <c r="K150" s="8" t="n"/>
       <c r="L150" s="8" t="n"/>
       <c r="M150" s="8" t="n"/>
       <c r="N150" s="8" t="n"/>
       <c r="O150" s="8" t="n"/>
-      <c r="P150" s="9" t="n"/>
-      <c r="Q150" s="9" t="n"/>
+      <c r="P150" s="8" t="n"/>
+      <c r="Q150" s="8" t="n"/>
       <c r="R150" s="9" t="n"/>
       <c r="S150" s="9" t="n"/>
       <c r="T150" s="9" t="n"/>
       <c r="U150" s="9" t="n"/>
-      <c r="V150" s="9" t="n"/>
+      <c r="V150" s="10" t="n"/>
       <c r="W150" s="10" t="n"/>
       <c r="X150" s="10" t="n"/>
       <c r="Y150" s="10" t="n"/>
-      <c r="Z150" s="11" t="n"/>
-      <c r="AA150" s="11" t="n"/>
+      <c r="Z150" s="10" t="n"/>
+      <c r="AA150" s="10" t="n"/>
+      <c r="AB150" s="10" t="n"/>
+      <c r="AC150" s="11" t="n"/>
+      <c r="AD150" s="11" t="n"/>
+      <c r="AE150" s="11" t="n"/>
+      <c r="AF150" s="12" t="n"/>
+      <c r="AG150" s="12" t="n"/>
+      <c r="AH150" s="7" t="n"/>
     </row>
     <row r="151">
       <c r="A151" s="6" t="n"/>
@@ -5170,25 +6349,32 @@
       <c r="F151" s="7" t="n"/>
       <c r="G151" s="7" t="n"/>
       <c r="H151" s="7" t="n"/>
-      <c r="I151" s="7" t="n"/>
-      <c r="J151" s="7" t="n"/>
-      <c r="K151" s="7" t="n"/>
+      <c r="I151" s="8" t="n"/>
+      <c r="J151" s="8" t="n"/>
+      <c r="K151" s="8" t="n"/>
       <c r="L151" s="8" t="n"/>
       <c r="M151" s="8" t="n"/>
       <c r="N151" s="8" t="n"/>
       <c r="O151" s="8" t="n"/>
-      <c r="P151" s="9" t="n"/>
-      <c r="Q151" s="9" t="n"/>
+      <c r="P151" s="8" t="n"/>
+      <c r="Q151" s="8" t="n"/>
       <c r="R151" s="9" t="n"/>
       <c r="S151" s="9" t="n"/>
       <c r="T151" s="9" t="n"/>
       <c r="U151" s="9" t="n"/>
-      <c r="V151" s="9" t="n"/>
+      <c r="V151" s="10" t="n"/>
       <c r="W151" s="10" t="n"/>
       <c r="X151" s="10" t="n"/>
       <c r="Y151" s="10" t="n"/>
-      <c r="Z151" s="11" t="n"/>
-      <c r="AA151" s="11" t="n"/>
+      <c r="Z151" s="10" t="n"/>
+      <c r="AA151" s="10" t="n"/>
+      <c r="AB151" s="10" t="n"/>
+      <c r="AC151" s="11" t="n"/>
+      <c r="AD151" s="11" t="n"/>
+      <c r="AE151" s="11" t="n"/>
+      <c r="AF151" s="12" t="n"/>
+      <c r="AG151" s="12" t="n"/>
+      <c r="AH151" s="7" t="n"/>
     </row>
     <row r="152">
       <c r="A152" s="6" t="n"/>
@@ -5198,25 +6384,32 @@
       <c r="F152" s="7" t="n"/>
       <c r="G152" s="7" t="n"/>
       <c r="H152" s="7" t="n"/>
-      <c r="I152" s="7" t="n"/>
-      <c r="J152" s="7" t="n"/>
-      <c r="K152" s="7" t="n"/>
+      <c r="I152" s="8" t="n"/>
+      <c r="J152" s="8" t="n"/>
+      <c r="K152" s="8" t="n"/>
       <c r="L152" s="8" t="n"/>
       <c r="M152" s="8" t="n"/>
       <c r="N152" s="8" t="n"/>
       <c r="O152" s="8" t="n"/>
-      <c r="P152" s="9" t="n"/>
-      <c r="Q152" s="9" t="n"/>
+      <c r="P152" s="8" t="n"/>
+      <c r="Q152" s="8" t="n"/>
       <c r="R152" s="9" t="n"/>
       <c r="S152" s="9" t="n"/>
       <c r="T152" s="9" t="n"/>
       <c r="U152" s="9" t="n"/>
-      <c r="V152" s="9" t="n"/>
+      <c r="V152" s="10" t="n"/>
       <c r="W152" s="10" t="n"/>
       <c r="X152" s="10" t="n"/>
       <c r="Y152" s="10" t="n"/>
-      <c r="Z152" s="11" t="n"/>
-      <c r="AA152" s="11" t="n"/>
+      <c r="Z152" s="10" t="n"/>
+      <c r="AA152" s="10" t="n"/>
+      <c r="AB152" s="10" t="n"/>
+      <c r="AC152" s="11" t="n"/>
+      <c r="AD152" s="11" t="n"/>
+      <c r="AE152" s="11" t="n"/>
+      <c r="AF152" s="12" t="n"/>
+      <c r="AG152" s="12" t="n"/>
+      <c r="AH152" s="7" t="n"/>
     </row>
     <row r="153">
       <c r="A153" s="6" t="n"/>
@@ -5226,25 +6419,32 @@
       <c r="F153" s="7" t="n"/>
       <c r="G153" s="7" t="n"/>
       <c r="H153" s="7" t="n"/>
-      <c r="I153" s="7" t="n"/>
-      <c r="J153" s="7" t="n"/>
-      <c r="K153" s="7" t="n"/>
+      <c r="I153" s="8" t="n"/>
+      <c r="J153" s="8" t="n"/>
+      <c r="K153" s="8" t="n"/>
       <c r="L153" s="8" t="n"/>
       <c r="M153" s="8" t="n"/>
       <c r="N153" s="8" t="n"/>
       <c r="O153" s="8" t="n"/>
-      <c r="P153" s="9" t="n"/>
-      <c r="Q153" s="9" t="n"/>
+      <c r="P153" s="8" t="n"/>
+      <c r="Q153" s="8" t="n"/>
       <c r="R153" s="9" t="n"/>
       <c r="S153" s="9" t="n"/>
       <c r="T153" s="9" t="n"/>
       <c r="U153" s="9" t="n"/>
-      <c r="V153" s="9" t="n"/>
+      <c r="V153" s="10" t="n"/>
       <c r="W153" s="10" t="n"/>
       <c r="X153" s="10" t="n"/>
       <c r="Y153" s="10" t="n"/>
-      <c r="Z153" s="11" t="n"/>
-      <c r="AA153" s="11" t="n"/>
+      <c r="Z153" s="10" t="n"/>
+      <c r="AA153" s="10" t="n"/>
+      <c r="AB153" s="10" t="n"/>
+      <c r="AC153" s="11" t="n"/>
+      <c r="AD153" s="11" t="n"/>
+      <c r="AE153" s="11" t="n"/>
+      <c r="AF153" s="12" t="n"/>
+      <c r="AG153" s="12" t="n"/>
+      <c r="AH153" s="7" t="n"/>
     </row>
     <row r="154">
       <c r="A154" s="6" t="n"/>
@@ -5254,25 +6454,32 @@
       <c r="F154" s="7" t="n"/>
       <c r="G154" s="7" t="n"/>
       <c r="H154" s="7" t="n"/>
-      <c r="I154" s="7" t="n"/>
-      <c r="J154" s="7" t="n"/>
-      <c r="K154" s="7" t="n"/>
+      <c r="I154" s="8" t="n"/>
+      <c r="J154" s="8" t="n"/>
+      <c r="K154" s="8" t="n"/>
       <c r="L154" s="8" t="n"/>
       <c r="M154" s="8" t="n"/>
       <c r="N154" s="8" t="n"/>
       <c r="O154" s="8" t="n"/>
-      <c r="P154" s="9" t="n"/>
-      <c r="Q154" s="9" t="n"/>
+      <c r="P154" s="8" t="n"/>
+      <c r="Q154" s="8" t="n"/>
       <c r="R154" s="9" t="n"/>
       <c r="S154" s="9" t="n"/>
       <c r="T154" s="9" t="n"/>
       <c r="U154" s="9" t="n"/>
-      <c r="V154" s="9" t="n"/>
+      <c r="V154" s="10" t="n"/>
       <c r="W154" s="10" t="n"/>
       <c r="X154" s="10" t="n"/>
       <c r="Y154" s="10" t="n"/>
-      <c r="Z154" s="11" t="n"/>
-      <c r="AA154" s="11" t="n"/>
+      <c r="Z154" s="10" t="n"/>
+      <c r="AA154" s="10" t="n"/>
+      <c r="AB154" s="10" t="n"/>
+      <c r="AC154" s="11" t="n"/>
+      <c r="AD154" s="11" t="n"/>
+      <c r="AE154" s="11" t="n"/>
+      <c r="AF154" s="12" t="n"/>
+      <c r="AG154" s="12" t="n"/>
+      <c r="AH154" s="7" t="n"/>
     </row>
     <row r="155">
       <c r="A155" s="6" t="n"/>
@@ -5282,25 +6489,32 @@
       <c r="F155" s="7" t="n"/>
       <c r="G155" s="7" t="n"/>
       <c r="H155" s="7" t="n"/>
-      <c r="I155" s="7" t="n"/>
-      <c r="J155" s="7" t="n"/>
-      <c r="K155" s="7" t="n"/>
+      <c r="I155" s="8" t="n"/>
+      <c r="J155" s="8" t="n"/>
+      <c r="K155" s="8" t="n"/>
       <c r="L155" s="8" t="n"/>
       <c r="M155" s="8" t="n"/>
       <c r="N155" s="8" t="n"/>
       <c r="O155" s="8" t="n"/>
-      <c r="P155" s="9" t="n"/>
-      <c r="Q155" s="9" t="n"/>
+      <c r="P155" s="8" t="n"/>
+      <c r="Q155" s="8" t="n"/>
       <c r="R155" s="9" t="n"/>
       <c r="S155" s="9" t="n"/>
       <c r="T155" s="9" t="n"/>
       <c r="U155" s="9" t="n"/>
-      <c r="V155" s="9" t="n"/>
+      <c r="V155" s="10" t="n"/>
       <c r="W155" s="10" t="n"/>
       <c r="X155" s="10" t="n"/>
       <c r="Y155" s="10" t="n"/>
-      <c r="Z155" s="11" t="n"/>
-      <c r="AA155" s="11" t="n"/>
+      <c r="Z155" s="10" t="n"/>
+      <c r="AA155" s="10" t="n"/>
+      <c r="AB155" s="10" t="n"/>
+      <c r="AC155" s="11" t="n"/>
+      <c r="AD155" s="11" t="n"/>
+      <c r="AE155" s="11" t="n"/>
+      <c r="AF155" s="12" t="n"/>
+      <c r="AG155" s="12" t="n"/>
+      <c r="AH155" s="7" t="n"/>
     </row>
     <row r="156">
       <c r="A156" s="6" t="n"/>
@@ -5310,25 +6524,32 @@
       <c r="F156" s="7" t="n"/>
       <c r="G156" s="7" t="n"/>
       <c r="H156" s="7" t="n"/>
-      <c r="I156" s="7" t="n"/>
-      <c r="J156" s="7" t="n"/>
-      <c r="K156" s="7" t="n"/>
+      <c r="I156" s="8" t="n"/>
+      <c r="J156" s="8" t="n"/>
+      <c r="K156" s="8" t="n"/>
       <c r="L156" s="8" t="n"/>
       <c r="M156" s="8" t="n"/>
       <c r="N156" s="8" t="n"/>
       <c r="O156" s="8" t="n"/>
-      <c r="P156" s="9" t="n"/>
-      <c r="Q156" s="9" t="n"/>
+      <c r="P156" s="8" t="n"/>
+      <c r="Q156" s="8" t="n"/>
       <c r="R156" s="9" t="n"/>
       <c r="S156" s="9" t="n"/>
       <c r="T156" s="9" t="n"/>
       <c r="U156" s="9" t="n"/>
-      <c r="V156" s="9" t="n"/>
+      <c r="V156" s="10" t="n"/>
       <c r="W156" s="10" t="n"/>
       <c r="X156" s="10" t="n"/>
       <c r="Y156" s="10" t="n"/>
-      <c r="Z156" s="11" t="n"/>
-      <c r="AA156" s="11" t="n"/>
+      <c r="Z156" s="10" t="n"/>
+      <c r="AA156" s="10" t="n"/>
+      <c r="AB156" s="10" t="n"/>
+      <c r="AC156" s="11" t="n"/>
+      <c r="AD156" s="11" t="n"/>
+      <c r="AE156" s="11" t="n"/>
+      <c r="AF156" s="12" t="n"/>
+      <c r="AG156" s="12" t="n"/>
+      <c r="AH156" s="7" t="n"/>
     </row>
     <row r="157">
       <c r="A157" s="6" t="n"/>
@@ -5338,25 +6559,32 @@
       <c r="F157" s="7" t="n"/>
       <c r="G157" s="7" t="n"/>
       <c r="H157" s="7" t="n"/>
-      <c r="I157" s="7" t="n"/>
-      <c r="J157" s="7" t="n"/>
-      <c r="K157" s="7" t="n"/>
+      <c r="I157" s="8" t="n"/>
+      <c r="J157" s="8" t="n"/>
+      <c r="K157" s="8" t="n"/>
       <c r="L157" s="8" t="n"/>
       <c r="M157" s="8" t="n"/>
       <c r="N157" s="8" t="n"/>
       <c r="O157" s="8" t="n"/>
-      <c r="P157" s="9" t="n"/>
-      <c r="Q157" s="9" t="n"/>
+      <c r="P157" s="8" t="n"/>
+      <c r="Q157" s="8" t="n"/>
       <c r="R157" s="9" t="n"/>
       <c r="S157" s="9" t="n"/>
       <c r="T157" s="9" t="n"/>
       <c r="U157" s="9" t="n"/>
-      <c r="V157" s="9" t="n"/>
+      <c r="V157" s="10" t="n"/>
       <c r="W157" s="10" t="n"/>
       <c r="X157" s="10" t="n"/>
       <c r="Y157" s="10" t="n"/>
-      <c r="Z157" s="11" t="n"/>
-      <c r="AA157" s="11" t="n"/>
+      <c r="Z157" s="10" t="n"/>
+      <c r="AA157" s="10" t="n"/>
+      <c r="AB157" s="10" t="n"/>
+      <c r="AC157" s="11" t="n"/>
+      <c r="AD157" s="11" t="n"/>
+      <c r="AE157" s="11" t="n"/>
+      <c r="AF157" s="12" t="n"/>
+      <c r="AG157" s="12" t="n"/>
+      <c r="AH157" s="7" t="n"/>
     </row>
     <row r="158">
       <c r="A158" s="6" t="n"/>
@@ -5366,25 +6594,32 @@
       <c r="F158" s="7" t="n"/>
       <c r="G158" s="7" t="n"/>
       <c r="H158" s="7" t="n"/>
-      <c r="I158" s="7" t="n"/>
-      <c r="J158" s="7" t="n"/>
-      <c r="K158" s="7" t="n"/>
+      <c r="I158" s="8" t="n"/>
+      <c r="J158" s="8" t="n"/>
+      <c r="K158" s="8" t="n"/>
       <c r="L158" s="8" t="n"/>
       <c r="M158" s="8" t="n"/>
       <c r="N158" s="8" t="n"/>
       <c r="O158" s="8" t="n"/>
-      <c r="P158" s="9" t="n"/>
-      <c r="Q158" s="9" t="n"/>
+      <c r="P158" s="8" t="n"/>
+      <c r="Q158" s="8" t="n"/>
       <c r="R158" s="9" t="n"/>
       <c r="S158" s="9" t="n"/>
       <c r="T158" s="9" t="n"/>
       <c r="U158" s="9" t="n"/>
-      <c r="V158" s="9" t="n"/>
+      <c r="V158" s="10" t="n"/>
       <c r="W158" s="10" t="n"/>
       <c r="X158" s="10" t="n"/>
       <c r="Y158" s="10" t="n"/>
-      <c r="Z158" s="11" t="n"/>
-      <c r="AA158" s="11" t="n"/>
+      <c r="Z158" s="10" t="n"/>
+      <c r="AA158" s="10" t="n"/>
+      <c r="AB158" s="10" t="n"/>
+      <c r="AC158" s="11" t="n"/>
+      <c r="AD158" s="11" t="n"/>
+      <c r="AE158" s="11" t="n"/>
+      <c r="AF158" s="12" t="n"/>
+      <c r="AG158" s="12" t="n"/>
+      <c r="AH158" s="7" t="n"/>
     </row>
     <row r="159">
       <c r="A159" s="6" t="n"/>
@@ -5394,25 +6629,32 @@
       <c r="F159" s="7" t="n"/>
       <c r="G159" s="7" t="n"/>
       <c r="H159" s="7" t="n"/>
-      <c r="I159" s="7" t="n"/>
-      <c r="J159" s="7" t="n"/>
-      <c r="K159" s="7" t="n"/>
+      <c r="I159" s="8" t="n"/>
+      <c r="J159" s="8" t="n"/>
+      <c r="K159" s="8" t="n"/>
       <c r="L159" s="8" t="n"/>
       <c r="M159" s="8" t="n"/>
       <c r="N159" s="8" t="n"/>
       <c r="O159" s="8" t="n"/>
-      <c r="P159" s="9" t="n"/>
-      <c r="Q159" s="9" t="n"/>
+      <c r="P159" s="8" t="n"/>
+      <c r="Q159" s="8" t="n"/>
       <c r="R159" s="9" t="n"/>
       <c r="S159" s="9" t="n"/>
       <c r="T159" s="9" t="n"/>
       <c r="U159" s="9" t="n"/>
-      <c r="V159" s="9" t="n"/>
+      <c r="V159" s="10" t="n"/>
       <c r="W159" s="10" t="n"/>
       <c r="X159" s="10" t="n"/>
       <c r="Y159" s="10" t="n"/>
-      <c r="Z159" s="11" t="n"/>
-      <c r="AA159" s="11" t="n"/>
+      <c r="Z159" s="10" t="n"/>
+      <c r="AA159" s="10" t="n"/>
+      <c r="AB159" s="10" t="n"/>
+      <c r="AC159" s="11" t="n"/>
+      <c r="AD159" s="11" t="n"/>
+      <c r="AE159" s="11" t="n"/>
+      <c r="AF159" s="12" t="n"/>
+      <c r="AG159" s="12" t="n"/>
+      <c r="AH159" s="7" t="n"/>
     </row>
     <row r="160">
       <c r="A160" s="6" t="n"/>
@@ -5422,25 +6664,32 @@
       <c r="F160" s="7" t="n"/>
       <c r="G160" s="7" t="n"/>
       <c r="H160" s="7" t="n"/>
-      <c r="I160" s="7" t="n"/>
-      <c r="J160" s="7" t="n"/>
-      <c r="K160" s="7" t="n"/>
+      <c r="I160" s="8" t="n"/>
+      <c r="J160" s="8" t="n"/>
+      <c r="K160" s="8" t="n"/>
       <c r="L160" s="8" t="n"/>
       <c r="M160" s="8" t="n"/>
       <c r="N160" s="8" t="n"/>
       <c r="O160" s="8" t="n"/>
-      <c r="P160" s="9" t="n"/>
-      <c r="Q160" s="9" t="n"/>
+      <c r="P160" s="8" t="n"/>
+      <c r="Q160" s="8" t="n"/>
       <c r="R160" s="9" t="n"/>
       <c r="S160" s="9" t="n"/>
       <c r="T160" s="9" t="n"/>
       <c r="U160" s="9" t="n"/>
-      <c r="V160" s="9" t="n"/>
+      <c r="V160" s="10" t="n"/>
       <c r="W160" s="10" t="n"/>
       <c r="X160" s="10" t="n"/>
       <c r="Y160" s="10" t="n"/>
-      <c r="Z160" s="11" t="n"/>
-      <c r="AA160" s="11" t="n"/>
+      <c r="Z160" s="10" t="n"/>
+      <c r="AA160" s="10" t="n"/>
+      <c r="AB160" s="10" t="n"/>
+      <c r="AC160" s="11" t="n"/>
+      <c r="AD160" s="11" t="n"/>
+      <c r="AE160" s="11" t="n"/>
+      <c r="AF160" s="12" t="n"/>
+      <c r="AG160" s="12" t="n"/>
+      <c r="AH160" s="7" t="n"/>
     </row>
     <row r="161">
       <c r="A161" s="6" t="n"/>
@@ -5450,25 +6699,32 @@
       <c r="F161" s="7" t="n"/>
       <c r="G161" s="7" t="n"/>
       <c r="H161" s="7" t="n"/>
-      <c r="I161" s="7" t="n"/>
-      <c r="J161" s="7" t="n"/>
-      <c r="K161" s="7" t="n"/>
+      <c r="I161" s="8" t="n"/>
+      <c r="J161" s="8" t="n"/>
+      <c r="K161" s="8" t="n"/>
       <c r="L161" s="8" t="n"/>
       <c r="M161" s="8" t="n"/>
       <c r="N161" s="8" t="n"/>
       <c r="O161" s="8" t="n"/>
-      <c r="P161" s="9" t="n"/>
-      <c r="Q161" s="9" t="n"/>
+      <c r="P161" s="8" t="n"/>
+      <c r="Q161" s="8" t="n"/>
       <c r="R161" s="9" t="n"/>
       <c r="S161" s="9" t="n"/>
       <c r="T161" s="9" t="n"/>
       <c r="U161" s="9" t="n"/>
-      <c r="V161" s="9" t="n"/>
+      <c r="V161" s="10" t="n"/>
       <c r="W161" s="10" t="n"/>
       <c r="X161" s="10" t="n"/>
       <c r="Y161" s="10" t="n"/>
-      <c r="Z161" s="11" t="n"/>
-      <c r="AA161" s="11" t="n"/>
+      <c r="Z161" s="10" t="n"/>
+      <c r="AA161" s="10" t="n"/>
+      <c r="AB161" s="10" t="n"/>
+      <c r="AC161" s="11" t="n"/>
+      <c r="AD161" s="11" t="n"/>
+      <c r="AE161" s="11" t="n"/>
+      <c r="AF161" s="12" t="n"/>
+      <c r="AG161" s="12" t="n"/>
+      <c r="AH161" s="7" t="n"/>
     </row>
     <row r="162">
       <c r="A162" s="6" t="n"/>
@@ -5478,25 +6734,32 @@
       <c r="F162" s="7" t="n"/>
       <c r="G162" s="7" t="n"/>
       <c r="H162" s="7" t="n"/>
-      <c r="I162" s="7" t="n"/>
-      <c r="J162" s="7" t="n"/>
-      <c r="K162" s="7" t="n"/>
+      <c r="I162" s="8" t="n"/>
+      <c r="J162" s="8" t="n"/>
+      <c r="K162" s="8" t="n"/>
       <c r="L162" s="8" t="n"/>
       <c r="M162" s="8" t="n"/>
       <c r="N162" s="8" t="n"/>
       <c r="O162" s="8" t="n"/>
-      <c r="P162" s="9" t="n"/>
-      <c r="Q162" s="9" t="n"/>
+      <c r="P162" s="8" t="n"/>
+      <c r="Q162" s="8" t="n"/>
       <c r="R162" s="9" t="n"/>
       <c r="S162" s="9" t="n"/>
       <c r="T162" s="9" t="n"/>
       <c r="U162" s="9" t="n"/>
-      <c r="V162" s="9" t="n"/>
+      <c r="V162" s="10" t="n"/>
       <c r="W162" s="10" t="n"/>
       <c r="X162" s="10" t="n"/>
       <c r="Y162" s="10" t="n"/>
-      <c r="Z162" s="11" t="n"/>
-      <c r="AA162" s="11" t="n"/>
+      <c r="Z162" s="10" t="n"/>
+      <c r="AA162" s="10" t="n"/>
+      <c r="AB162" s="10" t="n"/>
+      <c r="AC162" s="11" t="n"/>
+      <c r="AD162" s="11" t="n"/>
+      <c r="AE162" s="11" t="n"/>
+      <c r="AF162" s="12" t="n"/>
+      <c r="AG162" s="12" t="n"/>
+      <c r="AH162" s="7" t="n"/>
     </row>
     <row r="163">
       <c r="A163" s="6" t="n"/>
@@ -5506,25 +6769,32 @@
       <c r="F163" s="7" t="n"/>
       <c r="G163" s="7" t="n"/>
       <c r="H163" s="7" t="n"/>
-      <c r="I163" s="7" t="n"/>
-      <c r="J163" s="7" t="n"/>
-      <c r="K163" s="7" t="n"/>
+      <c r="I163" s="8" t="n"/>
+      <c r="J163" s="8" t="n"/>
+      <c r="K163" s="8" t="n"/>
       <c r="L163" s="8" t="n"/>
       <c r="M163" s="8" t="n"/>
       <c r="N163" s="8" t="n"/>
       <c r="O163" s="8" t="n"/>
-      <c r="P163" s="9" t="n"/>
-      <c r="Q163" s="9" t="n"/>
+      <c r="P163" s="8" t="n"/>
+      <c r="Q163" s="8" t="n"/>
       <c r="R163" s="9" t="n"/>
       <c r="S163" s="9" t="n"/>
       <c r="T163" s="9" t="n"/>
       <c r="U163" s="9" t="n"/>
-      <c r="V163" s="9" t="n"/>
+      <c r="V163" s="10" t="n"/>
       <c r="W163" s="10" t="n"/>
       <c r="X163" s="10" t="n"/>
       <c r="Y163" s="10" t="n"/>
-      <c r="Z163" s="11" t="n"/>
-      <c r="AA163" s="11" t="n"/>
+      <c r="Z163" s="10" t="n"/>
+      <c r="AA163" s="10" t="n"/>
+      <c r="AB163" s="10" t="n"/>
+      <c r="AC163" s="11" t="n"/>
+      <c r="AD163" s="11" t="n"/>
+      <c r="AE163" s="11" t="n"/>
+      <c r="AF163" s="12" t="n"/>
+      <c r="AG163" s="12" t="n"/>
+      <c r="AH163" s="7" t="n"/>
     </row>
     <row r="164">
       <c r="A164" s="6" t="n"/>
@@ -5534,25 +6804,32 @@
       <c r="F164" s="7" t="n"/>
       <c r="G164" s="7" t="n"/>
       <c r="H164" s="7" t="n"/>
-      <c r="I164" s="7" t="n"/>
-      <c r="J164" s="7" t="n"/>
-      <c r="K164" s="7" t="n"/>
+      <c r="I164" s="8" t="n"/>
+      <c r="J164" s="8" t="n"/>
+      <c r="K164" s="8" t="n"/>
       <c r="L164" s="8" t="n"/>
       <c r="M164" s="8" t="n"/>
       <c r="N164" s="8" t="n"/>
       <c r="O164" s="8" t="n"/>
-      <c r="P164" s="9" t="n"/>
-      <c r="Q164" s="9" t="n"/>
+      <c r="P164" s="8" t="n"/>
+      <c r="Q164" s="8" t="n"/>
       <c r="R164" s="9" t="n"/>
       <c r="S164" s="9" t="n"/>
       <c r="T164" s="9" t="n"/>
       <c r="U164" s="9" t="n"/>
-      <c r="V164" s="9" t="n"/>
+      <c r="V164" s="10" t="n"/>
       <c r="W164" s="10" t="n"/>
       <c r="X164" s="10" t="n"/>
       <c r="Y164" s="10" t="n"/>
-      <c r="Z164" s="11" t="n"/>
-      <c r="AA164" s="11" t="n"/>
+      <c r="Z164" s="10" t="n"/>
+      <c r="AA164" s="10" t="n"/>
+      <c r="AB164" s="10" t="n"/>
+      <c r="AC164" s="11" t="n"/>
+      <c r="AD164" s="11" t="n"/>
+      <c r="AE164" s="11" t="n"/>
+      <c r="AF164" s="12" t="n"/>
+      <c r="AG164" s="12" t="n"/>
+      <c r="AH164" s="7" t="n"/>
     </row>
     <row r="165">
       <c r="A165" s="6" t="n"/>
@@ -5562,25 +6839,32 @@
       <c r="F165" s="7" t="n"/>
       <c r="G165" s="7" t="n"/>
       <c r="H165" s="7" t="n"/>
-      <c r="I165" s="7" t="n"/>
-      <c r="J165" s="7" t="n"/>
-      <c r="K165" s="7" t="n"/>
+      <c r="I165" s="8" t="n"/>
+      <c r="J165" s="8" t="n"/>
+      <c r="K165" s="8" t="n"/>
       <c r="L165" s="8" t="n"/>
       <c r="M165" s="8" t="n"/>
       <c r="N165" s="8" t="n"/>
       <c r="O165" s="8" t="n"/>
-      <c r="P165" s="9" t="n"/>
-      <c r="Q165" s="9" t="n"/>
+      <c r="P165" s="8" t="n"/>
+      <c r="Q165" s="8" t="n"/>
       <c r="R165" s="9" t="n"/>
       <c r="S165" s="9" t="n"/>
       <c r="T165" s="9" t="n"/>
       <c r="U165" s="9" t="n"/>
-      <c r="V165" s="9" t="n"/>
+      <c r="V165" s="10" t="n"/>
       <c r="W165" s="10" t="n"/>
       <c r="X165" s="10" t="n"/>
       <c r="Y165" s="10" t="n"/>
-      <c r="Z165" s="11" t="n"/>
-      <c r="AA165" s="11" t="n"/>
+      <c r="Z165" s="10" t="n"/>
+      <c r="AA165" s="10" t="n"/>
+      <c r="AB165" s="10" t="n"/>
+      <c r="AC165" s="11" t="n"/>
+      <c r="AD165" s="11" t="n"/>
+      <c r="AE165" s="11" t="n"/>
+      <c r="AF165" s="12" t="n"/>
+      <c r="AG165" s="12" t="n"/>
+      <c r="AH165" s="7" t="n"/>
     </row>
     <row r="166">
       <c r="A166" s="6" t="n"/>
@@ -5590,25 +6874,32 @@
       <c r="F166" s="7" t="n"/>
       <c r="G166" s="7" t="n"/>
       <c r="H166" s="7" t="n"/>
-      <c r="I166" s="7" t="n"/>
-      <c r="J166" s="7" t="n"/>
-      <c r="K166" s="7" t="n"/>
+      <c r="I166" s="8" t="n"/>
+      <c r="J166" s="8" t="n"/>
+      <c r="K166" s="8" t="n"/>
       <c r="L166" s="8" t="n"/>
       <c r="M166" s="8" t="n"/>
       <c r="N166" s="8" t="n"/>
       <c r="O166" s="8" t="n"/>
-      <c r="P166" s="9" t="n"/>
-      <c r="Q166" s="9" t="n"/>
+      <c r="P166" s="8" t="n"/>
+      <c r="Q166" s="8" t="n"/>
       <c r="R166" s="9" t="n"/>
       <c r="S166" s="9" t="n"/>
       <c r="T166" s="9" t="n"/>
       <c r="U166" s="9" t="n"/>
-      <c r="V166" s="9" t="n"/>
+      <c r="V166" s="10" t="n"/>
       <c r="W166" s="10" t="n"/>
       <c r="X166" s="10" t="n"/>
       <c r="Y166" s="10" t="n"/>
-      <c r="Z166" s="11" t="n"/>
-      <c r="AA166" s="11" t="n"/>
+      <c r="Z166" s="10" t="n"/>
+      <c r="AA166" s="10" t="n"/>
+      <c r="AB166" s="10" t="n"/>
+      <c r="AC166" s="11" t="n"/>
+      <c r="AD166" s="11" t="n"/>
+      <c r="AE166" s="11" t="n"/>
+      <c r="AF166" s="12" t="n"/>
+      <c r="AG166" s="12" t="n"/>
+      <c r="AH166" s="7" t="n"/>
     </row>
     <row r="167">
       <c r="A167" s="6" t="n"/>
@@ -5618,25 +6909,32 @@
       <c r="F167" s="7" t="n"/>
       <c r="G167" s="7" t="n"/>
       <c r="H167" s="7" t="n"/>
-      <c r="I167" s="7" t="n"/>
-      <c r="J167" s="7" t="n"/>
-      <c r="K167" s="7" t="n"/>
+      <c r="I167" s="8" t="n"/>
+      <c r="J167" s="8" t="n"/>
+      <c r="K167" s="8" t="n"/>
       <c r="L167" s="8" t="n"/>
       <c r="M167" s="8" t="n"/>
       <c r="N167" s="8" t="n"/>
       <c r="O167" s="8" t="n"/>
-      <c r="P167" s="9" t="n"/>
-      <c r="Q167" s="9" t="n"/>
+      <c r="P167" s="8" t="n"/>
+      <c r="Q167" s="8" t="n"/>
       <c r="R167" s="9" t="n"/>
       <c r="S167" s="9" t="n"/>
       <c r="T167" s="9" t="n"/>
       <c r="U167" s="9" t="n"/>
-      <c r="V167" s="9" t="n"/>
+      <c r="V167" s="10" t="n"/>
       <c r="W167" s="10" t="n"/>
       <c r="X167" s="10" t="n"/>
       <c r="Y167" s="10" t="n"/>
-      <c r="Z167" s="11" t="n"/>
-      <c r="AA167" s="11" t="n"/>
+      <c r="Z167" s="10" t="n"/>
+      <c r="AA167" s="10" t="n"/>
+      <c r="AB167" s="10" t="n"/>
+      <c r="AC167" s="11" t="n"/>
+      <c r="AD167" s="11" t="n"/>
+      <c r="AE167" s="11" t="n"/>
+      <c r="AF167" s="12" t="n"/>
+      <c r="AG167" s="12" t="n"/>
+      <c r="AH167" s="7" t="n"/>
     </row>
     <row r="168">
       <c r="A168" s="6" t="n"/>
@@ -5646,25 +6944,32 @@
       <c r="F168" s="7" t="n"/>
       <c r="G168" s="7" t="n"/>
       <c r="H168" s="7" t="n"/>
-      <c r="I168" s="7" t="n"/>
-      <c r="J168" s="7" t="n"/>
-      <c r="K168" s="7" t="n"/>
+      <c r="I168" s="8" t="n"/>
+      <c r="J168" s="8" t="n"/>
+      <c r="K168" s="8" t="n"/>
       <c r="L168" s="8" t="n"/>
       <c r="M168" s="8" t="n"/>
       <c r="N168" s="8" t="n"/>
       <c r="O168" s="8" t="n"/>
-      <c r="P168" s="9" t="n"/>
-      <c r="Q168" s="9" t="n"/>
+      <c r="P168" s="8" t="n"/>
+      <c r="Q168" s="8" t="n"/>
       <c r="R168" s="9" t="n"/>
       <c r="S168" s="9" t="n"/>
       <c r="T168" s="9" t="n"/>
       <c r="U168" s="9" t="n"/>
-      <c r="V168" s="9" t="n"/>
+      <c r="V168" s="10" t="n"/>
       <c r="W168" s="10" t="n"/>
       <c r="X168" s="10" t="n"/>
       <c r="Y168" s="10" t="n"/>
-      <c r="Z168" s="11" t="n"/>
-      <c r="AA168" s="11" t="n"/>
+      <c r="Z168" s="10" t="n"/>
+      <c r="AA168" s="10" t="n"/>
+      <c r="AB168" s="10" t="n"/>
+      <c r="AC168" s="11" t="n"/>
+      <c r="AD168" s="11" t="n"/>
+      <c r="AE168" s="11" t="n"/>
+      <c r="AF168" s="12" t="n"/>
+      <c r="AG168" s="12" t="n"/>
+      <c r="AH168" s="7" t="n"/>
     </row>
     <row r="169">
       <c r="A169" s="6" t="n"/>
@@ -5674,25 +6979,32 @@
       <c r="F169" s="7" t="n"/>
       <c r="G169" s="7" t="n"/>
       <c r="H169" s="7" t="n"/>
-      <c r="I169" s="7" t="n"/>
-      <c r="J169" s="7" t="n"/>
-      <c r="K169" s="7" t="n"/>
+      <c r="I169" s="8" t="n"/>
+      <c r="J169" s="8" t="n"/>
+      <c r="K169" s="8" t="n"/>
       <c r="L169" s="8" t="n"/>
       <c r="M169" s="8" t="n"/>
       <c r="N169" s="8" t="n"/>
       <c r="O169" s="8" t="n"/>
-      <c r="P169" s="9" t="n"/>
-      <c r="Q169" s="9" t="n"/>
+      <c r="P169" s="8" t="n"/>
+      <c r="Q169" s="8" t="n"/>
       <c r="R169" s="9" t="n"/>
       <c r="S169" s="9" t="n"/>
       <c r="T169" s="9" t="n"/>
       <c r="U169" s="9" t="n"/>
-      <c r="V169" s="9" t="n"/>
+      <c r="V169" s="10" t="n"/>
       <c r="W169" s="10" t="n"/>
       <c r="X169" s="10" t="n"/>
       <c r="Y169" s="10" t="n"/>
-      <c r="Z169" s="11" t="n"/>
-      <c r="AA169" s="11" t="n"/>
+      <c r="Z169" s="10" t="n"/>
+      <c r="AA169" s="10" t="n"/>
+      <c r="AB169" s="10" t="n"/>
+      <c r="AC169" s="11" t="n"/>
+      <c r="AD169" s="11" t="n"/>
+      <c r="AE169" s="11" t="n"/>
+      <c r="AF169" s="12" t="n"/>
+      <c r="AG169" s="12" t="n"/>
+      <c r="AH169" s="7" t="n"/>
     </row>
     <row r="170">
       <c r="A170" s="6" t="n"/>
@@ -5702,25 +7014,32 @@
       <c r="F170" s="7" t="n"/>
       <c r="G170" s="7" t="n"/>
       <c r="H170" s="7" t="n"/>
-      <c r="I170" s="7" t="n"/>
-      <c r="J170" s="7" t="n"/>
-      <c r="K170" s="7" t="n"/>
+      <c r="I170" s="8" t="n"/>
+      <c r="J170" s="8" t="n"/>
+      <c r="K170" s="8" t="n"/>
       <c r="L170" s="8" t="n"/>
       <c r="M170" s="8" t="n"/>
       <c r="N170" s="8" t="n"/>
       <c r="O170" s="8" t="n"/>
-      <c r="P170" s="9" t="n"/>
-      <c r="Q170" s="9" t="n"/>
+      <c r="P170" s="8" t="n"/>
+      <c r="Q170" s="8" t="n"/>
       <c r="R170" s="9" t="n"/>
       <c r="S170" s="9" t="n"/>
       <c r="T170" s="9" t="n"/>
       <c r="U170" s="9" t="n"/>
-      <c r="V170" s="9" t="n"/>
+      <c r="V170" s="10" t="n"/>
       <c r="W170" s="10" t="n"/>
       <c r="X170" s="10" t="n"/>
       <c r="Y170" s="10" t="n"/>
-      <c r="Z170" s="11" t="n"/>
-      <c r="AA170" s="11" t="n"/>
+      <c r="Z170" s="10" t="n"/>
+      <c r="AA170" s="10" t="n"/>
+      <c r="AB170" s="10" t="n"/>
+      <c r="AC170" s="11" t="n"/>
+      <c r="AD170" s="11" t="n"/>
+      <c r="AE170" s="11" t="n"/>
+      <c r="AF170" s="12" t="n"/>
+      <c r="AG170" s="12" t="n"/>
+      <c r="AH170" s="7" t="n"/>
     </row>
     <row r="171">
       <c r="A171" s="6" t="n"/>
@@ -5730,25 +7049,32 @@
       <c r="F171" s="7" t="n"/>
       <c r="G171" s="7" t="n"/>
       <c r="H171" s="7" t="n"/>
-      <c r="I171" s="7" t="n"/>
-      <c r="J171" s="7" t="n"/>
-      <c r="K171" s="7" t="n"/>
+      <c r="I171" s="8" t="n"/>
+      <c r="J171" s="8" t="n"/>
+      <c r="K171" s="8" t="n"/>
       <c r="L171" s="8" t="n"/>
       <c r="M171" s="8" t="n"/>
       <c r="N171" s="8" t="n"/>
       <c r="O171" s="8" t="n"/>
-      <c r="P171" s="9" t="n"/>
-      <c r="Q171" s="9" t="n"/>
+      <c r="P171" s="8" t="n"/>
+      <c r="Q171" s="8" t="n"/>
       <c r="R171" s="9" t="n"/>
       <c r="S171" s="9" t="n"/>
       <c r="T171" s="9" t="n"/>
       <c r="U171" s="9" t="n"/>
-      <c r="V171" s="9" t="n"/>
+      <c r="V171" s="10" t="n"/>
       <c r="W171" s="10" t="n"/>
       <c r="X171" s="10" t="n"/>
       <c r="Y171" s="10" t="n"/>
-      <c r="Z171" s="11" t="n"/>
-      <c r="AA171" s="11" t="n"/>
+      <c r="Z171" s="10" t="n"/>
+      <c r="AA171" s="10" t="n"/>
+      <c r="AB171" s="10" t="n"/>
+      <c r="AC171" s="11" t="n"/>
+      <c r="AD171" s="11" t="n"/>
+      <c r="AE171" s="11" t="n"/>
+      <c r="AF171" s="12" t="n"/>
+      <c r="AG171" s="12" t="n"/>
+      <c r="AH171" s="7" t="n"/>
     </row>
     <row r="172">
       <c r="A172" s="6" t="n"/>
@@ -5758,25 +7084,32 @@
       <c r="F172" s="7" t="n"/>
       <c r="G172" s="7" t="n"/>
       <c r="H172" s="7" t="n"/>
-      <c r="I172" s="7" t="n"/>
-      <c r="J172" s="7" t="n"/>
-      <c r="K172" s="7" t="n"/>
+      <c r="I172" s="8" t="n"/>
+      <c r="J172" s="8" t="n"/>
+      <c r="K172" s="8" t="n"/>
       <c r="L172" s="8" t="n"/>
       <c r="M172" s="8" t="n"/>
       <c r="N172" s="8" t="n"/>
       <c r="O172" s="8" t="n"/>
-      <c r="P172" s="9" t="n"/>
-      <c r="Q172" s="9" t="n"/>
+      <c r="P172" s="8" t="n"/>
+      <c r="Q172" s="8" t="n"/>
       <c r="R172" s="9" t="n"/>
       <c r="S172" s="9" t="n"/>
       <c r="T172" s="9" t="n"/>
       <c r="U172" s="9" t="n"/>
-      <c r="V172" s="9" t="n"/>
+      <c r="V172" s="10" t="n"/>
       <c r="W172" s="10" t="n"/>
       <c r="X172" s="10" t="n"/>
       <c r="Y172" s="10" t="n"/>
-      <c r="Z172" s="11" t="n"/>
-      <c r="AA172" s="11" t="n"/>
+      <c r="Z172" s="10" t="n"/>
+      <c r="AA172" s="10" t="n"/>
+      <c r="AB172" s="10" t="n"/>
+      <c r="AC172" s="11" t="n"/>
+      <c r="AD172" s="11" t="n"/>
+      <c r="AE172" s="11" t="n"/>
+      <c r="AF172" s="12" t="n"/>
+      <c r="AG172" s="12" t="n"/>
+      <c r="AH172" s="7" t="n"/>
     </row>
     <row r="173">
       <c r="A173" s="6" t="n"/>
@@ -5786,25 +7119,32 @@
       <c r="F173" s="7" t="n"/>
       <c r="G173" s="7" t="n"/>
       <c r="H173" s="7" t="n"/>
-      <c r="I173" s="7" t="n"/>
-      <c r="J173" s="7" t="n"/>
-      <c r="K173" s="7" t="n"/>
+      <c r="I173" s="8" t="n"/>
+      <c r="J173" s="8" t="n"/>
+      <c r="K173" s="8" t="n"/>
       <c r="L173" s="8" t="n"/>
       <c r="M173" s="8" t="n"/>
       <c r="N173" s="8" t="n"/>
       <c r="O173" s="8" t="n"/>
-      <c r="P173" s="9" t="n"/>
-      <c r="Q173" s="9" t="n"/>
+      <c r="P173" s="8" t="n"/>
+      <c r="Q173" s="8" t="n"/>
       <c r="R173" s="9" t="n"/>
       <c r="S173" s="9" t="n"/>
       <c r="T173" s="9" t="n"/>
       <c r="U173" s="9" t="n"/>
-      <c r="V173" s="9" t="n"/>
+      <c r="V173" s="10" t="n"/>
       <c r="W173" s="10" t="n"/>
       <c r="X173" s="10" t="n"/>
       <c r="Y173" s="10" t="n"/>
-      <c r="Z173" s="11" t="n"/>
-      <c r="AA173" s="11" t="n"/>
+      <c r="Z173" s="10" t="n"/>
+      <c r="AA173" s="10" t="n"/>
+      <c r="AB173" s="10" t="n"/>
+      <c r="AC173" s="11" t="n"/>
+      <c r="AD173" s="11" t="n"/>
+      <c r="AE173" s="11" t="n"/>
+      <c r="AF173" s="12" t="n"/>
+      <c r="AG173" s="12" t="n"/>
+      <c r="AH173" s="7" t="n"/>
     </row>
     <row r="174">
       <c r="A174" s="6" t="n"/>
@@ -5814,25 +7154,32 @@
       <c r="F174" s="7" t="n"/>
       <c r="G174" s="7" t="n"/>
       <c r="H174" s="7" t="n"/>
-      <c r="I174" s="7" t="n"/>
-      <c r="J174" s="7" t="n"/>
-      <c r="K174" s="7" t="n"/>
+      <c r="I174" s="8" t="n"/>
+      <c r="J174" s="8" t="n"/>
+      <c r="K174" s="8" t="n"/>
       <c r="L174" s="8" t="n"/>
       <c r="M174" s="8" t="n"/>
       <c r="N174" s="8" t="n"/>
       <c r="O174" s="8" t="n"/>
-      <c r="P174" s="9" t="n"/>
-      <c r="Q174" s="9" t="n"/>
+      <c r="P174" s="8" t="n"/>
+      <c r="Q174" s="8" t="n"/>
       <c r="R174" s="9" t="n"/>
       <c r="S174" s="9" t="n"/>
       <c r="T174" s="9" t="n"/>
       <c r="U174" s="9" t="n"/>
-      <c r="V174" s="9" t="n"/>
+      <c r="V174" s="10" t="n"/>
       <c r="W174" s="10" t="n"/>
       <c r="X174" s="10" t="n"/>
       <c r="Y174" s="10" t="n"/>
-      <c r="Z174" s="11" t="n"/>
-      <c r="AA174" s="11" t="n"/>
+      <c r="Z174" s="10" t="n"/>
+      <c r="AA174" s="10" t="n"/>
+      <c r="AB174" s="10" t="n"/>
+      <c r="AC174" s="11" t="n"/>
+      <c r="AD174" s="11" t="n"/>
+      <c r="AE174" s="11" t="n"/>
+      <c r="AF174" s="12" t="n"/>
+      <c r="AG174" s="12" t="n"/>
+      <c r="AH174" s="7" t="n"/>
     </row>
     <row r="175">
       <c r="A175" s="6" t="n"/>
@@ -5842,25 +7189,32 @@
       <c r="F175" s="7" t="n"/>
       <c r="G175" s="7" t="n"/>
       <c r="H175" s="7" t="n"/>
-      <c r="I175" s="7" t="n"/>
-      <c r="J175" s="7" t="n"/>
-      <c r="K175" s="7" t="n"/>
+      <c r="I175" s="8" t="n"/>
+      <c r="J175" s="8" t="n"/>
+      <c r="K175" s="8" t="n"/>
       <c r="L175" s="8" t="n"/>
       <c r="M175" s="8" t="n"/>
       <c r="N175" s="8" t="n"/>
       <c r="O175" s="8" t="n"/>
-      <c r="P175" s="9" t="n"/>
-      <c r="Q175" s="9" t="n"/>
+      <c r="P175" s="8" t="n"/>
+      <c r="Q175" s="8" t="n"/>
       <c r="R175" s="9" t="n"/>
       <c r="S175" s="9" t="n"/>
       <c r="T175" s="9" t="n"/>
       <c r="U175" s="9" t="n"/>
-      <c r="V175" s="9" t="n"/>
+      <c r="V175" s="10" t="n"/>
       <c r="W175" s="10" t="n"/>
       <c r="X175" s="10" t="n"/>
       <c r="Y175" s="10" t="n"/>
-      <c r="Z175" s="11" t="n"/>
-      <c r="AA175" s="11" t="n"/>
+      <c r="Z175" s="10" t="n"/>
+      <c r="AA175" s="10" t="n"/>
+      <c r="AB175" s="10" t="n"/>
+      <c r="AC175" s="11" t="n"/>
+      <c r="AD175" s="11" t="n"/>
+      <c r="AE175" s="11" t="n"/>
+      <c r="AF175" s="12" t="n"/>
+      <c r="AG175" s="12" t="n"/>
+      <c r="AH175" s="7" t="n"/>
     </row>
     <row r="176">
       <c r="A176" s="6" t="n"/>
@@ -5870,25 +7224,32 @@
       <c r="F176" s="7" t="n"/>
       <c r="G176" s="7" t="n"/>
       <c r="H176" s="7" t="n"/>
-      <c r="I176" s="7" t="n"/>
-      <c r="J176" s="7" t="n"/>
-      <c r="K176" s="7" t="n"/>
+      <c r="I176" s="8" t="n"/>
+      <c r="J176" s="8" t="n"/>
+      <c r="K176" s="8" t="n"/>
       <c r="L176" s="8" t="n"/>
       <c r="M176" s="8" t="n"/>
       <c r="N176" s="8" t="n"/>
       <c r="O176" s="8" t="n"/>
-      <c r="P176" s="9" t="n"/>
-      <c r="Q176" s="9" t="n"/>
+      <c r="P176" s="8" t="n"/>
+      <c r="Q176" s="8" t="n"/>
       <c r="R176" s="9" t="n"/>
       <c r="S176" s="9" t="n"/>
       <c r="T176" s="9" t="n"/>
       <c r="U176" s="9" t="n"/>
-      <c r="V176" s="9" t="n"/>
+      <c r="V176" s="10" t="n"/>
       <c r="W176" s="10" t="n"/>
       <c r="X176" s="10" t="n"/>
       <c r="Y176" s="10" t="n"/>
-      <c r="Z176" s="11" t="n"/>
-      <c r="AA176" s="11" t="n"/>
+      <c r="Z176" s="10" t="n"/>
+      <c r="AA176" s="10" t="n"/>
+      <c r="AB176" s="10" t="n"/>
+      <c r="AC176" s="11" t="n"/>
+      <c r="AD176" s="11" t="n"/>
+      <c r="AE176" s="11" t="n"/>
+      <c r="AF176" s="12" t="n"/>
+      <c r="AG176" s="12" t="n"/>
+      <c r="AH176" s="7" t="n"/>
     </row>
     <row r="177">
       <c r="A177" s="6" t="n"/>
@@ -5898,25 +7259,32 @@
       <c r="F177" s="7" t="n"/>
       <c r="G177" s="7" t="n"/>
       <c r="H177" s="7" t="n"/>
-      <c r="I177" s="7" t="n"/>
-      <c r="J177" s="7" t="n"/>
-      <c r="K177" s="7" t="n"/>
+      <c r="I177" s="8" t="n"/>
+      <c r="J177" s="8" t="n"/>
+      <c r="K177" s="8" t="n"/>
       <c r="L177" s="8" t="n"/>
       <c r="M177" s="8" t="n"/>
       <c r="N177" s="8" t="n"/>
       <c r="O177" s="8" t="n"/>
-      <c r="P177" s="9" t="n"/>
-      <c r="Q177" s="9" t="n"/>
+      <c r="P177" s="8" t="n"/>
+      <c r="Q177" s="8" t="n"/>
       <c r="R177" s="9" t="n"/>
       <c r="S177" s="9" t="n"/>
       <c r="T177" s="9" t="n"/>
       <c r="U177" s="9" t="n"/>
-      <c r="V177" s="9" t="n"/>
+      <c r="V177" s="10" t="n"/>
       <c r="W177" s="10" t="n"/>
       <c r="X177" s="10" t="n"/>
       <c r="Y177" s="10" t="n"/>
-      <c r="Z177" s="11" t="n"/>
-      <c r="AA177" s="11" t="n"/>
+      <c r="Z177" s="10" t="n"/>
+      <c r="AA177" s="10" t="n"/>
+      <c r="AB177" s="10" t="n"/>
+      <c r="AC177" s="11" t="n"/>
+      <c r="AD177" s="11" t="n"/>
+      <c r="AE177" s="11" t="n"/>
+      <c r="AF177" s="12" t="n"/>
+      <c r="AG177" s="12" t="n"/>
+      <c r="AH177" s="7" t="n"/>
     </row>
     <row r="178">
       <c r="A178" s="6" t="n"/>
@@ -5926,25 +7294,32 @@
       <c r="F178" s="7" t="n"/>
       <c r="G178" s="7" t="n"/>
       <c r="H178" s="7" t="n"/>
-      <c r="I178" s="7" t="n"/>
-      <c r="J178" s="7" t="n"/>
-      <c r="K178" s="7" t="n"/>
+      <c r="I178" s="8" t="n"/>
+      <c r="J178" s="8" t="n"/>
+      <c r="K178" s="8" t="n"/>
       <c r="L178" s="8" t="n"/>
       <c r="M178" s="8" t="n"/>
       <c r="N178" s="8" t="n"/>
       <c r="O178" s="8" t="n"/>
-      <c r="P178" s="9" t="n"/>
-      <c r="Q178" s="9" t="n"/>
+      <c r="P178" s="8" t="n"/>
+      <c r="Q178" s="8" t="n"/>
       <c r="R178" s="9" t="n"/>
       <c r="S178" s="9" t="n"/>
       <c r="T178" s="9" t="n"/>
       <c r="U178" s="9" t="n"/>
-      <c r="V178" s="9" t="n"/>
+      <c r="V178" s="10" t="n"/>
       <c r="W178" s="10" t="n"/>
       <c r="X178" s="10" t="n"/>
       <c r="Y178" s="10" t="n"/>
-      <c r="Z178" s="11" t="n"/>
-      <c r="AA178" s="11" t="n"/>
+      <c r="Z178" s="10" t="n"/>
+      <c r="AA178" s="10" t="n"/>
+      <c r="AB178" s="10" t="n"/>
+      <c r="AC178" s="11" t="n"/>
+      <c r="AD178" s="11" t="n"/>
+      <c r="AE178" s="11" t="n"/>
+      <c r="AF178" s="12" t="n"/>
+      <c r="AG178" s="12" t="n"/>
+      <c r="AH178" s="7" t="n"/>
     </row>
     <row r="179">
       <c r="A179" s="6" t="n"/>
@@ -5954,25 +7329,32 @@
       <c r="F179" s="7" t="n"/>
       <c r="G179" s="7" t="n"/>
       <c r="H179" s="7" t="n"/>
-      <c r="I179" s="7" t="n"/>
-      <c r="J179" s="7" t="n"/>
-      <c r="K179" s="7" t="n"/>
+      <c r="I179" s="8" t="n"/>
+      <c r="J179" s="8" t="n"/>
+      <c r="K179" s="8" t="n"/>
       <c r="L179" s="8" t="n"/>
       <c r="M179" s="8" t="n"/>
       <c r="N179" s="8" t="n"/>
       <c r="O179" s="8" t="n"/>
-      <c r="P179" s="9" t="n"/>
-      <c r="Q179" s="9" t="n"/>
+      <c r="P179" s="8" t="n"/>
+      <c r="Q179" s="8" t="n"/>
       <c r="R179" s="9" t="n"/>
       <c r="S179" s="9" t="n"/>
       <c r="T179" s="9" t="n"/>
       <c r="U179" s="9" t="n"/>
-      <c r="V179" s="9" t="n"/>
+      <c r="V179" s="10" t="n"/>
       <c r="W179" s="10" t="n"/>
       <c r="X179" s="10" t="n"/>
       <c r="Y179" s="10" t="n"/>
-      <c r="Z179" s="11" t="n"/>
-      <c r="AA179" s="11" t="n"/>
+      <c r="Z179" s="10" t="n"/>
+      <c r="AA179" s="10" t="n"/>
+      <c r="AB179" s="10" t="n"/>
+      <c r="AC179" s="11" t="n"/>
+      <c r="AD179" s="11" t="n"/>
+      <c r="AE179" s="11" t="n"/>
+      <c r="AF179" s="12" t="n"/>
+      <c r="AG179" s="12" t="n"/>
+      <c r="AH179" s="7" t="n"/>
     </row>
     <row r="180">
       <c r="A180" s="6" t="n"/>
@@ -5982,25 +7364,32 @@
       <c r="F180" s="7" t="n"/>
       <c r="G180" s="7" t="n"/>
       <c r="H180" s="7" t="n"/>
-      <c r="I180" s="7" t="n"/>
-      <c r="J180" s="7" t="n"/>
-      <c r="K180" s="7" t="n"/>
+      <c r="I180" s="8" t="n"/>
+      <c r="J180" s="8" t="n"/>
+      <c r="K180" s="8" t="n"/>
       <c r="L180" s="8" t="n"/>
       <c r="M180" s="8" t="n"/>
       <c r="N180" s="8" t="n"/>
       <c r="O180" s="8" t="n"/>
-      <c r="P180" s="9" t="n"/>
-      <c r="Q180" s="9" t="n"/>
+      <c r="P180" s="8" t="n"/>
+      <c r="Q180" s="8" t="n"/>
       <c r="R180" s="9" t="n"/>
       <c r="S180" s="9" t="n"/>
       <c r="T180" s="9" t="n"/>
       <c r="U180" s="9" t="n"/>
-      <c r="V180" s="9" t="n"/>
+      <c r="V180" s="10" t="n"/>
       <c r="W180" s="10" t="n"/>
       <c r="X180" s="10" t="n"/>
       <c r="Y180" s="10" t="n"/>
-      <c r="Z180" s="11" t="n"/>
-      <c r="AA180" s="11" t="n"/>
+      <c r="Z180" s="10" t="n"/>
+      <c r="AA180" s="10" t="n"/>
+      <c r="AB180" s="10" t="n"/>
+      <c r="AC180" s="11" t="n"/>
+      <c r="AD180" s="11" t="n"/>
+      <c r="AE180" s="11" t="n"/>
+      <c r="AF180" s="12" t="n"/>
+      <c r="AG180" s="12" t="n"/>
+      <c r="AH180" s="7" t="n"/>
     </row>
     <row r="181">
       <c r="A181" s="6" t="n"/>
@@ -6010,25 +7399,32 @@
       <c r="F181" s="7" t="n"/>
       <c r="G181" s="7" t="n"/>
       <c r="H181" s="7" t="n"/>
-      <c r="I181" s="7" t="n"/>
-      <c r="J181" s="7" t="n"/>
-      <c r="K181" s="7" t="n"/>
+      <c r="I181" s="8" t="n"/>
+      <c r="J181" s="8" t="n"/>
+      <c r="K181" s="8" t="n"/>
       <c r="L181" s="8" t="n"/>
       <c r="M181" s="8" t="n"/>
       <c r="N181" s="8" t="n"/>
       <c r="O181" s="8" t="n"/>
-      <c r="P181" s="9" t="n"/>
-      <c r="Q181" s="9" t="n"/>
+      <c r="P181" s="8" t="n"/>
+      <c r="Q181" s="8" t="n"/>
       <c r="R181" s="9" t="n"/>
       <c r="S181" s="9" t="n"/>
       <c r="T181" s="9" t="n"/>
       <c r="U181" s="9" t="n"/>
-      <c r="V181" s="9" t="n"/>
+      <c r="V181" s="10" t="n"/>
       <c r="W181" s="10" t="n"/>
       <c r="X181" s="10" t="n"/>
       <c r="Y181" s="10" t="n"/>
-      <c r="Z181" s="11" t="n"/>
-      <c r="AA181" s="11" t="n"/>
+      <c r="Z181" s="10" t="n"/>
+      <c r="AA181" s="10" t="n"/>
+      <c r="AB181" s="10" t="n"/>
+      <c r="AC181" s="11" t="n"/>
+      <c r="AD181" s="11" t="n"/>
+      <c r="AE181" s="11" t="n"/>
+      <c r="AF181" s="12" t="n"/>
+      <c r="AG181" s="12" t="n"/>
+      <c r="AH181" s="7" t="n"/>
     </row>
     <row r="182">
       <c r="A182" s="6" t="n"/>
@@ -6038,25 +7434,32 @@
       <c r="F182" s="7" t="n"/>
       <c r="G182" s="7" t="n"/>
       <c r="H182" s="7" t="n"/>
-      <c r="I182" s="7" t="n"/>
-      <c r="J182" s="7" t="n"/>
-      <c r="K182" s="7" t="n"/>
+      <c r="I182" s="8" t="n"/>
+      <c r="J182" s="8" t="n"/>
+      <c r="K182" s="8" t="n"/>
       <c r="L182" s="8" t="n"/>
       <c r="M182" s="8" t="n"/>
       <c r="N182" s="8" t="n"/>
       <c r="O182" s="8" t="n"/>
-      <c r="P182" s="9" t="n"/>
-      <c r="Q182" s="9" t="n"/>
+      <c r="P182" s="8" t="n"/>
+      <c r="Q182" s="8" t="n"/>
       <c r="R182" s="9" t="n"/>
       <c r="S182" s="9" t="n"/>
       <c r="T182" s="9" t="n"/>
       <c r="U182" s="9" t="n"/>
-      <c r="V182" s="9" t="n"/>
+      <c r="V182" s="10" t="n"/>
       <c r="W182" s="10" t="n"/>
       <c r="X182" s="10" t="n"/>
       <c r="Y182" s="10" t="n"/>
-      <c r="Z182" s="11" t="n"/>
-      <c r="AA182" s="11" t="n"/>
+      <c r="Z182" s="10" t="n"/>
+      <c r="AA182" s="10" t="n"/>
+      <c r="AB182" s="10" t="n"/>
+      <c r="AC182" s="11" t="n"/>
+      <c r="AD182" s="11" t="n"/>
+      <c r="AE182" s="11" t="n"/>
+      <c r="AF182" s="12" t="n"/>
+      <c r="AG182" s="12" t="n"/>
+      <c r="AH182" s="7" t="n"/>
     </row>
     <row r="183">
       <c r="A183" s="6" t="n"/>
@@ -6066,25 +7469,32 @@
       <c r="F183" s="7" t="n"/>
       <c r="G183" s="7" t="n"/>
       <c r="H183" s="7" t="n"/>
-      <c r="I183" s="7" t="n"/>
-      <c r="J183" s="7" t="n"/>
-      <c r="K183" s="7" t="n"/>
+      <c r="I183" s="8" t="n"/>
+      <c r="J183" s="8" t="n"/>
+      <c r="K183" s="8" t="n"/>
       <c r="L183" s="8" t="n"/>
       <c r="M183" s="8" t="n"/>
       <c r="N183" s="8" t="n"/>
       <c r="O183" s="8" t="n"/>
-      <c r="P183" s="9" t="n"/>
-      <c r="Q183" s="9" t="n"/>
+      <c r="P183" s="8" t="n"/>
+      <c r="Q183" s="8" t="n"/>
       <c r="R183" s="9" t="n"/>
       <c r="S183" s="9" t="n"/>
       <c r="T183" s="9" t="n"/>
       <c r="U183" s="9" t="n"/>
-      <c r="V183" s="9" t="n"/>
+      <c r="V183" s="10" t="n"/>
       <c r="W183" s="10" t="n"/>
       <c r="X183" s="10" t="n"/>
       <c r="Y183" s="10" t="n"/>
-      <c r="Z183" s="11" t="n"/>
-      <c r="AA183" s="11" t="n"/>
+      <c r="Z183" s="10" t="n"/>
+      <c r="AA183" s="10" t="n"/>
+      <c r="AB183" s="10" t="n"/>
+      <c r="AC183" s="11" t="n"/>
+      <c r="AD183" s="11" t="n"/>
+      <c r="AE183" s="11" t="n"/>
+      <c r="AF183" s="12" t="n"/>
+      <c r="AG183" s="12" t="n"/>
+      <c r="AH183" s="7" t="n"/>
     </row>
     <row r="184">
       <c r="A184" s="6" t="n"/>
@@ -6094,25 +7504,32 @@
       <c r="F184" s="7" t="n"/>
       <c r="G184" s="7" t="n"/>
       <c r="H184" s="7" t="n"/>
-      <c r="I184" s="7" t="n"/>
-      <c r="J184" s="7" t="n"/>
-      <c r="K184" s="7" t="n"/>
+      <c r="I184" s="8" t="n"/>
+      <c r="J184" s="8" t="n"/>
+      <c r="K184" s="8" t="n"/>
       <c r="L184" s="8" t="n"/>
       <c r="M184" s="8" t="n"/>
       <c r="N184" s="8" t="n"/>
       <c r="O184" s="8" t="n"/>
-      <c r="P184" s="9" t="n"/>
-      <c r="Q184" s="9" t="n"/>
+      <c r="P184" s="8" t="n"/>
+      <c r="Q184" s="8" t="n"/>
       <c r="R184" s="9" t="n"/>
       <c r="S184" s="9" t="n"/>
       <c r="T184" s="9" t="n"/>
       <c r="U184" s="9" t="n"/>
-      <c r="V184" s="9" t="n"/>
+      <c r="V184" s="10" t="n"/>
       <c r="W184" s="10" t="n"/>
       <c r="X184" s="10" t="n"/>
       <c r="Y184" s="10" t="n"/>
-      <c r="Z184" s="11" t="n"/>
-      <c r="AA184" s="11" t="n"/>
+      <c r="Z184" s="10" t="n"/>
+      <c r="AA184" s="10" t="n"/>
+      <c r="AB184" s="10" t="n"/>
+      <c r="AC184" s="11" t="n"/>
+      <c r="AD184" s="11" t="n"/>
+      <c r="AE184" s="11" t="n"/>
+      <c r="AF184" s="12" t="n"/>
+      <c r="AG184" s="12" t="n"/>
+      <c r="AH184" s="7" t="n"/>
     </row>
     <row r="185">
       <c r="A185" s="6" t="n"/>
@@ -6122,25 +7539,32 @@
       <c r="F185" s="7" t="n"/>
       <c r="G185" s="7" t="n"/>
       <c r="H185" s="7" t="n"/>
-      <c r="I185" s="7" t="n"/>
-      <c r="J185" s="7" t="n"/>
-      <c r="K185" s="7" t="n"/>
+      <c r="I185" s="8" t="n"/>
+      <c r="J185" s="8" t="n"/>
+      <c r="K185" s="8" t="n"/>
       <c r="L185" s="8" t="n"/>
       <c r="M185" s="8" t="n"/>
       <c r="N185" s="8" t="n"/>
       <c r="O185" s="8" t="n"/>
-      <c r="P185" s="9" t="n"/>
-      <c r="Q185" s="9" t="n"/>
+      <c r="P185" s="8" t="n"/>
+      <c r="Q185" s="8" t="n"/>
       <c r="R185" s="9" t="n"/>
       <c r="S185" s="9" t="n"/>
       <c r="T185" s="9" t="n"/>
       <c r="U185" s="9" t="n"/>
-      <c r="V185" s="9" t="n"/>
+      <c r="V185" s="10" t="n"/>
       <c r="W185" s="10" t="n"/>
       <c r="X185" s="10" t="n"/>
       <c r="Y185" s="10" t="n"/>
-      <c r="Z185" s="11" t="n"/>
-      <c r="AA185" s="11" t="n"/>
+      <c r="Z185" s="10" t="n"/>
+      <c r="AA185" s="10" t="n"/>
+      <c r="AB185" s="10" t="n"/>
+      <c r="AC185" s="11" t="n"/>
+      <c r="AD185" s="11" t="n"/>
+      <c r="AE185" s="11" t="n"/>
+      <c r="AF185" s="12" t="n"/>
+      <c r="AG185" s="12" t="n"/>
+      <c r="AH185" s="7" t="n"/>
     </row>
     <row r="186">
       <c r="A186" s="6" t="n"/>
@@ -6150,25 +7574,32 @@
       <c r="F186" s="7" t="n"/>
       <c r="G186" s="7" t="n"/>
       <c r="H186" s="7" t="n"/>
-      <c r="I186" s="7" t="n"/>
-      <c r="J186" s="7" t="n"/>
-      <c r="K186" s="7" t="n"/>
+      <c r="I186" s="8" t="n"/>
+      <c r="J186" s="8" t="n"/>
+      <c r="K186" s="8" t="n"/>
       <c r="L186" s="8" t="n"/>
       <c r="M186" s="8" t="n"/>
       <c r="N186" s="8" t="n"/>
       <c r="O186" s="8" t="n"/>
-      <c r="P186" s="9" t="n"/>
-      <c r="Q186" s="9" t="n"/>
+      <c r="P186" s="8" t="n"/>
+      <c r="Q186" s="8" t="n"/>
       <c r="R186" s="9" t="n"/>
       <c r="S186" s="9" t="n"/>
       <c r="T186" s="9" t="n"/>
       <c r="U186" s="9" t="n"/>
-      <c r="V186" s="9" t="n"/>
+      <c r="V186" s="10" t="n"/>
       <c r="W186" s="10" t="n"/>
       <c r="X186" s="10" t="n"/>
       <c r="Y186" s="10" t="n"/>
-      <c r="Z186" s="11" t="n"/>
-      <c r="AA186" s="11" t="n"/>
+      <c r="Z186" s="10" t="n"/>
+      <c r="AA186" s="10" t="n"/>
+      <c r="AB186" s="10" t="n"/>
+      <c r="AC186" s="11" t="n"/>
+      <c r="AD186" s="11" t="n"/>
+      <c r="AE186" s="11" t="n"/>
+      <c r="AF186" s="12" t="n"/>
+      <c r="AG186" s="12" t="n"/>
+      <c r="AH186" s="7" t="n"/>
     </row>
     <row r="187">
       <c r="A187" s="6" t="n"/>
@@ -6178,25 +7609,32 @@
       <c r="F187" s="7" t="n"/>
       <c r="G187" s="7" t="n"/>
       <c r="H187" s="7" t="n"/>
-      <c r="I187" s="7" t="n"/>
-      <c r="J187" s="7" t="n"/>
-      <c r="K187" s="7" t="n"/>
+      <c r="I187" s="8" t="n"/>
+      <c r="J187" s="8" t="n"/>
+      <c r="K187" s="8" t="n"/>
       <c r="L187" s="8" t="n"/>
       <c r="M187" s="8" t="n"/>
       <c r="N187" s="8" t="n"/>
       <c r="O187" s="8" t="n"/>
-      <c r="P187" s="9" t="n"/>
-      <c r="Q187" s="9" t="n"/>
+      <c r="P187" s="8" t="n"/>
+      <c r="Q187" s="8" t="n"/>
       <c r="R187" s="9" t="n"/>
       <c r="S187" s="9" t="n"/>
       <c r="T187" s="9" t="n"/>
       <c r="U187" s="9" t="n"/>
-      <c r="V187" s="9" t="n"/>
+      <c r="V187" s="10" t="n"/>
       <c r="W187" s="10" t="n"/>
       <c r="X187" s="10" t="n"/>
       <c r="Y187" s="10" t="n"/>
-      <c r="Z187" s="11" t="n"/>
-      <c r="AA187" s="11" t="n"/>
+      <c r="Z187" s="10" t="n"/>
+      <c r="AA187" s="10" t="n"/>
+      <c r="AB187" s="10" t="n"/>
+      <c r="AC187" s="11" t="n"/>
+      <c r="AD187" s="11" t="n"/>
+      <c r="AE187" s="11" t="n"/>
+      <c r="AF187" s="12" t="n"/>
+      <c r="AG187" s="12" t="n"/>
+      <c r="AH187" s="7" t="n"/>
     </row>
     <row r="188">
       <c r="A188" s="6" t="n"/>
@@ -6206,25 +7644,32 @@
       <c r="F188" s="7" t="n"/>
       <c r="G188" s="7" t="n"/>
       <c r="H188" s="7" t="n"/>
-      <c r="I188" s="7" t="n"/>
-      <c r="J188" s="7" t="n"/>
-      <c r="K188" s="7" t="n"/>
+      <c r="I188" s="8" t="n"/>
+      <c r="J188" s="8" t="n"/>
+      <c r="K188" s="8" t="n"/>
       <c r="L188" s="8" t="n"/>
       <c r="M188" s="8" t="n"/>
       <c r="N188" s="8" t="n"/>
       <c r="O188" s="8" t="n"/>
-      <c r="P188" s="9" t="n"/>
-      <c r="Q188" s="9" t="n"/>
+      <c r="P188" s="8" t="n"/>
+      <c r="Q188" s="8" t="n"/>
       <c r="R188" s="9" t="n"/>
       <c r="S188" s="9" t="n"/>
       <c r="T188" s="9" t="n"/>
       <c r="U188" s="9" t="n"/>
-      <c r="V188" s="9" t="n"/>
+      <c r="V188" s="10" t="n"/>
       <c r="W188" s="10" t="n"/>
       <c r="X188" s="10" t="n"/>
       <c r="Y188" s="10" t="n"/>
-      <c r="Z188" s="11" t="n"/>
-      <c r="AA188" s="11" t="n"/>
+      <c r="Z188" s="10" t="n"/>
+      <c r="AA188" s="10" t="n"/>
+      <c r="AB188" s="10" t="n"/>
+      <c r="AC188" s="11" t="n"/>
+      <c r="AD188" s="11" t="n"/>
+      <c r="AE188" s="11" t="n"/>
+      <c r="AF188" s="12" t="n"/>
+      <c r="AG188" s="12" t="n"/>
+      <c r="AH188" s="7" t="n"/>
     </row>
     <row r="189">
       <c r="A189" s="6" t="n"/>
@@ -6234,25 +7679,32 @@
       <c r="F189" s="7" t="n"/>
       <c r="G189" s="7" t="n"/>
       <c r="H189" s="7" t="n"/>
-      <c r="I189" s="7" t="n"/>
-      <c r="J189" s="7" t="n"/>
-      <c r="K189" s="7" t="n"/>
+      <c r="I189" s="8" t="n"/>
+      <c r="J189" s="8" t="n"/>
+      <c r="K189" s="8" t="n"/>
       <c r="L189" s="8" t="n"/>
       <c r="M189" s="8" t="n"/>
       <c r="N189" s="8" t="n"/>
       <c r="O189" s="8" t="n"/>
-      <c r="P189" s="9" t="n"/>
-      <c r="Q189" s="9" t="n"/>
+      <c r="P189" s="8" t="n"/>
+      <c r="Q189" s="8" t="n"/>
       <c r="R189" s="9" t="n"/>
       <c r="S189" s="9" t="n"/>
       <c r="T189" s="9" t="n"/>
       <c r="U189" s="9" t="n"/>
-      <c r="V189" s="9" t="n"/>
+      <c r="V189" s="10" t="n"/>
       <c r="W189" s="10" t="n"/>
       <c r="X189" s="10" t="n"/>
       <c r="Y189" s="10" t="n"/>
-      <c r="Z189" s="11" t="n"/>
-      <c r="AA189" s="11" t="n"/>
+      <c r="Z189" s="10" t="n"/>
+      <c r="AA189" s="10" t="n"/>
+      <c r="AB189" s="10" t="n"/>
+      <c r="AC189" s="11" t="n"/>
+      <c r="AD189" s="11" t="n"/>
+      <c r="AE189" s="11" t="n"/>
+      <c r="AF189" s="12" t="n"/>
+      <c r="AG189" s="12" t="n"/>
+      <c r="AH189" s="7" t="n"/>
     </row>
     <row r="190">
       <c r="A190" s="6" t="n"/>
@@ -6262,25 +7714,32 @@
       <c r="F190" s="7" t="n"/>
       <c r="G190" s="7" t="n"/>
       <c r="H190" s="7" t="n"/>
-      <c r="I190" s="7" t="n"/>
-      <c r="J190" s="7" t="n"/>
-      <c r="K190" s="7" t="n"/>
+      <c r="I190" s="8" t="n"/>
+      <c r="J190" s="8" t="n"/>
+      <c r="K190" s="8" t="n"/>
       <c r="L190" s="8" t="n"/>
       <c r="M190" s="8" t="n"/>
       <c r="N190" s="8" t="n"/>
       <c r="O190" s="8" t="n"/>
-      <c r="P190" s="9" t="n"/>
-      <c r="Q190" s="9" t="n"/>
+      <c r="P190" s="8" t="n"/>
+      <c r="Q190" s="8" t="n"/>
       <c r="R190" s="9" t="n"/>
       <c r="S190" s="9" t="n"/>
       <c r="T190" s="9" t="n"/>
       <c r="U190" s="9" t="n"/>
-      <c r="V190" s="9" t="n"/>
+      <c r="V190" s="10" t="n"/>
       <c r="W190" s="10" t="n"/>
       <c r="X190" s="10" t="n"/>
       <c r="Y190" s="10" t="n"/>
-      <c r="Z190" s="11" t="n"/>
-      <c r="AA190" s="11" t="n"/>
+      <c r="Z190" s="10" t="n"/>
+      <c r="AA190" s="10" t="n"/>
+      <c r="AB190" s="10" t="n"/>
+      <c r="AC190" s="11" t="n"/>
+      <c r="AD190" s="11" t="n"/>
+      <c r="AE190" s="11" t="n"/>
+      <c r="AF190" s="12" t="n"/>
+      <c r="AG190" s="12" t="n"/>
+      <c r="AH190" s="7" t="n"/>
     </row>
     <row r="191">
       <c r="A191" s="6" t="n"/>
@@ -6290,25 +7749,32 @@
       <c r="F191" s="7" t="n"/>
       <c r="G191" s="7" t="n"/>
       <c r="H191" s="7" t="n"/>
-      <c r="I191" s="7" t="n"/>
-      <c r="J191" s="7" t="n"/>
-      <c r="K191" s="7" t="n"/>
+      <c r="I191" s="8" t="n"/>
+      <c r="J191" s="8" t="n"/>
+      <c r="K191" s="8" t="n"/>
       <c r="L191" s="8" t="n"/>
       <c r="M191" s="8" t="n"/>
       <c r="N191" s="8" t="n"/>
       <c r="O191" s="8" t="n"/>
-      <c r="P191" s="9" t="n"/>
-      <c r="Q191" s="9" t="n"/>
+      <c r="P191" s="8" t="n"/>
+      <c r="Q191" s="8" t="n"/>
       <c r="R191" s="9" t="n"/>
       <c r="S191" s="9" t="n"/>
       <c r="T191" s="9" t="n"/>
       <c r="U191" s="9" t="n"/>
-      <c r="V191" s="9" t="n"/>
+      <c r="V191" s="10" t="n"/>
       <c r="W191" s="10" t="n"/>
       <c r="X191" s="10" t="n"/>
       <c r="Y191" s="10" t="n"/>
-      <c r="Z191" s="11" t="n"/>
-      <c r="AA191" s="11" t="n"/>
+      <c r="Z191" s="10" t="n"/>
+      <c r="AA191" s="10" t="n"/>
+      <c r="AB191" s="10" t="n"/>
+      <c r="AC191" s="11" t="n"/>
+      <c r="AD191" s="11" t="n"/>
+      <c r="AE191" s="11" t="n"/>
+      <c r="AF191" s="12" t="n"/>
+      <c r="AG191" s="12" t="n"/>
+      <c r="AH191" s="7" t="n"/>
     </row>
     <row r="192">
       <c r="A192" s="6" t="n"/>
@@ -6318,25 +7784,32 @@
       <c r="F192" s="7" t="n"/>
       <c r="G192" s="7" t="n"/>
       <c r="H192" s="7" t="n"/>
-      <c r="I192" s="7" t="n"/>
-      <c r="J192" s="7" t="n"/>
-      <c r="K192" s="7" t="n"/>
+      <c r="I192" s="8" t="n"/>
+      <c r="J192" s="8" t="n"/>
+      <c r="K192" s="8" t="n"/>
       <c r="L192" s="8" t="n"/>
       <c r="M192" s="8" t="n"/>
       <c r="N192" s="8" t="n"/>
       <c r="O192" s="8" t="n"/>
-      <c r="P192" s="9" t="n"/>
-      <c r="Q192" s="9" t="n"/>
+      <c r="P192" s="8" t="n"/>
+      <c r="Q192" s="8" t="n"/>
       <c r="R192" s="9" t="n"/>
       <c r="S192" s="9" t="n"/>
       <c r="T192" s="9" t="n"/>
       <c r="U192" s="9" t="n"/>
-      <c r="V192" s="9" t="n"/>
+      <c r="V192" s="10" t="n"/>
       <c r="W192" s="10" t="n"/>
       <c r="X192" s="10" t="n"/>
       <c r="Y192" s="10" t="n"/>
-      <c r="Z192" s="11" t="n"/>
-      <c r="AA192" s="11" t="n"/>
+      <c r="Z192" s="10" t="n"/>
+      <c r="AA192" s="10" t="n"/>
+      <c r="AB192" s="10" t="n"/>
+      <c r="AC192" s="11" t="n"/>
+      <c r="AD192" s="11" t="n"/>
+      <c r="AE192" s="11" t="n"/>
+      <c r="AF192" s="12" t="n"/>
+      <c r="AG192" s="12" t="n"/>
+      <c r="AH192" s="7" t="n"/>
     </row>
     <row r="193">
       <c r="A193" s="6" t="n"/>
@@ -6346,25 +7819,32 @@
       <c r="F193" s="7" t="n"/>
       <c r="G193" s="7" t="n"/>
       <c r="H193" s="7" t="n"/>
-      <c r="I193" s="7" t="n"/>
-      <c r="J193" s="7" t="n"/>
-      <c r="K193" s="7" t="n"/>
+      <c r="I193" s="8" t="n"/>
+      <c r="J193" s="8" t="n"/>
+      <c r="K193" s="8" t="n"/>
       <c r="L193" s="8" t="n"/>
       <c r="M193" s="8" t="n"/>
       <c r="N193" s="8" t="n"/>
       <c r="O193" s="8" t="n"/>
-      <c r="P193" s="9" t="n"/>
-      <c r="Q193" s="9" t="n"/>
+      <c r="P193" s="8" t="n"/>
+      <c r="Q193" s="8" t="n"/>
       <c r="R193" s="9" t="n"/>
       <c r="S193" s="9" t="n"/>
       <c r="T193" s="9" t="n"/>
       <c r="U193" s="9" t="n"/>
-      <c r="V193" s="9" t="n"/>
+      <c r="V193" s="10" t="n"/>
       <c r="W193" s="10" t="n"/>
       <c r="X193" s="10" t="n"/>
       <c r="Y193" s="10" t="n"/>
-      <c r="Z193" s="11" t="n"/>
-      <c r="AA193" s="11" t="n"/>
+      <c r="Z193" s="10" t="n"/>
+      <c r="AA193" s="10" t="n"/>
+      <c r="AB193" s="10" t="n"/>
+      <c r="AC193" s="11" t="n"/>
+      <c r="AD193" s="11" t="n"/>
+      <c r="AE193" s="11" t="n"/>
+      <c r="AF193" s="12" t="n"/>
+      <c r="AG193" s="12" t="n"/>
+      <c r="AH193" s="7" t="n"/>
     </row>
     <row r="194">
       <c r="A194" s="6" t="n"/>
@@ -6374,25 +7854,32 @@
       <c r="F194" s="7" t="n"/>
       <c r="G194" s="7" t="n"/>
       <c r="H194" s="7" t="n"/>
-      <c r="I194" s="7" t="n"/>
-      <c r="J194" s="7" t="n"/>
-      <c r="K194" s="7" t="n"/>
+      <c r="I194" s="8" t="n"/>
+      <c r="J194" s="8" t="n"/>
+      <c r="K194" s="8" t="n"/>
       <c r="L194" s="8" t="n"/>
       <c r="M194" s="8" t="n"/>
       <c r="N194" s="8" t="n"/>
       <c r="O194" s="8" t="n"/>
-      <c r="P194" s="9" t="n"/>
-      <c r="Q194" s="9" t="n"/>
+      <c r="P194" s="8" t="n"/>
+      <c r="Q194" s="8" t="n"/>
       <c r="R194" s="9" t="n"/>
       <c r="S194" s="9" t="n"/>
       <c r="T194" s="9" t="n"/>
       <c r="U194" s="9" t="n"/>
-      <c r="V194" s="9" t="n"/>
+      <c r="V194" s="10" t="n"/>
       <c r="W194" s="10" t="n"/>
       <c r="X194" s="10" t="n"/>
       <c r="Y194" s="10" t="n"/>
-      <c r="Z194" s="11" t="n"/>
-      <c r="AA194" s="11" t="n"/>
+      <c r="Z194" s="10" t="n"/>
+      <c r="AA194" s="10" t="n"/>
+      <c r="AB194" s="10" t="n"/>
+      <c r="AC194" s="11" t="n"/>
+      <c r="AD194" s="11" t="n"/>
+      <c r="AE194" s="11" t="n"/>
+      <c r="AF194" s="12" t="n"/>
+      <c r="AG194" s="12" t="n"/>
+      <c r="AH194" s="7" t="n"/>
     </row>
     <row r="195">
       <c r="A195" s="6" t="n"/>
@@ -6402,25 +7889,32 @@
       <c r="F195" s="7" t="n"/>
       <c r="G195" s="7" t="n"/>
       <c r="H195" s="7" t="n"/>
-      <c r="I195" s="7" t="n"/>
-      <c r="J195" s="7" t="n"/>
-      <c r="K195" s="7" t="n"/>
+      <c r="I195" s="8" t="n"/>
+      <c r="J195" s="8" t="n"/>
+      <c r="K195" s="8" t="n"/>
       <c r="L195" s="8" t="n"/>
       <c r="M195" s="8" t="n"/>
       <c r="N195" s="8" t="n"/>
       <c r="O195" s="8" t="n"/>
-      <c r="P195" s="9" t="n"/>
-      <c r="Q195" s="9" t="n"/>
+      <c r="P195" s="8" t="n"/>
+      <c r="Q195" s="8" t="n"/>
       <c r="R195" s="9" t="n"/>
       <c r="S195" s="9" t="n"/>
       <c r="T195" s="9" t="n"/>
       <c r="U195" s="9" t="n"/>
-      <c r="V195" s="9" t="n"/>
+      <c r="V195" s="10" t="n"/>
       <c r="W195" s="10" t="n"/>
       <c r="X195" s="10" t="n"/>
       <c r="Y195" s="10" t="n"/>
-      <c r="Z195" s="11" t="n"/>
-      <c r="AA195" s="11" t="n"/>
+      <c r="Z195" s="10" t="n"/>
+      <c r="AA195" s="10" t="n"/>
+      <c r="AB195" s="10" t="n"/>
+      <c r="AC195" s="11" t="n"/>
+      <c r="AD195" s="11" t="n"/>
+      <c r="AE195" s="11" t="n"/>
+      <c r="AF195" s="12" t="n"/>
+      <c r="AG195" s="12" t="n"/>
+      <c r="AH195" s="7" t="n"/>
     </row>
     <row r="196">
       <c r="A196" s="6" t="n"/>
@@ -6430,25 +7924,32 @@
       <c r="F196" s="7" t="n"/>
       <c r="G196" s="7" t="n"/>
       <c r="H196" s="7" t="n"/>
-      <c r="I196" s="7" t="n"/>
-      <c r="J196" s="7" t="n"/>
-      <c r="K196" s="7" t="n"/>
+      <c r="I196" s="8" t="n"/>
+      <c r="J196" s="8" t="n"/>
+      <c r="K196" s="8" t="n"/>
       <c r="L196" s="8" t="n"/>
       <c r="M196" s="8" t="n"/>
       <c r="N196" s="8" t="n"/>
       <c r="O196" s="8" t="n"/>
-      <c r="P196" s="9" t="n"/>
-      <c r="Q196" s="9" t="n"/>
+      <c r="P196" s="8" t="n"/>
+      <c r="Q196" s="8" t="n"/>
       <c r="R196" s="9" t="n"/>
       <c r="S196" s="9" t="n"/>
       <c r="T196" s="9" t="n"/>
       <c r="U196" s="9" t="n"/>
-      <c r="V196" s="9" t="n"/>
+      <c r="V196" s="10" t="n"/>
       <c r="W196" s="10" t="n"/>
       <c r="X196" s="10" t="n"/>
       <c r="Y196" s="10" t="n"/>
-      <c r="Z196" s="11" t="n"/>
-      <c r="AA196" s="11" t="n"/>
+      <c r="Z196" s="10" t="n"/>
+      <c r="AA196" s="10" t="n"/>
+      <c r="AB196" s="10" t="n"/>
+      <c r="AC196" s="11" t="n"/>
+      <c r="AD196" s="11" t="n"/>
+      <c r="AE196" s="11" t="n"/>
+      <c r="AF196" s="12" t="n"/>
+      <c r="AG196" s="12" t="n"/>
+      <c r="AH196" s="7" t="n"/>
     </row>
     <row r="197">
       <c r="A197" s="6" t="n"/>
@@ -6458,25 +7959,32 @@
       <c r="F197" s="7" t="n"/>
       <c r="G197" s="7" t="n"/>
       <c r="H197" s="7" t="n"/>
-      <c r="I197" s="7" t="n"/>
-      <c r="J197" s="7" t="n"/>
-      <c r="K197" s="7" t="n"/>
+      <c r="I197" s="8" t="n"/>
+      <c r="J197" s="8" t="n"/>
+      <c r="K197" s="8" t="n"/>
       <c r="L197" s="8" t="n"/>
       <c r="M197" s="8" t="n"/>
       <c r="N197" s="8" t="n"/>
       <c r="O197" s="8" t="n"/>
-      <c r="P197" s="9" t="n"/>
-      <c r="Q197" s="9" t="n"/>
+      <c r="P197" s="8" t="n"/>
+      <c r="Q197" s="8" t="n"/>
       <c r="R197" s="9" t="n"/>
       <c r="S197" s="9" t="n"/>
       <c r="T197" s="9" t="n"/>
       <c r="U197" s="9" t="n"/>
-      <c r="V197" s="9" t="n"/>
+      <c r="V197" s="10" t="n"/>
       <c r="W197" s="10" t="n"/>
       <c r="X197" s="10" t="n"/>
       <c r="Y197" s="10" t="n"/>
-      <c r="Z197" s="11" t="n"/>
-      <c r="AA197" s="11" t="n"/>
+      <c r="Z197" s="10" t="n"/>
+      <c r="AA197" s="10" t="n"/>
+      <c r="AB197" s="10" t="n"/>
+      <c r="AC197" s="11" t="n"/>
+      <c r="AD197" s="11" t="n"/>
+      <c r="AE197" s="11" t="n"/>
+      <c r="AF197" s="12" t="n"/>
+      <c r="AG197" s="12" t="n"/>
+      <c r="AH197" s="7" t="n"/>
     </row>
     <row r="198">
       <c r="A198" s="6" t="n"/>
@@ -6486,25 +7994,32 @@
       <c r="F198" s="7" t="n"/>
       <c r="G198" s="7" t="n"/>
       <c r="H198" s="7" t="n"/>
-      <c r="I198" s="7" t="n"/>
-      <c r="J198" s="7" t="n"/>
-      <c r="K198" s="7" t="n"/>
+      <c r="I198" s="8" t="n"/>
+      <c r="J198" s="8" t="n"/>
+      <c r="K198" s="8" t="n"/>
       <c r="L198" s="8" t="n"/>
       <c r="M198" s="8" t="n"/>
       <c r="N198" s="8" t="n"/>
       <c r="O198" s="8" t="n"/>
-      <c r="P198" s="9" t="n"/>
-      <c r="Q198" s="9" t="n"/>
+      <c r="P198" s="8" t="n"/>
+      <c r="Q198" s="8" t="n"/>
       <c r="R198" s="9" t="n"/>
       <c r="S198" s="9" t="n"/>
       <c r="T198" s="9" t="n"/>
       <c r="U198" s="9" t="n"/>
-      <c r="V198" s="9" t="n"/>
+      <c r="V198" s="10" t="n"/>
       <c r="W198" s="10" t="n"/>
       <c r="X198" s="10" t="n"/>
       <c r="Y198" s="10" t="n"/>
-      <c r="Z198" s="11" t="n"/>
-      <c r="AA198" s="11" t="n"/>
+      <c r="Z198" s="10" t="n"/>
+      <c r="AA198" s="10" t="n"/>
+      <c r="AB198" s="10" t="n"/>
+      <c r="AC198" s="11" t="n"/>
+      <c r="AD198" s="11" t="n"/>
+      <c r="AE198" s="11" t="n"/>
+      <c r="AF198" s="12" t="n"/>
+      <c r="AG198" s="12" t="n"/>
+      <c r="AH198" s="7" t="n"/>
     </row>
     <row r="199">
       <c r="A199" s="6" t="n"/>
@@ -6514,25 +8029,32 @@
       <c r="F199" s="7" t="n"/>
       <c r="G199" s="7" t="n"/>
       <c r="H199" s="7" t="n"/>
-      <c r="I199" s="7" t="n"/>
-      <c r="J199" s="7" t="n"/>
-      <c r="K199" s="7" t="n"/>
+      <c r="I199" s="8" t="n"/>
+      <c r="J199" s="8" t="n"/>
+      <c r="K199" s="8" t="n"/>
       <c r="L199" s="8" t="n"/>
       <c r="M199" s="8" t="n"/>
       <c r="N199" s="8" t="n"/>
       <c r="O199" s="8" t="n"/>
-      <c r="P199" s="9" t="n"/>
-      <c r="Q199" s="9" t="n"/>
+      <c r="P199" s="8" t="n"/>
+      <c r="Q199" s="8" t="n"/>
       <c r="R199" s="9" t="n"/>
       <c r="S199" s="9" t="n"/>
       <c r="T199" s="9" t="n"/>
       <c r="U199" s="9" t="n"/>
-      <c r="V199" s="9" t="n"/>
+      <c r="V199" s="10" t="n"/>
       <c r="W199" s="10" t="n"/>
       <c r="X199" s="10" t="n"/>
       <c r="Y199" s="10" t="n"/>
-      <c r="Z199" s="11" t="n"/>
-      <c r="AA199" s="11" t="n"/>
+      <c r="Z199" s="10" t="n"/>
+      <c r="AA199" s="10" t="n"/>
+      <c r="AB199" s="10" t="n"/>
+      <c r="AC199" s="11" t="n"/>
+      <c r="AD199" s="11" t="n"/>
+      <c r="AE199" s="11" t="n"/>
+      <c r="AF199" s="12" t="n"/>
+      <c r="AG199" s="12" t="n"/>
+      <c r="AH199" s="7" t="n"/>
     </row>
     <row r="200">
       <c r="A200" s="6" t="n"/>
@@ -6542,25 +8064,32 @@
       <c r="F200" s="7" t="n"/>
       <c r="G200" s="7" t="n"/>
       <c r="H200" s="7" t="n"/>
-      <c r="I200" s="7" t="n"/>
-      <c r="J200" s="7" t="n"/>
-      <c r="K200" s="7" t="n"/>
+      <c r="I200" s="8" t="n"/>
+      <c r="J200" s="8" t="n"/>
+      <c r="K200" s="8" t="n"/>
       <c r="L200" s="8" t="n"/>
       <c r="M200" s="8" t="n"/>
       <c r="N200" s="8" t="n"/>
       <c r="O200" s="8" t="n"/>
-      <c r="P200" s="9" t="n"/>
-      <c r="Q200" s="9" t="n"/>
+      <c r="P200" s="8" t="n"/>
+      <c r="Q200" s="8" t="n"/>
       <c r="R200" s="9" t="n"/>
       <c r="S200" s="9" t="n"/>
       <c r="T200" s="9" t="n"/>
       <c r="U200" s="9" t="n"/>
-      <c r="V200" s="9" t="n"/>
+      <c r="V200" s="10" t="n"/>
       <c r="W200" s="10" t="n"/>
       <c r="X200" s="10" t="n"/>
       <c r="Y200" s="10" t="n"/>
-      <c r="Z200" s="11" t="n"/>
-      <c r="AA200" s="11" t="n"/>
+      <c r="Z200" s="10" t="n"/>
+      <c r="AA200" s="10" t="n"/>
+      <c r="AB200" s="10" t="n"/>
+      <c r="AC200" s="11" t="n"/>
+      <c r="AD200" s="11" t="n"/>
+      <c r="AE200" s="11" t="n"/>
+      <c r="AF200" s="12" t="n"/>
+      <c r="AG200" s="12" t="n"/>
+      <c r="AH200" s="7" t="n"/>
     </row>
     <row r="201">
       <c r="A201" s="6" t="n"/>
@@ -6570,25 +8099,32 @@
       <c r="F201" s="7" t="n"/>
       <c r="G201" s="7" t="n"/>
       <c r="H201" s="7" t="n"/>
-      <c r="I201" s="7" t="n"/>
-      <c r="J201" s="7" t="n"/>
-      <c r="K201" s="7" t="n"/>
+      <c r="I201" s="8" t="n"/>
+      <c r="J201" s="8" t="n"/>
+      <c r="K201" s="8" t="n"/>
       <c r="L201" s="8" t="n"/>
       <c r="M201" s="8" t="n"/>
       <c r="N201" s="8" t="n"/>
       <c r="O201" s="8" t="n"/>
-      <c r="P201" s="9" t="n"/>
-      <c r="Q201" s="9" t="n"/>
+      <c r="P201" s="8" t="n"/>
+      <c r="Q201" s="8" t="n"/>
       <c r="R201" s="9" t="n"/>
       <c r="S201" s="9" t="n"/>
       <c r="T201" s="9" t="n"/>
       <c r="U201" s="9" t="n"/>
-      <c r="V201" s="9" t="n"/>
+      <c r="V201" s="10" t="n"/>
       <c r="W201" s="10" t="n"/>
       <c r="X201" s="10" t="n"/>
       <c r="Y201" s="10" t="n"/>
-      <c r="Z201" s="11" t="n"/>
-      <c r="AA201" s="11" t="n"/>
+      <c r="Z201" s="10" t="n"/>
+      <c r="AA201" s="10" t="n"/>
+      <c r="AB201" s="10" t="n"/>
+      <c r="AC201" s="11" t="n"/>
+      <c r="AD201" s="11" t="n"/>
+      <c r="AE201" s="11" t="n"/>
+      <c r="AF201" s="12" t="n"/>
+      <c r="AG201" s="12" t="n"/>
+      <c r="AH201" s="7" t="n"/>
     </row>
     <row r="202">
       <c r="A202" s="6" t="n"/>
@@ -14998,7 +16534,7 @@
     <dataValidation sqref="A2:A3001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Date" error="Date au format JJ/MM/AAAA" type="date" operator="greaterThan">
       <formula1>DATE(2020,1,1)</formula1>
     </dataValidation>
-    <dataValidation sqref="C2:AA3001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Nombre" error="Nombre entier positif ou case vide" type="whole" operator="greaterThanOrEqual">
+    <dataValidation sqref="C2:AG3001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Nombre" error="Nombre entier positif ou case vide" type="whole" operator="greaterThanOrEqual">
       <formula1>0</formula1>
     </dataValidation>
   </dataValidations>
